--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131860591</v>
+        <v>131860622</v>
       </c>
       <c r="B2" t="n">
-        <v>91832</v>
+        <v>92292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>669198</v>
+        <v>669211</v>
       </c>
       <c r="R2" t="n">
-        <v>6692769</v>
+        <v>6692779</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -756,6 +756,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -772,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131860688</v>
+        <v>131860605</v>
       </c>
       <c r="B3" t="n">
-        <v>92487</v>
+        <v>96378</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1339</v>
+        <v>2818</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>669177</v>
+        <v>668988</v>
       </c>
       <c r="R3" t="n">
-        <v>6692736</v>
+        <v>6692259</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -853,21 +868,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131860605</v>
+        <v>131860688</v>
       </c>
       <c r="B4" t="n">
-        <v>96378</v>
+        <v>92487</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2818</v>
+        <v>1339</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668988</v>
+        <v>669177</v>
       </c>
       <c r="R4" t="n">
-        <v>6692259</v>
+        <v>6692736</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -965,6 +965,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -981,32 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131860622</v>
+        <v>131860591</v>
       </c>
       <c r="B5" t="n">
-        <v>92292</v>
+        <v>91832</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>669211</v>
+        <v>669198</v>
       </c>
       <c r="R5" t="n">
-        <v>6692779</v>
+        <v>6692769</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1062,21 +1077,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131860656</v>
+        <v>131860695</v>
       </c>
       <c r="B8" t="n">
-        <v>4780</v>
+        <v>101243</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>669149</v>
+        <v>669270</v>
       </c>
       <c r="R8" t="n">
-        <v>6692521</v>
+        <v>6692768</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1388,21 +1388,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1419,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131860695</v>
+        <v>131860656</v>
       </c>
       <c r="B9" t="n">
-        <v>101243</v>
+        <v>4780</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1430,21 +1415,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>669270</v>
+        <v>669149</v>
       </c>
       <c r="R9" t="n">
-        <v>6692768</v>
+        <v>6692521</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1500,6 +1485,21 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1613,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131860637</v>
+        <v>131860684</v>
       </c>
       <c r="B11" t="n">
-        <v>80329</v>
+        <v>80304</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1624,21 +1624,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229497</v>
+        <v>6457</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>669335</v>
+        <v>669173</v>
       </c>
       <c r="R11" t="n">
-        <v>6692778</v>
+        <v>6692783</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1725,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131860684</v>
+        <v>131860637</v>
       </c>
       <c r="B12" t="n">
-        <v>80304</v>
+        <v>80329</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1736,21 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6457</v>
+        <v>229497</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>669173</v>
+        <v>669335</v>
       </c>
       <c r="R12" t="n">
-        <v>6692783</v>
+        <v>6692778</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -2158,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131860616</v>
+        <v>131860604</v>
       </c>
       <c r="B16" t="n">
-        <v>80273</v>
+        <v>96378</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2169,34 +2169,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6456</v>
+        <v>2818</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>669151</v>
+        <v>669204</v>
       </c>
       <c r="R16" t="n">
-        <v>6692600</v>
+        <v>6692601</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2231,33 +2235,29 @@
           <t>2026-03-22</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2275,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131860603</v>
+        <v>131860616</v>
       </c>
       <c r="B17" t="n">
-        <v>96378</v>
+        <v>80273</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2286,21 +2286,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2818</v>
+        <v>6456</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>669306</v>
+        <v>669151</v>
       </c>
       <c r="R17" t="n">
-        <v>6692797</v>
+        <v>6692600</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2348,6 +2348,11 @@
           <t>2026-03-22</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2359,17 +2364,17 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2387,7 +2392,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131860604</v>
+        <v>131860603</v>
       </c>
       <c r="B18" t="n">
         <v>96378</v>
@@ -2416,20 +2421,16 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>669204</v>
+        <v>669306</v>
       </c>
       <c r="R18" t="n">
-        <v>6692601</v>
+        <v>6692797</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2470,23 +2471,22 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2601,32 +2601,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131860588</v>
+        <v>131860618</v>
       </c>
       <c r="B20" t="n">
-        <v>91832</v>
+        <v>80273</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>669143</v>
+        <v>669202</v>
       </c>
       <c r="R20" t="n">
-        <v>6692724</v>
+        <v>6692608</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2682,6 +2682,21 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2698,32 +2713,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131860618</v>
+        <v>131860589</v>
       </c>
       <c r="B21" t="n">
-        <v>80273</v>
+        <v>91832</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2733,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>669202</v>
+        <v>669210</v>
       </c>
       <c r="R21" t="n">
-        <v>6692608</v>
+        <v>6692779</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2779,21 +2794,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2810,32 +2810,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131860635</v>
+        <v>131860588</v>
       </c>
       <c r="B22" t="n">
-        <v>80329</v>
+        <v>91832</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>669236</v>
+        <v>669143</v>
       </c>
       <c r="R22" t="n">
-        <v>6692814</v>
+        <v>6692724</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2891,21 +2891,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2922,32 +2907,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131860589</v>
+        <v>131860635</v>
       </c>
       <c r="B23" t="n">
-        <v>91832</v>
+        <v>80329</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2957,10 +2942,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>669210</v>
+        <v>669236</v>
       </c>
       <c r="R23" t="n">
-        <v>6692779</v>
+        <v>6692814</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3003,6 +2988,21 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3325,50 +3325,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131860609</v>
+        <v>131860696</v>
       </c>
       <c r="B27" t="n">
-        <v>57899</v>
+        <v>101243</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>669095</v>
+        <v>669141</v>
       </c>
       <c r="R27" t="n">
-        <v>6692372</v>
+        <v>6692607</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3427,10 +3422,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131860690</v>
+        <v>131860694</v>
       </c>
       <c r="B28" t="n">
-        <v>92487</v>
+        <v>101243</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3438,21 +3433,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3462,10 +3457,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>669205</v>
+        <v>669321</v>
       </c>
       <c r="R28" t="n">
-        <v>6692610</v>
+        <v>6692768</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3508,21 +3503,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3539,10 +3519,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131860694</v>
+        <v>131860690</v>
       </c>
       <c r="B29" t="n">
-        <v>101243</v>
+        <v>92487</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3550,21 +3530,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>1339</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3574,10 +3554,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>669321</v>
+        <v>669205</v>
       </c>
       <c r="R29" t="n">
-        <v>6692768</v>
+        <v>6692610</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3620,6 +3600,21 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3636,45 +3631,50 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131860696</v>
+        <v>131860609</v>
       </c>
       <c r="B30" t="n">
-        <v>101243</v>
+        <v>57899</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>669141</v>
+        <v>669095</v>
       </c>
       <c r="R30" t="n">
-        <v>6692607</v>
+        <v>6692372</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3733,7 +3733,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131860613</v>
+        <v>131860615</v>
       </c>
       <c r="B31" t="n">
         <v>80273</v>
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>669232</v>
+        <v>669217</v>
       </c>
       <c r="R31" t="n">
-        <v>6692800</v>
+        <v>6692612</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3957,10 +3957,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131860689</v>
+        <v>131860613</v>
       </c>
       <c r="B33" t="n">
-        <v>92487</v>
+        <v>80273</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3968,21 +3968,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1339</v>
+        <v>6456</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3992,10 +3992,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>669316</v>
+        <v>669232</v>
       </c>
       <c r="R33" t="n">
-        <v>6692776</v>
+        <v>6692800</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4041,17 +4041,17 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4293,10 +4293,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131860615</v>
+        <v>131860689</v>
       </c>
       <c r="B36" t="n">
-        <v>80273</v>
+        <v>92487</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4304,21 +4304,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6456</v>
+        <v>1339</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4328,10 +4328,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>669217</v>
+        <v>669316</v>
       </c>
       <c r="R36" t="n">
-        <v>6692612</v>
+        <v>6692776</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4377,17 +4377,17 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4696,10 +4696,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131860699</v>
+        <v>131860655</v>
       </c>
       <c r="B40" t="n">
-        <v>101243</v>
+        <v>4780</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4707,21 +4707,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4731,10 +4731,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>668997</v>
+        <v>669222</v>
       </c>
       <c r="R40" t="n">
-        <v>6692214</v>
+        <v>6692642</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4777,6 +4777,21 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4793,7 +4808,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131860655</v>
+        <v>131860654</v>
       </c>
       <c r="B41" t="n">
         <v>4780</v>
@@ -4828,10 +4843,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>669222</v>
+        <v>669197</v>
       </c>
       <c r="R41" t="n">
-        <v>6692642</v>
+        <v>6692720</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5002,10 +5017,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131860654</v>
+        <v>131860699</v>
       </c>
       <c r="B43" t="n">
-        <v>4780</v>
+        <v>101243</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5013,21 +5028,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5037,10 +5052,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>669197</v>
+        <v>668997</v>
       </c>
       <c r="R43" t="n">
-        <v>6692720</v>
+        <v>6692214</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5083,21 +5098,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5226,10 +5226,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131860642</v>
+        <v>131860648</v>
       </c>
       <c r="B45" t="n">
-        <v>80329</v>
+        <v>75370</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5237,21 +5237,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229497</v>
+        <v>6426</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>669212</v>
+        <v>669219</v>
       </c>
       <c r="R45" t="n">
-        <v>6692609</v>
+        <v>6692641</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5307,21 +5307,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5338,10 +5323,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131860648</v>
+        <v>131860620</v>
       </c>
       <c r="B46" t="n">
-        <v>75370</v>
+        <v>80273</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5349,21 +5334,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6426</v>
+        <v>6456</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5373,10 +5358,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>669219</v>
+        <v>669176</v>
       </c>
       <c r="R46" t="n">
-        <v>6692641</v>
+        <v>6692603</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5419,6 +5404,21 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5435,10 +5435,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131860620</v>
+        <v>131860642</v>
       </c>
       <c r="B47" t="n">
-        <v>80273</v>
+        <v>80329</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5446,21 +5446,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5470,10 +5470,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>669176</v>
+        <v>669212</v>
       </c>
       <c r="R47" t="n">
-        <v>6692603</v>
+        <v>6692609</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5659,10 +5659,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131860634</v>
+        <v>131860685</v>
       </c>
       <c r="B49" t="n">
-        <v>80329</v>
+        <v>80304</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5670,21 +5670,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229497</v>
+        <v>6457</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>669233</v>
+        <v>669242</v>
       </c>
       <c r="R49" t="n">
-        <v>6692806</v>
+        <v>6692625</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5771,10 +5771,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131860685</v>
+        <v>131860634</v>
       </c>
       <c r="B50" t="n">
-        <v>80304</v>
+        <v>80329</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5782,21 +5782,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6457</v>
+        <v>229497</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5806,10 +5806,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>669242</v>
+        <v>669233</v>
       </c>
       <c r="R50" t="n">
-        <v>6692625</v>
+        <v>6692806</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5883,10 +5883,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131860691</v>
+        <v>131860683</v>
       </c>
       <c r="B51" t="n">
-        <v>92487</v>
+        <v>80304</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5894,21 +5894,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1339</v>
+        <v>6457</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5918,10 +5918,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>669198</v>
+        <v>669167</v>
       </c>
       <c r="R51" t="n">
-        <v>6692600</v>
+        <v>6692763</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5967,17 +5967,17 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -5995,10 +5995,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131860683</v>
+        <v>131860691</v>
       </c>
       <c r="B52" t="n">
-        <v>80304</v>
+        <v>92487</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6006,21 +6006,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6457</v>
+        <v>1339</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6030,10 +6030,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>669167</v>
+        <v>669198</v>
       </c>
       <c r="R52" t="n">
-        <v>6692763</v>
+        <v>6692600</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6079,17 +6079,17 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6107,10 +6107,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131860643</v>
+        <v>131860651</v>
       </c>
       <c r="B53" t="n">
-        <v>80329</v>
+        <v>96474</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6118,21 +6118,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229497</v>
+        <v>210</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6142,10 +6142,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>669201</v>
+        <v>669305</v>
       </c>
       <c r="R53" t="n">
-        <v>6692608</v>
+        <v>6692798</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6191,17 +6191,17 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6219,10 +6219,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131860651</v>
+        <v>131860641</v>
       </c>
       <c r="B54" t="n">
-        <v>96474</v>
+        <v>80329</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6230,21 +6230,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>210</v>
+        <v>229497</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6254,10 +6254,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>669305</v>
+        <v>669218</v>
       </c>
       <c r="R54" t="n">
-        <v>6692798</v>
+        <v>6692611</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6303,17 +6303,17 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6331,7 +6331,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131860641</v>
+        <v>131860643</v>
       </c>
       <c r="B55" t="n">
         <v>80329</v>
@@ -6366,10 +6366,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>669218</v>
+        <v>669201</v>
       </c>
       <c r="R55" t="n">
-        <v>6692611</v>
+        <v>6692608</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -1516,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131860649</v>
+        <v>131860684</v>
       </c>
       <c r="B10" t="n">
-        <v>96474</v>
+        <v>80304</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1527,21 +1527,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>210</v>
+        <v>6457</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>669159</v>
+        <v>669173</v>
       </c>
       <c r="R10" t="n">
-        <v>6692588</v>
+        <v>6692783</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1597,6 +1597,21 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1613,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131860684</v>
+        <v>131860649</v>
       </c>
       <c r="B11" t="n">
-        <v>80304</v>
+        <v>96474</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1624,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6457</v>
+        <v>210</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>669173</v>
+        <v>669159</v>
       </c>
       <c r="R11" t="n">
-        <v>6692783</v>
+        <v>6692588</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1694,21 +1709,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -2713,7 +2713,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131860589</v>
+        <v>131860588</v>
       </c>
       <c r="B21" t="n">
         <v>91832</v>
@@ -2748,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>669210</v>
+        <v>669143</v>
       </c>
       <c r="R21" t="n">
-        <v>6692779</v>
+        <v>6692724</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2810,32 +2810,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131860588</v>
+        <v>131860635</v>
       </c>
       <c r="B22" t="n">
-        <v>91832</v>
+        <v>80329</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>669143</v>
+        <v>669236</v>
       </c>
       <c r="R22" t="n">
-        <v>6692724</v>
+        <v>6692814</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2891,6 +2891,21 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2907,10 +2922,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131860635</v>
+        <v>131860702</v>
       </c>
       <c r="B23" t="n">
-        <v>80329</v>
+        <v>101243</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2918,21 +2933,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2942,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>669236</v>
+        <v>669289</v>
       </c>
       <c r="R23" t="n">
-        <v>6692814</v>
+        <v>6692778</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2988,21 +3003,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3019,32 +3019,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131860702</v>
+        <v>131860589</v>
       </c>
       <c r="B24" t="n">
-        <v>101243</v>
+        <v>91832</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>669289</v>
+        <v>669210</v>
       </c>
       <c r="R24" t="n">
-        <v>6692778</v>
+        <v>6692779</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3733,10 +3733,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131860615</v>
+        <v>131860689</v>
       </c>
       <c r="B31" t="n">
-        <v>80273</v>
+        <v>92487</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3744,21 +3744,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6456</v>
+        <v>1339</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>669217</v>
+        <v>669316</v>
       </c>
       <c r="R31" t="n">
-        <v>6692612</v>
+        <v>6692776</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3817,17 +3817,17 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -3845,32 +3845,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131860662</v>
+        <v>131860615</v>
       </c>
       <c r="B32" t="n">
-        <v>79264</v>
+        <v>80273</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3880,10 +3880,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>669203</v>
+        <v>669217</v>
       </c>
       <c r="R32" t="n">
-        <v>6692759</v>
+        <v>6692612</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3929,17 +3929,17 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -3957,32 +3957,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131860613</v>
+        <v>131860662</v>
       </c>
       <c r="B33" t="n">
-        <v>80273</v>
+        <v>79264</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3992,10 +3992,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>669232</v>
+        <v>669203</v>
       </c>
       <c r="R33" t="n">
-        <v>6692800</v>
+        <v>6692759</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4041,17 +4041,17 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4069,32 +4069,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131860661</v>
+        <v>131860613</v>
       </c>
       <c r="B34" t="n">
-        <v>79264</v>
+        <v>80273</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>669202</v>
+        <v>669232</v>
       </c>
       <c r="R34" t="n">
-        <v>6692764</v>
+        <v>6692800</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4153,17 +4153,17 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4181,32 +4181,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131860687</v>
+        <v>131860661</v>
       </c>
       <c r="B35" t="n">
-        <v>5178</v>
+        <v>79264</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4216,10 +4216,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>669223</v>
+        <v>669202</v>
       </c>
       <c r="R35" t="n">
-        <v>6692603</v>
+        <v>6692764</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4293,10 +4293,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131860689</v>
+        <v>131860687</v>
       </c>
       <c r="B36" t="n">
-        <v>92487</v>
+        <v>5178</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4304,21 +4304,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1339</v>
+        <v>100526</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4328,10 +4328,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>669316</v>
+        <v>669223</v>
       </c>
       <c r="R36" t="n">
-        <v>6692776</v>
+        <v>6692603</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -5114,10 +5114,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131860652</v>
+        <v>131860648</v>
       </c>
       <c r="B44" t="n">
-        <v>96474</v>
+        <v>75370</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5125,21 +5125,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>210</v>
+        <v>6426</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5149,10 +5149,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>668992</v>
+        <v>669219</v>
       </c>
       <c r="R44" t="n">
-        <v>6692504</v>
+        <v>6692641</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5195,21 +5195,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5226,10 +5211,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131860648</v>
+        <v>131860620</v>
       </c>
       <c r="B45" t="n">
-        <v>75370</v>
+        <v>80273</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5237,21 +5222,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6426</v>
+        <v>6456</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5261,10 +5246,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>669219</v>
+        <v>669176</v>
       </c>
       <c r="R45" t="n">
-        <v>6692641</v>
+        <v>6692603</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5307,6 +5292,21 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5323,10 +5323,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131860620</v>
+        <v>131860642</v>
       </c>
       <c r="B46" t="n">
-        <v>80273</v>
+        <v>80329</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5334,21 +5334,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5358,10 +5358,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>669176</v>
+        <v>669212</v>
       </c>
       <c r="R46" t="n">
-        <v>6692603</v>
+        <v>6692609</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5435,7 +5435,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131860642</v>
+        <v>131860639</v>
       </c>
       <c r="B47" t="n">
         <v>80329</v>
@@ -5470,10 +5470,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>669212</v>
+        <v>669215</v>
       </c>
       <c r="R47" t="n">
-        <v>6692609</v>
+        <v>6692608</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5547,10 +5547,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131860639</v>
+        <v>131860652</v>
       </c>
       <c r="B48" t="n">
-        <v>80329</v>
+        <v>96474</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5558,21 +5558,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229497</v>
+        <v>210</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5582,10 +5582,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>669215</v>
+        <v>668992</v>
       </c>
       <c r="R48" t="n">
-        <v>6692608</v>
+        <v>6692504</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5631,17 +5631,17 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5659,10 +5659,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131860685</v>
+        <v>131860634</v>
       </c>
       <c r="B49" t="n">
-        <v>80304</v>
+        <v>80329</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5670,21 +5670,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6457</v>
+        <v>229497</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>669242</v>
+        <v>669233</v>
       </c>
       <c r="R49" t="n">
-        <v>6692625</v>
+        <v>6692806</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5771,10 +5771,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131860634</v>
+        <v>131860685</v>
       </c>
       <c r="B50" t="n">
-        <v>80329</v>
+        <v>80304</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5782,21 +5782,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>229497</v>
+        <v>6457</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5806,10 +5806,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>669233</v>
+        <v>669242</v>
       </c>
       <c r="R50" t="n">
-        <v>6692806</v>
+        <v>6692625</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6107,10 +6107,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131860651</v>
+        <v>131860641</v>
       </c>
       <c r="B53" t="n">
-        <v>96474</v>
+        <v>80329</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6118,21 +6118,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>210</v>
+        <v>229497</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6142,10 +6142,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>669305</v>
+        <v>669218</v>
       </c>
       <c r="R53" t="n">
-        <v>6692798</v>
+        <v>6692611</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6191,17 +6191,17 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6219,7 +6219,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131860641</v>
+        <v>131860643</v>
       </c>
       <c r="B54" t="n">
         <v>80329</v>
@@ -6254,10 +6254,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>669218</v>
+        <v>669201</v>
       </c>
       <c r="R54" t="n">
-        <v>6692611</v>
+        <v>6692608</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6331,10 +6331,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131860643</v>
+        <v>131860651</v>
       </c>
       <c r="B55" t="n">
-        <v>80329</v>
+        <v>96474</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6342,21 +6342,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>229497</v>
+        <v>210</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6366,10 +6366,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>669201</v>
+        <v>669305</v>
       </c>
       <c r="R55" t="n">
-        <v>6692608</v>
+        <v>6692798</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6415,17 +6415,17 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131860622</v>
+        <v>131860605</v>
       </c>
       <c r="B2" t="n">
-        <v>92292</v>
+        <v>96384</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>2818</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>669211</v>
+        <v>668988</v>
       </c>
       <c r="R2" t="n">
-        <v>6692779</v>
+        <v>6692259</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -756,21 +756,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -787,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131860605</v>
+        <v>131860622</v>
       </c>
       <c r="B3" t="n">
-        <v>96378</v>
+        <v>92298</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2818</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>668988</v>
+        <v>669211</v>
       </c>
       <c r="R3" t="n">
-        <v>6692259</v>
+        <v>6692779</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -868,6 +853,21 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -887,7 +887,7 @@
         <v>131860688</v>
       </c>
       <c r="B4" t="n">
-        <v>92487</v>
+        <v>92493</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>131860591</v>
       </c>
       <c r="B5" t="n">
-        <v>91832</v>
+        <v>91838</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>131860608</v>
       </c>
       <c r="B6" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131860695</v>
+        <v>131860656</v>
       </c>
       <c r="B8" t="n">
-        <v>101243</v>
+        <v>4780</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>669270</v>
+        <v>669149</v>
       </c>
       <c r="R8" t="n">
-        <v>6692768</v>
+        <v>6692521</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1388,6 +1388,21 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1404,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131860656</v>
+        <v>131860695</v>
       </c>
       <c r="B9" t="n">
-        <v>4780</v>
+        <v>101249</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1415,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>669149</v>
+        <v>669270</v>
       </c>
       <c r="R9" t="n">
-        <v>6692521</v>
+        <v>6692768</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1486,21 +1501,6 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
+          <t>Åsa Nordling, Ingemar Södergren, Tove Widén</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1519,7 +1519,7 @@
         <v>131860684</v>
       </c>
       <c r="B10" t="n">
-        <v>80304</v>
+        <v>80306</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131860649</v>
+        <v>131860637</v>
       </c>
       <c r="B11" t="n">
-        <v>96474</v>
+        <v>80331</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1639,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>210</v>
+        <v>229497</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>669159</v>
+        <v>669335</v>
       </c>
       <c r="R11" t="n">
-        <v>6692588</v>
+        <v>6692778</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1709,6 +1709,21 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1725,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131860637</v>
+        <v>131860649</v>
       </c>
       <c r="B12" t="n">
-        <v>80329</v>
+        <v>96480</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1736,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229497</v>
+        <v>210</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>669335</v>
+        <v>669159</v>
       </c>
       <c r="R12" t="n">
-        <v>6692778</v>
+        <v>6692588</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1806,21 +1821,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1840,7 +1840,7 @@
         <v>131860660</v>
       </c>
       <c r="B13" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>131860697</v>
       </c>
       <c r="B14" t="n">
-        <v>101243</v>
+        <v>101249</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>131860614</v>
       </c>
       <c r="B15" t="n">
-        <v>80273</v>
+        <v>80275</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2158,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131860604</v>
+        <v>131860603</v>
       </c>
       <c r="B16" t="n">
-        <v>96378</v>
+        <v>96384</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2187,20 +2187,16 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>669204</v>
+        <v>669306</v>
       </c>
       <c r="R16" t="n">
-        <v>6692601</v>
+        <v>6692797</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2241,23 +2237,22 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2275,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131860616</v>
+        <v>131860604</v>
       </c>
       <c r="B17" t="n">
-        <v>80273</v>
+        <v>96384</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2286,34 +2281,38 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6456</v>
+        <v>2818</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>669151</v>
+        <v>669204</v>
       </c>
       <c r="R17" t="n">
-        <v>6692600</v>
+        <v>6692601</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2348,33 +2347,29 @@
           <t>2026-03-22</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2392,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131860603</v>
+        <v>131860616</v>
       </c>
       <c r="B18" t="n">
-        <v>96378</v>
+        <v>80275</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2403,21 +2398,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2818</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2427,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>669306</v>
+        <v>669151</v>
       </c>
       <c r="R18" t="n">
-        <v>6692797</v>
+        <v>6692600</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2465,6 +2460,11 @@
           <t>2026-03-22</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2476,17 +2476,17 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2507,7 +2507,7 @@
         <v>131860595</v>
       </c>
       <c r="B19" t="n">
-        <v>91832</v>
+        <v>91838</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,32 +2601,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131860618</v>
+        <v>131860589</v>
       </c>
       <c r="B20" t="n">
-        <v>80273</v>
+        <v>91838</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>669202</v>
+        <v>669210</v>
       </c>
       <c r="R20" t="n">
-        <v>6692608</v>
+        <v>6692779</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2682,21 +2682,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2716,7 +2701,7 @@
         <v>131860588</v>
       </c>
       <c r="B21" t="n">
-        <v>91832</v>
+        <v>91838</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2810,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131860635</v>
+        <v>131860618</v>
       </c>
       <c r="B22" t="n">
-        <v>80329</v>
+        <v>80275</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2821,21 +2806,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2845,10 +2830,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>669236</v>
+        <v>669202</v>
       </c>
       <c r="R22" t="n">
-        <v>6692814</v>
+        <v>6692608</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2922,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131860702</v>
+        <v>131860635</v>
       </c>
       <c r="B23" t="n">
-        <v>101243</v>
+        <v>80331</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2933,21 +2918,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>229497</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2957,10 +2942,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>669289</v>
+        <v>669236</v>
       </c>
       <c r="R23" t="n">
-        <v>6692778</v>
+        <v>6692814</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3003,6 +2988,21 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3019,32 +3019,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131860589</v>
+        <v>131860702</v>
       </c>
       <c r="B24" t="n">
-        <v>91832</v>
+        <v>101249</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>669210</v>
+        <v>669289</v>
       </c>
       <c r="R24" t="n">
-        <v>6692779</v>
+        <v>6692778</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3116,10 +3116,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131860692</v>
+        <v>131860617</v>
       </c>
       <c r="B25" t="n">
-        <v>101243</v>
+        <v>80275</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3127,21 +3127,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>6456</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>669245</v>
+        <v>669355</v>
       </c>
       <c r="R25" t="n">
-        <v>6692828</v>
+        <v>6692827</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3197,6 +3197,21 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3213,10 +3228,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131860617</v>
+        <v>131860692</v>
       </c>
       <c r="B26" t="n">
-        <v>80273</v>
+        <v>101249</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3224,21 +3239,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6456</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3248,10 +3263,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>669355</v>
+        <v>669245</v>
       </c>
       <c r="R26" t="n">
-        <v>6692827</v>
+        <v>6692828</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3294,21 +3309,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3325,10 +3325,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131860696</v>
+        <v>131860690</v>
       </c>
       <c r="B27" t="n">
-        <v>101243</v>
+        <v>92493</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3336,21 +3336,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>1339</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3360,10 +3360,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>669141</v>
+        <v>669205</v>
       </c>
       <c r="R27" t="n">
-        <v>6692607</v>
+        <v>6692610</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3406,6 +3406,21 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3422,45 +3437,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131860694</v>
+        <v>131860609</v>
       </c>
       <c r="B28" t="n">
-        <v>101243</v>
+        <v>57901</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>669321</v>
+        <v>669095</v>
       </c>
       <c r="R28" t="n">
-        <v>6692768</v>
+        <v>6692372</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3519,10 +3539,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131860690</v>
+        <v>131860696</v>
       </c>
       <c r="B29" t="n">
-        <v>92487</v>
+        <v>101249</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3530,21 +3550,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3554,10 +3574,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>669205</v>
+        <v>669141</v>
       </c>
       <c r="R29" t="n">
-        <v>6692610</v>
+        <v>6692607</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3600,21 +3620,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3631,50 +3636,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131860609</v>
+        <v>131860694</v>
       </c>
       <c r="B30" t="n">
-        <v>57899</v>
+        <v>101249</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>669095</v>
+        <v>669321</v>
       </c>
       <c r="R30" t="n">
-        <v>6692372</v>
+        <v>6692768</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3733,10 +3733,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131860689</v>
+        <v>131860687</v>
       </c>
       <c r="B31" t="n">
-        <v>92487</v>
+        <v>5178</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3744,21 +3744,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1339</v>
+        <v>100526</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>669316</v>
+        <v>669223</v>
       </c>
       <c r="R31" t="n">
-        <v>6692776</v>
+        <v>6692603</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3845,10 +3845,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131860615</v>
+        <v>131860689</v>
       </c>
       <c r="B32" t="n">
-        <v>80273</v>
+        <v>92493</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3856,21 +3856,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6456</v>
+        <v>1339</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3880,10 +3880,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>669217</v>
+        <v>669316</v>
       </c>
       <c r="R32" t="n">
-        <v>6692612</v>
+        <v>6692776</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3929,17 +3929,17 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -3957,32 +3957,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131860662</v>
+        <v>131860613</v>
       </c>
       <c r="B33" t="n">
-        <v>79264</v>
+        <v>80275</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3992,10 +3992,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>669203</v>
+        <v>669232</v>
       </c>
       <c r="R33" t="n">
-        <v>6692759</v>
+        <v>6692800</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4041,17 +4041,17 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4069,10 +4069,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131860613</v>
+        <v>131860615</v>
       </c>
       <c r="B34" t="n">
-        <v>80273</v>
+        <v>80275</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>669232</v>
+        <v>669217</v>
       </c>
       <c r="R34" t="n">
-        <v>6692800</v>
+        <v>6692612</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4181,10 +4181,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131860661</v>
+        <v>131860662</v>
       </c>
       <c r="B35" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4216,10 +4216,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>669202</v>
+        <v>669203</v>
       </c>
       <c r="R35" t="n">
-        <v>6692764</v>
+        <v>6692759</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4293,32 +4293,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131860687</v>
+        <v>131860661</v>
       </c>
       <c r="B36" t="n">
-        <v>5178</v>
+        <v>79266</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4328,10 +4328,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>669223</v>
+        <v>669202</v>
       </c>
       <c r="R36" t="n">
-        <v>6692603</v>
+        <v>6692764</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4408,7 +4408,7 @@
         <v>131860698</v>
       </c>
       <c r="B37" t="n">
-        <v>101243</v>
+        <v>101249</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>131860593</v>
       </c>
       <c r="B38" t="n">
-        <v>91832</v>
+        <v>91838</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>131860607</v>
       </c>
       <c r="B39" t="n">
-        <v>96378</v>
+        <v>96384</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4696,10 +4696,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131860655</v>
+        <v>131860700</v>
       </c>
       <c r="B40" t="n">
-        <v>4780</v>
+        <v>101249</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4707,21 +4707,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4731,10 +4731,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>669222</v>
+        <v>668963</v>
       </c>
       <c r="R40" t="n">
-        <v>6692642</v>
+        <v>6692271</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4777,21 +4777,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4808,10 +4793,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131860654</v>
+        <v>131860699</v>
       </c>
       <c r="B41" t="n">
-        <v>4780</v>
+        <v>101249</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4819,21 +4804,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4843,10 +4828,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>669197</v>
+        <v>668997</v>
       </c>
       <c r="R41" t="n">
-        <v>6692720</v>
+        <v>6692214</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4889,21 +4874,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -4920,10 +4890,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131860700</v>
+        <v>131860655</v>
       </c>
       <c r="B42" t="n">
-        <v>101243</v>
+        <v>4780</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4931,21 +4901,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4955,10 +4925,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>668963</v>
+        <v>669222</v>
       </c>
       <c r="R42" t="n">
-        <v>6692271</v>
+        <v>6692642</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5001,6 +4971,21 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5017,10 +5002,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131860699</v>
+        <v>131860654</v>
       </c>
       <c r="B43" t="n">
-        <v>101243</v>
+        <v>4780</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5028,21 +5013,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5052,10 +5037,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>668997</v>
+        <v>669197</v>
       </c>
       <c r="R43" t="n">
-        <v>6692214</v>
+        <v>6692720</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5098,6 +5083,21 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5114,10 +5114,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131860648</v>
+        <v>131860642</v>
       </c>
       <c r="B44" t="n">
-        <v>75370</v>
+        <v>80331</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5125,21 +5125,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6426</v>
+        <v>229497</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5149,10 +5149,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>669219</v>
+        <v>669212</v>
       </c>
       <c r="R44" t="n">
-        <v>6692641</v>
+        <v>6692609</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5195,6 +5195,21 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5211,10 +5226,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131860620</v>
+        <v>131860639</v>
       </c>
       <c r="B45" t="n">
-        <v>80273</v>
+        <v>80331</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5222,21 +5237,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5246,10 +5261,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>669176</v>
+        <v>669215</v>
       </c>
       <c r="R45" t="n">
-        <v>6692603</v>
+        <v>6692608</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5323,10 +5338,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131860642</v>
+        <v>131860652</v>
       </c>
       <c r="B46" t="n">
-        <v>80329</v>
+        <v>96480</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5334,21 +5349,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229497</v>
+        <v>210</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5358,10 +5373,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>669212</v>
+        <v>668992</v>
       </c>
       <c r="R46" t="n">
-        <v>6692609</v>
+        <v>6692504</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5407,17 +5422,17 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5435,10 +5450,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131860639</v>
+        <v>131860620</v>
       </c>
       <c r="B47" t="n">
-        <v>80329</v>
+        <v>80275</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5446,21 +5461,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5470,10 +5485,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>669215</v>
+        <v>669176</v>
       </c>
       <c r="R47" t="n">
-        <v>6692608</v>
+        <v>6692603</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5547,10 +5562,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131860652</v>
+        <v>131860648</v>
       </c>
       <c r="B48" t="n">
-        <v>96474</v>
+        <v>75372</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5558,21 +5573,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>210</v>
+        <v>6426</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5582,10 +5597,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>668992</v>
+        <v>669219</v>
       </c>
       <c r="R48" t="n">
-        <v>6692504</v>
+        <v>6692641</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5628,21 +5643,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5659,10 +5659,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131860634</v>
+        <v>131860685</v>
       </c>
       <c r="B49" t="n">
-        <v>80329</v>
+        <v>80306</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5670,21 +5670,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229497</v>
+        <v>6457</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>669233</v>
+        <v>669242</v>
       </c>
       <c r="R49" t="n">
-        <v>6692806</v>
+        <v>6692625</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5771,10 +5771,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131860685</v>
+        <v>131860634</v>
       </c>
       <c r="B50" t="n">
-        <v>80304</v>
+        <v>80331</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5782,21 +5782,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6457</v>
+        <v>229497</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5806,10 +5806,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>669242</v>
+        <v>669233</v>
       </c>
       <c r="R50" t="n">
-        <v>6692625</v>
+        <v>6692806</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5883,10 +5883,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131860683</v>
+        <v>131860691</v>
       </c>
       <c r="B51" t="n">
-        <v>80304</v>
+        <v>92493</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5894,21 +5894,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6457</v>
+        <v>1339</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5918,10 +5918,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>669167</v>
+        <v>669198</v>
       </c>
       <c r="R51" t="n">
-        <v>6692763</v>
+        <v>6692600</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5967,17 +5967,17 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -5995,10 +5995,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131860691</v>
+        <v>131860683</v>
       </c>
       <c r="B52" t="n">
-        <v>92487</v>
+        <v>80306</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6006,21 +6006,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1339</v>
+        <v>6457</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6030,10 +6030,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>669198</v>
+        <v>669167</v>
       </c>
       <c r="R52" t="n">
-        <v>6692600</v>
+        <v>6692763</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6079,17 +6079,17 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6107,10 +6107,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131860641</v>
+        <v>131860651</v>
       </c>
       <c r="B53" t="n">
-        <v>80329</v>
+        <v>96480</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6118,21 +6118,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229497</v>
+        <v>210</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6142,10 +6142,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>669218</v>
+        <v>669305</v>
       </c>
       <c r="R53" t="n">
-        <v>6692611</v>
+        <v>6692798</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6191,17 +6191,17 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6219,10 +6219,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131860643</v>
+        <v>131860641</v>
       </c>
       <c r="B54" t="n">
-        <v>80329</v>
+        <v>80331</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6254,10 +6254,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>669201</v>
+        <v>669218</v>
       </c>
       <c r="R54" t="n">
-        <v>6692608</v>
+        <v>6692611</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6331,10 +6331,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131860651</v>
+        <v>131860643</v>
       </c>
       <c r="B55" t="n">
-        <v>96474</v>
+        <v>80331</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6342,21 +6342,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>210</v>
+        <v>229497</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6366,10 +6366,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>669305</v>
+        <v>669201</v>
       </c>
       <c r="R55" t="n">
-        <v>6692798</v>
+        <v>6692608</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6415,17 +6415,17 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6446,7 +6446,7 @@
         <v>131860701</v>
       </c>
       <c r="B56" t="n">
-        <v>101243</v>
+        <v>101249</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131860605</v>
+        <v>131860622</v>
       </c>
       <c r="B2" t="n">
-        <v>96384</v>
+        <v>92298</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2818</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>668988</v>
+        <v>669211</v>
       </c>
       <c r="R2" t="n">
-        <v>6692259</v>
+        <v>6692779</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -756,6 +756,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -772,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131860622</v>
+        <v>131860688</v>
       </c>
       <c r="B3" t="n">
-        <v>92298</v>
+        <v>92493</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>1339</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>669211</v>
+        <v>669177</v>
       </c>
       <c r="R3" t="n">
-        <v>6692779</v>
+        <v>6692736</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -884,32 +899,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131860688</v>
+        <v>131860591</v>
       </c>
       <c r="B4" t="n">
-        <v>92493</v>
+        <v>91838</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>669177</v>
+        <v>669198</v>
       </c>
       <c r="R4" t="n">
-        <v>6692736</v>
+        <v>6692769</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -965,21 +980,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -996,32 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131860591</v>
+        <v>131860605</v>
       </c>
       <c r="B5" t="n">
-        <v>91838</v>
+        <v>96384</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>2818</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>669198</v>
+        <v>668988</v>
       </c>
       <c r="R5" t="n">
-        <v>6692769</v>
+        <v>6692259</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1093,32 +1093,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131860608</v>
+        <v>131860653</v>
       </c>
       <c r="B6" t="n">
-        <v>57901</v>
+        <v>4780</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>669103</v>
+        <v>669179</v>
       </c>
       <c r="R6" t="n">
-        <v>6692390</v>
+        <v>6692717</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1166,11 +1166,6 @@
           <t>2026-03-22</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Flög in i skogen och satte sig ett träd.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1179,6 +1174,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1195,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131860653</v>
+        <v>131860608</v>
       </c>
       <c r="B7" t="n">
-        <v>4780</v>
+        <v>57901</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>669179</v>
+        <v>669103</v>
       </c>
       <c r="R7" t="n">
-        <v>6692717</v>
+        <v>6692390</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1268,6 +1278,11 @@
           <t>2026-03-22</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Flög in i skogen och satte sig ett träd.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1276,21 +1291,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131860656</v>
+        <v>131860695</v>
       </c>
       <c r="B8" t="n">
-        <v>4780</v>
+        <v>101249</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>669149</v>
+        <v>669270</v>
       </c>
       <c r="R8" t="n">
-        <v>6692521</v>
+        <v>6692768</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,21 +1389,6 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
@@ -1412,17 +1397,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
+          <t>Åsa Nordling, Ingemar Södergren, Tove Widén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131860695</v>
+        <v>131860656</v>
       </c>
       <c r="B9" t="n">
-        <v>101249</v>
+        <v>4780</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1430,21 +1415,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>669270</v>
+        <v>669149</v>
       </c>
       <c r="R9" t="n">
-        <v>6692768</v>
+        <v>6692521</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1501,6 +1486,21 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
@@ -1509,17 +1509,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Åsa Nordling, Ingemar Södergren, Tove Widén</t>
+          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131860684</v>
+        <v>131860649</v>
       </c>
       <c r="B10" t="n">
-        <v>80306</v>
+        <v>96480</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1527,21 +1527,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6457</v>
+        <v>210</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>669173</v>
+        <v>669159</v>
       </c>
       <c r="R10" t="n">
-        <v>6692783</v>
+        <v>6692588</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1597,21 +1597,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1628,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131860637</v>
+        <v>131860684</v>
       </c>
       <c r="B11" t="n">
-        <v>80331</v>
+        <v>80306</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1639,21 +1624,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229497</v>
+        <v>6457</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>669335</v>
+        <v>669173</v>
       </c>
       <c r="R11" t="n">
-        <v>6692778</v>
+        <v>6692783</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1740,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131860649</v>
+        <v>131860637</v>
       </c>
       <c r="B12" t="n">
-        <v>96480</v>
+        <v>80331</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,21 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>210</v>
+        <v>229497</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>669159</v>
+        <v>669335</v>
       </c>
       <c r="R12" t="n">
-        <v>6692588</v>
+        <v>6692778</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1821,6 +1806,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2158,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131860603</v>
+        <v>131860616</v>
       </c>
       <c r="B16" t="n">
-        <v>96384</v>
+        <v>80275</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2169,21 +2169,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2818</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>669306</v>
+        <v>669151</v>
       </c>
       <c r="R16" t="n">
-        <v>6692797</v>
+        <v>6692600</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2231,6 +2231,11 @@
           <t>2026-03-22</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2242,17 +2247,17 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2270,7 +2275,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131860604</v>
+        <v>131860603</v>
       </c>
       <c r="B17" t="n">
         <v>96384</v>
@@ -2299,20 +2304,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>669204</v>
+        <v>669306</v>
       </c>
       <c r="R17" t="n">
-        <v>6692601</v>
+        <v>6692797</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2353,23 +2354,22 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2387,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131860616</v>
+        <v>131860604</v>
       </c>
       <c r="B18" t="n">
-        <v>80275</v>
+        <v>96384</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2398,34 +2398,38 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6456</v>
+        <v>2818</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>669151</v>
+        <v>669204</v>
       </c>
       <c r="R18" t="n">
-        <v>6692600</v>
+        <v>6692601</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2460,33 +2464,29 @@
           <t>2026-03-22</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3437,50 +3437,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131860609</v>
+        <v>131860696</v>
       </c>
       <c r="B28" t="n">
-        <v>57901</v>
+        <v>101249</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>669095</v>
+        <v>669141</v>
       </c>
       <c r="R28" t="n">
-        <v>6692372</v>
+        <v>6692607</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3539,7 +3534,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131860696</v>
+        <v>131860694</v>
       </c>
       <c r="B29" t="n">
         <v>101249</v>
@@ -3574,10 +3569,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>669141</v>
+        <v>669321</v>
       </c>
       <c r="R29" t="n">
-        <v>6692607</v>
+        <v>6692768</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3636,45 +3631,50 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131860694</v>
+        <v>131860609</v>
       </c>
       <c r="B30" t="n">
-        <v>101249</v>
+        <v>57901</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>669321</v>
+        <v>669095</v>
       </c>
       <c r="R30" t="n">
-        <v>6692768</v>
+        <v>6692372</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -5114,10 +5114,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131860642</v>
+        <v>131860652</v>
       </c>
       <c r="B44" t="n">
-        <v>80331</v>
+        <v>96480</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5125,21 +5125,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229497</v>
+        <v>210</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5149,10 +5149,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>669212</v>
+        <v>668992</v>
       </c>
       <c r="R44" t="n">
-        <v>6692609</v>
+        <v>6692504</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5198,17 +5198,17 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5226,10 +5226,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131860639</v>
+        <v>131860620</v>
       </c>
       <c r="B45" t="n">
-        <v>80331</v>
+        <v>80275</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5237,21 +5237,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>669215</v>
+        <v>669176</v>
       </c>
       <c r="R45" t="n">
-        <v>6692608</v>
+        <v>6692603</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5338,10 +5338,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131860652</v>
+        <v>131860648</v>
       </c>
       <c r="B46" t="n">
-        <v>96480</v>
+        <v>75372</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5349,21 +5349,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>210</v>
+        <v>6426</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>668992</v>
+        <v>669219</v>
       </c>
       <c r="R46" t="n">
-        <v>6692504</v>
+        <v>6692641</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5419,21 +5419,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5450,10 +5435,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131860620</v>
+        <v>131860642</v>
       </c>
       <c r="B47" t="n">
-        <v>80275</v>
+        <v>80331</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5461,21 +5446,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5485,10 +5470,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>669176</v>
+        <v>669212</v>
       </c>
       <c r="R47" t="n">
-        <v>6692603</v>
+        <v>6692609</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5562,10 +5547,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131860648</v>
+        <v>131860639</v>
       </c>
       <c r="B48" t="n">
-        <v>75372</v>
+        <v>80331</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5573,21 +5558,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6426</v>
+        <v>229497</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5597,10 +5582,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>669219</v>
+        <v>669215</v>
       </c>
       <c r="R48" t="n">
-        <v>6692641</v>
+        <v>6692608</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5643,6 +5628,21 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5883,10 +5883,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131860691</v>
+        <v>131860683</v>
       </c>
       <c r="B51" t="n">
-        <v>92493</v>
+        <v>80306</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5894,21 +5894,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1339</v>
+        <v>6457</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5918,10 +5918,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>669198</v>
+        <v>669167</v>
       </c>
       <c r="R51" t="n">
-        <v>6692600</v>
+        <v>6692763</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5967,17 +5967,17 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -5995,10 +5995,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131860683</v>
+        <v>131860691</v>
       </c>
       <c r="B52" t="n">
-        <v>80306</v>
+        <v>92493</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6006,21 +6006,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6457</v>
+        <v>1339</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6030,10 +6030,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>669167</v>
+        <v>669198</v>
       </c>
       <c r="R52" t="n">
-        <v>6692763</v>
+        <v>6692600</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6079,17 +6079,17 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -1516,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131860649</v>
+        <v>131860684</v>
       </c>
       <c r="B10" t="n">
-        <v>96480</v>
+        <v>80306</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1527,21 +1527,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>210</v>
+        <v>6457</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>669159</v>
+        <v>669173</v>
       </c>
       <c r="R10" t="n">
-        <v>6692588</v>
+        <v>6692783</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1597,6 +1597,21 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1613,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131860684</v>
+        <v>131860637</v>
       </c>
       <c r="B11" t="n">
-        <v>80306</v>
+        <v>80331</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1624,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6457</v>
+        <v>229497</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>669173</v>
+        <v>669335</v>
       </c>
       <c r="R11" t="n">
-        <v>6692783</v>
+        <v>6692778</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1725,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131860637</v>
+        <v>131860649</v>
       </c>
       <c r="B12" t="n">
-        <v>80331</v>
+        <v>96480</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1736,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229497</v>
+        <v>210</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>669335</v>
+        <v>669159</v>
       </c>
       <c r="R12" t="n">
-        <v>6692778</v>
+        <v>6692588</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1806,21 +1821,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1949,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131860697</v>
+        <v>131860614</v>
       </c>
       <c r="B14" t="n">
-        <v>101249</v>
+        <v>80275</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1960,21 +1960,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>669157</v>
+        <v>669229</v>
       </c>
       <c r="R14" t="n">
-        <v>6692556</v>
+        <v>6692600</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2030,6 +2030,21 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2046,10 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131860614</v>
+        <v>131860697</v>
       </c>
       <c r="B15" t="n">
-        <v>80275</v>
+        <v>101249</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2057,21 +2072,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2081,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>669229</v>
+        <v>669157</v>
       </c>
       <c r="R15" t="n">
-        <v>6692600</v>
+        <v>6692556</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2127,21 +2142,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2158,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131860616</v>
+        <v>131860603</v>
       </c>
       <c r="B16" t="n">
-        <v>80275</v>
+        <v>96384</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2169,21 +2169,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6456</v>
+        <v>2818</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>669151</v>
+        <v>669306</v>
       </c>
       <c r="R16" t="n">
-        <v>6692600</v>
+        <v>6692797</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2231,11 +2231,6 @@
           <t>2026-03-22</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2247,17 +2242,17 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2275,7 +2270,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131860603</v>
+        <v>131860604</v>
       </c>
       <c r="B17" t="n">
         <v>96384</v>
@@ -2304,16 +2299,20 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>669306</v>
+        <v>669204</v>
       </c>
       <c r="R17" t="n">
-        <v>6692797</v>
+        <v>6692601</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2354,22 +2353,23 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2387,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131860604</v>
+        <v>131860616</v>
       </c>
       <c r="B18" t="n">
-        <v>96384</v>
+        <v>80275</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2398,38 +2398,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2818</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>669204</v>
+        <v>669151</v>
       </c>
       <c r="R18" t="n">
-        <v>6692601</v>
+        <v>6692600</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2464,29 +2460,33 @@
           <t>2026-03-22</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2601,32 +2601,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131860589</v>
+        <v>131860635</v>
       </c>
       <c r="B20" t="n">
-        <v>91838</v>
+        <v>80331</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>669210</v>
+        <v>669236</v>
       </c>
       <c r="R20" t="n">
-        <v>6692779</v>
+        <v>6692814</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2682,6 +2682,21 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2698,32 +2713,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131860588</v>
+        <v>131860702</v>
       </c>
       <c r="B21" t="n">
-        <v>91838</v>
+        <v>101249</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2733,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>669143</v>
+        <v>669289</v>
       </c>
       <c r="R21" t="n">
-        <v>6692724</v>
+        <v>6692778</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2795,32 +2810,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131860618</v>
+        <v>131860589</v>
       </c>
       <c r="B22" t="n">
-        <v>80275</v>
+        <v>91838</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2830,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>669202</v>
+        <v>669210</v>
       </c>
       <c r="R22" t="n">
-        <v>6692608</v>
+        <v>6692779</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2876,21 +2891,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2907,32 +2907,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131860635</v>
+        <v>131860588</v>
       </c>
       <c r="B23" t="n">
-        <v>80331</v>
+        <v>91838</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>669236</v>
+        <v>669143</v>
       </c>
       <c r="R23" t="n">
-        <v>6692814</v>
+        <v>6692724</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2988,21 +2988,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3019,10 +3004,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131860702</v>
+        <v>131860618</v>
       </c>
       <c r="B24" t="n">
-        <v>101249</v>
+        <v>80275</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3030,21 +3015,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>6456</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3054,10 +3039,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>669289</v>
+        <v>669202</v>
       </c>
       <c r="R24" t="n">
-        <v>6692778</v>
+        <v>6692608</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3100,6 +3085,21 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3437,45 +3437,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131860696</v>
+        <v>131860609</v>
       </c>
       <c r="B28" t="n">
-        <v>101249</v>
+        <v>57901</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>669141</v>
+        <v>669095</v>
       </c>
       <c r="R28" t="n">
-        <v>6692607</v>
+        <v>6692372</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3534,7 +3539,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131860694</v>
+        <v>131860696</v>
       </c>
       <c r="B29" t="n">
         <v>101249</v>
@@ -3569,10 +3574,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>669321</v>
+        <v>669141</v>
       </c>
       <c r="R29" t="n">
-        <v>6692768</v>
+        <v>6692607</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3631,50 +3636,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131860609</v>
+        <v>131860694</v>
       </c>
       <c r="B30" t="n">
-        <v>57901</v>
+        <v>101249</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>669095</v>
+        <v>669321</v>
       </c>
       <c r="R30" t="n">
-        <v>6692372</v>
+        <v>6692768</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -5883,10 +5883,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131860683</v>
+        <v>131860691</v>
       </c>
       <c r="B51" t="n">
-        <v>80306</v>
+        <v>92493</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5894,21 +5894,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6457</v>
+        <v>1339</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5918,10 +5918,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>669167</v>
+        <v>669198</v>
       </c>
       <c r="R51" t="n">
-        <v>6692763</v>
+        <v>6692600</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5967,17 +5967,17 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -5995,10 +5995,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131860691</v>
+        <v>131860683</v>
       </c>
       <c r="B52" t="n">
-        <v>92493</v>
+        <v>80306</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6006,21 +6006,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1339</v>
+        <v>6457</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6030,10 +6030,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>669198</v>
+        <v>669167</v>
       </c>
       <c r="R52" t="n">
-        <v>6692600</v>
+        <v>6692763</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6079,17 +6079,17 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131860695</v>
+        <v>131860656</v>
       </c>
       <c r="B8" t="n">
-        <v>101249</v>
+        <v>4780</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>669270</v>
+        <v>669149</v>
       </c>
       <c r="R8" t="n">
-        <v>6692768</v>
+        <v>6692521</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,6 +1389,21 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
@@ -1397,17 +1412,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Åsa Nordling, Ingemar Södergren, Tove Widén</t>
+          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131860656</v>
+        <v>131860695</v>
       </c>
       <c r="B9" t="n">
-        <v>4780</v>
+        <v>101249</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1415,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>669149</v>
+        <v>669270</v>
       </c>
       <c r="R9" t="n">
-        <v>6692521</v>
+        <v>6692768</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1486,21 +1501,6 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
+          <t>Åsa Nordling, Ingemar Södergren, Tove Widén</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -2601,32 +2601,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131860635</v>
+        <v>131860589</v>
       </c>
       <c r="B20" t="n">
-        <v>80331</v>
+        <v>91838</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>669236</v>
+        <v>669210</v>
       </c>
       <c r="R20" t="n">
-        <v>6692814</v>
+        <v>6692779</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2682,21 +2682,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2713,32 +2698,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131860702</v>
+        <v>131860588</v>
       </c>
       <c r="B21" t="n">
-        <v>101249</v>
+        <v>91838</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2748,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>669289</v>
+        <v>669143</v>
       </c>
       <c r="R21" t="n">
-        <v>6692778</v>
+        <v>6692724</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2810,32 +2795,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131860589</v>
+        <v>131860618</v>
       </c>
       <c r="B22" t="n">
-        <v>91838</v>
+        <v>80275</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2845,10 +2830,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>669210</v>
+        <v>669202</v>
       </c>
       <c r="R22" t="n">
-        <v>6692779</v>
+        <v>6692608</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2891,6 +2876,21 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2907,32 +2907,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131860588</v>
+        <v>131860635</v>
       </c>
       <c r="B23" t="n">
-        <v>91838</v>
+        <v>80331</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>669143</v>
+        <v>669236</v>
       </c>
       <c r="R23" t="n">
-        <v>6692724</v>
+        <v>6692814</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2988,6 +2988,21 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3004,10 +3019,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131860618</v>
+        <v>131860702</v>
       </c>
       <c r="B24" t="n">
-        <v>80275</v>
+        <v>101249</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3015,21 +3030,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6456</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3039,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>669202</v>
+        <v>669289</v>
       </c>
       <c r="R24" t="n">
-        <v>6692608</v>
+        <v>6692778</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3085,21 +3100,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3116,10 +3116,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131860617</v>
+        <v>131860692</v>
       </c>
       <c r="B25" t="n">
-        <v>80275</v>
+        <v>101249</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3127,21 +3127,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6456</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>669355</v>
+        <v>669245</v>
       </c>
       <c r="R25" t="n">
-        <v>6692827</v>
+        <v>6692828</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3197,21 +3197,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3228,10 +3213,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131860692</v>
+        <v>131860617</v>
       </c>
       <c r="B26" t="n">
-        <v>101249</v>
+        <v>80275</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3239,21 +3224,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>6456</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3263,10 +3248,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>669245</v>
+        <v>669355</v>
       </c>
       <c r="R26" t="n">
-        <v>6692828</v>
+        <v>6692827</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3309,6 +3294,21 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3437,50 +3437,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131860609</v>
+        <v>131860696</v>
       </c>
       <c r="B28" t="n">
-        <v>57901</v>
+        <v>101249</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>669095</v>
+        <v>669141</v>
       </c>
       <c r="R28" t="n">
-        <v>6692372</v>
+        <v>6692607</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3539,7 +3534,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131860696</v>
+        <v>131860694</v>
       </c>
       <c r="B29" t="n">
         <v>101249</v>
@@ -3574,10 +3569,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>669141</v>
+        <v>669321</v>
       </c>
       <c r="R29" t="n">
-        <v>6692607</v>
+        <v>6692768</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3636,45 +3631,50 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131860694</v>
+        <v>131860609</v>
       </c>
       <c r="B30" t="n">
-        <v>101249</v>
+        <v>57901</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>669321</v>
+        <v>669095</v>
       </c>
       <c r="R30" t="n">
-        <v>6692768</v>
+        <v>6692372</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3733,10 +3733,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131860687</v>
+        <v>131860689</v>
       </c>
       <c r="B31" t="n">
-        <v>5178</v>
+        <v>92493</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3744,21 +3744,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100526</v>
+        <v>1339</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>669223</v>
+        <v>669316</v>
       </c>
       <c r="R31" t="n">
-        <v>6692603</v>
+        <v>6692776</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3845,10 +3845,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131860689</v>
+        <v>131860613</v>
       </c>
       <c r="B32" t="n">
-        <v>92493</v>
+        <v>80275</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3856,21 +3856,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1339</v>
+        <v>6456</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3880,10 +3880,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>669316</v>
+        <v>669232</v>
       </c>
       <c r="R32" t="n">
-        <v>6692776</v>
+        <v>6692800</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3929,17 +3929,17 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -3957,7 +3957,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131860613</v>
+        <v>131860615</v>
       </c>
       <c r="B33" t="n">
         <v>80275</v>
@@ -3992,10 +3992,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>669232</v>
+        <v>669217</v>
       </c>
       <c r="R33" t="n">
-        <v>6692800</v>
+        <v>6692612</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4069,10 +4069,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131860615</v>
+        <v>131860687</v>
       </c>
       <c r="B34" t="n">
-        <v>80275</v>
+        <v>5178</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4080,21 +4080,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6456</v>
+        <v>100526</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>669217</v>
+        <v>669223</v>
       </c>
       <c r="R34" t="n">
-        <v>6692612</v>
+        <v>6692603</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4153,17 +4153,17 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY56"/>
+  <dimension ref="A1:AY81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1516,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131860684</v>
+        <v>131860649</v>
       </c>
       <c r="B10" t="n">
-        <v>80306</v>
+        <v>96480</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1527,21 +1527,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6457</v>
+        <v>210</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>669173</v>
+        <v>669159</v>
       </c>
       <c r="R10" t="n">
-        <v>6692783</v>
+        <v>6692588</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1597,21 +1597,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1628,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131860637</v>
+        <v>131860684</v>
       </c>
       <c r="B11" t="n">
-        <v>80331</v>
+        <v>80306</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1639,21 +1624,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229497</v>
+        <v>6457</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>669335</v>
+        <v>669173</v>
       </c>
       <c r="R11" t="n">
-        <v>6692778</v>
+        <v>6692783</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1740,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131860649</v>
+        <v>131860637</v>
       </c>
       <c r="B12" t="n">
-        <v>96480</v>
+        <v>80331</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,21 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>210</v>
+        <v>229497</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>669159</v>
+        <v>669335</v>
       </c>
       <c r="R12" t="n">
-        <v>6692588</v>
+        <v>6692778</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1821,6 +1806,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -3733,10 +3733,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131860689</v>
+        <v>131860687</v>
       </c>
       <c r="B31" t="n">
-        <v>92493</v>
+        <v>5178</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3744,21 +3744,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1339</v>
+        <v>100526</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>669316</v>
+        <v>669223</v>
       </c>
       <c r="R31" t="n">
-        <v>6692776</v>
+        <v>6692603</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3845,10 +3845,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131860613</v>
+        <v>131860689</v>
       </c>
       <c r="B32" t="n">
-        <v>80275</v>
+        <v>92493</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3856,21 +3856,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6456</v>
+        <v>1339</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3880,10 +3880,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>669232</v>
+        <v>669316</v>
       </c>
       <c r="R32" t="n">
-        <v>6692800</v>
+        <v>6692776</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3929,17 +3929,17 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -3957,7 +3957,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131860615</v>
+        <v>131860613</v>
       </c>
       <c r="B33" t="n">
         <v>80275</v>
@@ -3992,10 +3992,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>669217</v>
+        <v>669232</v>
       </c>
       <c r="R33" t="n">
-        <v>6692612</v>
+        <v>6692800</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4069,10 +4069,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131860687</v>
+        <v>131860615</v>
       </c>
       <c r="B34" t="n">
-        <v>5178</v>
+        <v>80275</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4080,21 +4080,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100526</v>
+        <v>6456</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>669223</v>
+        <v>669217</v>
       </c>
       <c r="R34" t="n">
-        <v>6692603</v>
+        <v>6692612</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4153,17 +4153,17 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5659,10 +5659,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131860685</v>
+        <v>131860634</v>
       </c>
       <c r="B49" t="n">
-        <v>80306</v>
+        <v>80331</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5670,21 +5670,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6457</v>
+        <v>229497</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>669242</v>
+        <v>669233</v>
       </c>
       <c r="R49" t="n">
-        <v>6692625</v>
+        <v>6692806</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5771,10 +5771,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131860634</v>
+        <v>131860685</v>
       </c>
       <c r="B50" t="n">
-        <v>80331</v>
+        <v>80306</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5782,21 +5782,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>229497</v>
+        <v>6457</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5806,10 +5806,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>669233</v>
+        <v>669242</v>
       </c>
       <c r="R50" t="n">
-        <v>6692806</v>
+        <v>6692625</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6538,6 +6538,2576 @@
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>132019922</v>
+      </c>
+      <c r="B57" t="n">
+        <v>101251</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Östensbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>669218</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6692730</v>
+      </c>
+      <c r="S57" t="n">
+        <v>15</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>132019904</v>
+      </c>
+      <c r="B58" t="n">
+        <v>91261</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>4189</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Kamjordstjärna</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Geastrum pectinatum</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Pers., nom.sanct</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Östensbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>669298</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6692803</v>
+      </c>
+      <c r="S58" t="n">
+        <v>15</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Kalkrik granskog, under gran</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>132019892</v>
+      </c>
+      <c r="B59" t="n">
+        <v>58065</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Östensbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>669331</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6692814</v>
+      </c>
+      <c r="S59" t="n">
+        <v>15</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>132019907</v>
+      </c>
+      <c r="B60" t="n">
+        <v>4780</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Östensbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>669141</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6692648</v>
+      </c>
+      <c r="S60" t="n">
+        <v>15</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>132019900</v>
+      </c>
+      <c r="B61" t="n">
+        <v>58278</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Östensbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>669289</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6692788</v>
+      </c>
+      <c r="S61" t="n">
+        <v>15</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>132019905</v>
+      </c>
+      <c r="B62" t="n">
+        <v>96482</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>210</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Östensbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>669143</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6692788</v>
+      </c>
+      <c r="S62" t="n">
+        <v>15</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>132019895</v>
+      </c>
+      <c r="B63" t="n">
+        <v>58065</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Östensbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>669191</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6692693</v>
+      </c>
+      <c r="S63" t="n">
+        <v>15</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>132019919</v>
+      </c>
+      <c r="B64" t="n">
+        <v>80308</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6457</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Dvärgtufs</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Scytinium teretiusculum</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Östensbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>669113</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6692721</v>
+      </c>
+      <c r="S64" t="n">
+        <v>15</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>Populas tremula</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>132019920</v>
+      </c>
+      <c r="B65" t="n">
+        <v>101251</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Östensbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>669116</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6692739</v>
+      </c>
+      <c r="S65" t="n">
+        <v>15</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>132019897</v>
+      </c>
+      <c r="B66" t="n">
+        <v>80277</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Östensbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>669126</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6692721</v>
+      </c>
+      <c r="S66" t="n">
+        <v>15</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>Populas tremula</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>132019889</v>
+      </c>
+      <c r="B67" t="n">
+        <v>91840</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Östensbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>669241</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6692784</v>
+      </c>
+      <c r="S67" t="n">
+        <v>15</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>132019903</v>
+      </c>
+      <c r="B68" t="n">
+        <v>75374</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Östensbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>669148</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6692645</v>
+      </c>
+      <c r="S68" t="n">
+        <v>15</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>132019898</v>
+      </c>
+      <c r="B69" t="n">
+        <v>80277</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Östensbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>669154</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6692684</v>
+      </c>
+      <c r="S69" t="n">
+        <v>15</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>Populas tremula</t>
+        </is>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>132019888</v>
+      </c>
+      <c r="B70" t="n">
+        <v>91840</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Östensbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>669198</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6692759</v>
+      </c>
+      <c r="S70" t="n">
+        <v>15</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>132019901</v>
+      </c>
+      <c r="B71" t="n">
+        <v>75374</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Östensbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>669196</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6692684</v>
+      </c>
+      <c r="S71" t="n">
+        <v>15</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>132019918</v>
+      </c>
+      <c r="B72" t="n">
+        <v>80308</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6457</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Dvärgtufs</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Scytinium teretiusculum</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Östensbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>669103</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6692699</v>
+      </c>
+      <c r="S72" t="n">
+        <v>15</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>Populas tremula</t>
+        </is>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>132019921</v>
+      </c>
+      <c r="B73" t="n">
+        <v>101251</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Östensbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>669204</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6692803</v>
+      </c>
+      <c r="S73" t="n">
+        <v>15</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>132019887</v>
+      </c>
+      <c r="B74" t="n">
+        <v>91840</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Östensbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>669285</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6692776</v>
+      </c>
+      <c r="S74" t="n">
+        <v>15</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>132019896</v>
+      </c>
+      <c r="B75" t="n">
+        <v>57903</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Östensbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>669209</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6692712</v>
+      </c>
+      <c r="S75" t="n">
+        <v>15</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>132019886</v>
+      </c>
+      <c r="B76" t="n">
+        <v>91840</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Östensbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>669131</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6692781</v>
+      </c>
+      <c r="S76" t="n">
+        <v>15</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>132019899</v>
+      </c>
+      <c r="B77" t="n">
+        <v>80277</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Östensbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>669151</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6692676</v>
+      </c>
+      <c r="S77" t="n">
+        <v>15</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>Populas tremula</t>
+        </is>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>132019906</v>
+      </c>
+      <c r="B78" t="n">
+        <v>4780</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Östensbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>669253</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6692762</v>
+      </c>
+      <c r="S78" t="n">
+        <v>15</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>132019908</v>
+      </c>
+      <c r="B79" t="n">
+        <v>79268</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Östensbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>669179</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6692672</v>
+      </c>
+      <c r="S79" t="n">
+        <v>15</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>132019894</v>
+      </c>
+      <c r="B80" t="n">
+        <v>58065</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Östensbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>669208</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6692665</v>
+      </c>
+      <c r="S80" t="n">
+        <v>15</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>132019893</v>
+      </c>
+      <c r="B81" t="n">
+        <v>58065</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Östensbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>669280</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6692724</v>
+      </c>
+      <c r="S81" t="n">
+        <v>15</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131860656</v>
+        <v>131860695</v>
       </c>
       <c r="B8" t="n">
-        <v>4780</v>
+        <v>101249</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>669149</v>
+        <v>669270</v>
       </c>
       <c r="R8" t="n">
-        <v>6692521</v>
+        <v>6692768</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,21 +1389,6 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
@@ -1412,17 +1397,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
+          <t>Åsa Nordling, Ingemar Södergren, Tove Widén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131860695</v>
+        <v>131860656</v>
       </c>
       <c r="B9" t="n">
-        <v>101249</v>
+        <v>4780</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1430,21 +1415,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>669270</v>
+        <v>669149</v>
       </c>
       <c r="R9" t="n">
-        <v>6692768</v>
+        <v>6692521</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1501,6 +1486,21 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
@@ -1509,17 +1509,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Åsa Nordling, Ingemar Södergren, Tove Widén</t>
+          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131860649</v>
+        <v>131860684</v>
       </c>
       <c r="B10" t="n">
-        <v>96480</v>
+        <v>80306</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1527,21 +1527,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>210</v>
+        <v>6457</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>669159</v>
+        <v>669173</v>
       </c>
       <c r="R10" t="n">
-        <v>6692588</v>
+        <v>6692783</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1597,6 +1597,21 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1613,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131860684</v>
+        <v>131860637</v>
       </c>
       <c r="B11" t="n">
-        <v>80306</v>
+        <v>80331</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1624,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6457</v>
+        <v>229497</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>669173</v>
+        <v>669335</v>
       </c>
       <c r="R11" t="n">
-        <v>6692783</v>
+        <v>6692778</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1725,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131860637</v>
+        <v>131860649</v>
       </c>
       <c r="B12" t="n">
-        <v>80331</v>
+        <v>96480</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1736,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229497</v>
+        <v>210</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>669335</v>
+        <v>669159</v>
       </c>
       <c r="R12" t="n">
-        <v>6692778</v>
+        <v>6692588</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1806,21 +1821,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2158,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131860603</v>
+        <v>131860616</v>
       </c>
       <c r="B16" t="n">
-        <v>96384</v>
+        <v>80275</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2169,21 +2169,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2818</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>669306</v>
+        <v>669151</v>
       </c>
       <c r="R16" t="n">
-        <v>6692797</v>
+        <v>6692600</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2231,6 +2231,11 @@
           <t>2026-03-22</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2242,17 +2247,17 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2270,7 +2275,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131860604</v>
+        <v>131860603</v>
       </c>
       <c r="B17" t="n">
         <v>96384</v>
@@ -2299,20 +2304,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>669204</v>
+        <v>669306</v>
       </c>
       <c r="R17" t="n">
-        <v>6692601</v>
+        <v>6692797</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2353,23 +2354,22 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2387,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131860616</v>
+        <v>131860604</v>
       </c>
       <c r="B18" t="n">
-        <v>80275</v>
+        <v>96384</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2398,34 +2398,38 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6456</v>
+        <v>2818</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>669151</v>
+        <v>669204</v>
       </c>
       <c r="R18" t="n">
-        <v>6692600</v>
+        <v>6692601</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2460,33 +2464,29 @@
           <t>2026-03-22</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -5114,10 +5114,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131860652</v>
+        <v>131860642</v>
       </c>
       <c r="B44" t="n">
-        <v>96480</v>
+        <v>80331</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5125,21 +5125,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>210</v>
+        <v>229497</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5149,10 +5149,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>668992</v>
+        <v>669212</v>
       </c>
       <c r="R44" t="n">
-        <v>6692504</v>
+        <v>6692609</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5198,17 +5198,17 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5226,10 +5226,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131860620</v>
+        <v>131860639</v>
       </c>
       <c r="B45" t="n">
-        <v>80275</v>
+        <v>80331</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5237,21 +5237,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>669176</v>
+        <v>669215</v>
       </c>
       <c r="R45" t="n">
-        <v>6692603</v>
+        <v>6692608</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5338,10 +5338,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131860648</v>
+        <v>131860652</v>
       </c>
       <c r="B46" t="n">
-        <v>75372</v>
+        <v>96480</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5349,21 +5349,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6426</v>
+        <v>210</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>669219</v>
+        <v>668992</v>
       </c>
       <c r="R46" t="n">
-        <v>6692641</v>
+        <v>6692504</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5419,6 +5419,21 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5435,10 +5450,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131860642</v>
+        <v>131860620</v>
       </c>
       <c r="B47" t="n">
-        <v>80331</v>
+        <v>80275</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5446,21 +5461,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5470,10 +5485,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>669212</v>
+        <v>669176</v>
       </c>
       <c r="R47" t="n">
-        <v>6692609</v>
+        <v>6692603</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5547,10 +5562,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131860639</v>
+        <v>131860648</v>
       </c>
       <c r="B48" t="n">
-        <v>80331</v>
+        <v>75372</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5558,21 +5573,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229497</v>
+        <v>6426</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5582,10 +5597,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>669215</v>
+        <v>669219</v>
       </c>
       <c r="R48" t="n">
-        <v>6692608</v>
+        <v>6692641</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5628,21 +5643,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5659,10 +5659,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131860634</v>
+        <v>131860685</v>
       </c>
       <c r="B49" t="n">
-        <v>80331</v>
+        <v>80306</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5670,21 +5670,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229497</v>
+        <v>6457</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>669233</v>
+        <v>669242</v>
       </c>
       <c r="R49" t="n">
-        <v>6692806</v>
+        <v>6692625</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5771,10 +5771,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131860685</v>
+        <v>131860634</v>
       </c>
       <c r="B50" t="n">
-        <v>80306</v>
+        <v>80331</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5782,21 +5782,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6457</v>
+        <v>229497</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5806,10 +5806,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>669242</v>
+        <v>669233</v>
       </c>
       <c r="R50" t="n">
-        <v>6692625</v>
+        <v>6692806</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -1949,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131860614</v>
+        <v>131860697</v>
       </c>
       <c r="B14" t="n">
-        <v>80275</v>
+        <v>101249</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1960,21 +1960,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>669229</v>
+        <v>669157</v>
       </c>
       <c r="R14" t="n">
-        <v>6692600</v>
+        <v>6692556</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2030,21 +2030,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2061,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131860697</v>
+        <v>131860614</v>
       </c>
       <c r="B15" t="n">
-        <v>101249</v>
+        <v>80275</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2072,21 +2057,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2096,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>669157</v>
+        <v>669229</v>
       </c>
       <c r="R15" t="n">
-        <v>6692556</v>
+        <v>6692600</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2142,6 +2127,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2158,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131860616</v>
+        <v>131860603</v>
       </c>
       <c r="B16" t="n">
-        <v>80275</v>
+        <v>96384</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2169,21 +2169,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6456</v>
+        <v>2818</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>669151</v>
+        <v>669306</v>
       </c>
       <c r="R16" t="n">
-        <v>6692600</v>
+        <v>6692797</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2231,11 +2231,6 @@
           <t>2026-03-22</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2247,17 +2242,17 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2275,7 +2270,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131860603</v>
+        <v>131860604</v>
       </c>
       <c r="B17" t="n">
         <v>96384</v>
@@ -2304,16 +2299,20 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>669306</v>
+        <v>669204</v>
       </c>
       <c r="R17" t="n">
-        <v>6692797</v>
+        <v>6692601</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2354,22 +2353,23 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2387,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131860604</v>
+        <v>131860616</v>
       </c>
       <c r="B18" t="n">
-        <v>96384</v>
+        <v>80275</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2398,38 +2398,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2818</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>669204</v>
+        <v>669151</v>
       </c>
       <c r="R18" t="n">
-        <v>6692601</v>
+        <v>6692600</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2464,29 +2460,33 @@
           <t>2026-03-22</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2601,32 +2601,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131860589</v>
+        <v>131860635</v>
       </c>
       <c r="B20" t="n">
-        <v>91838</v>
+        <v>80331</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>669210</v>
+        <v>669236</v>
       </c>
       <c r="R20" t="n">
-        <v>6692779</v>
+        <v>6692814</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2682,6 +2682,21 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2698,32 +2713,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131860588</v>
+        <v>131860702</v>
       </c>
       <c r="B21" t="n">
-        <v>91838</v>
+        <v>101249</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2733,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>669143</v>
+        <v>669289</v>
       </c>
       <c r="R21" t="n">
-        <v>6692724</v>
+        <v>6692778</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2795,32 +2810,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131860618</v>
+        <v>131860589</v>
       </c>
       <c r="B22" t="n">
-        <v>80275</v>
+        <v>91838</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2830,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>669202</v>
+        <v>669210</v>
       </c>
       <c r="R22" t="n">
-        <v>6692608</v>
+        <v>6692779</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2876,21 +2891,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2907,32 +2907,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131860635</v>
+        <v>131860588</v>
       </c>
       <c r="B23" t="n">
-        <v>80331</v>
+        <v>91838</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>669236</v>
+        <v>669143</v>
       </c>
       <c r="R23" t="n">
-        <v>6692814</v>
+        <v>6692724</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2988,21 +2988,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3019,10 +3004,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131860702</v>
+        <v>131860618</v>
       </c>
       <c r="B24" t="n">
-        <v>101249</v>
+        <v>80275</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3030,21 +3015,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>6456</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3054,10 +3039,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>669289</v>
+        <v>669202</v>
       </c>
       <c r="R24" t="n">
-        <v>6692778</v>
+        <v>6692608</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3100,6 +3085,21 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -5114,10 +5114,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131860642</v>
+        <v>131860652</v>
       </c>
       <c r="B44" t="n">
-        <v>80331</v>
+        <v>96480</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5125,21 +5125,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229497</v>
+        <v>210</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5149,10 +5149,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>669212</v>
+        <v>668992</v>
       </c>
       <c r="R44" t="n">
-        <v>6692609</v>
+        <v>6692504</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5198,17 +5198,17 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5226,10 +5226,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131860639</v>
+        <v>131860620</v>
       </c>
       <c r="B45" t="n">
-        <v>80331</v>
+        <v>80275</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5237,21 +5237,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>669215</v>
+        <v>669176</v>
       </c>
       <c r="R45" t="n">
-        <v>6692608</v>
+        <v>6692603</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5338,10 +5338,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131860652</v>
+        <v>131860648</v>
       </c>
       <c r="B46" t="n">
-        <v>96480</v>
+        <v>75372</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5349,21 +5349,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>210</v>
+        <v>6426</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>668992</v>
+        <v>669219</v>
       </c>
       <c r="R46" t="n">
-        <v>6692504</v>
+        <v>6692641</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5419,21 +5419,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5450,10 +5435,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131860620</v>
+        <v>131860642</v>
       </c>
       <c r="B47" t="n">
-        <v>80275</v>
+        <v>80331</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5461,21 +5446,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5485,10 +5470,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>669176</v>
+        <v>669212</v>
       </c>
       <c r="R47" t="n">
-        <v>6692603</v>
+        <v>6692609</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5562,10 +5547,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131860648</v>
+        <v>131860639</v>
       </c>
       <c r="B48" t="n">
-        <v>75372</v>
+        <v>80331</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5573,21 +5558,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6426</v>
+        <v>229497</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5597,10 +5582,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>669219</v>
+        <v>669215</v>
       </c>
       <c r="R48" t="n">
-        <v>6692641</v>
+        <v>6692608</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5643,6 +5628,21 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5883,10 +5883,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131860691</v>
+        <v>131860683</v>
       </c>
       <c r="B51" t="n">
-        <v>92493</v>
+        <v>80306</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5894,21 +5894,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1339</v>
+        <v>6457</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5918,10 +5918,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>669198</v>
+        <v>669167</v>
       </c>
       <c r="R51" t="n">
-        <v>6692600</v>
+        <v>6692763</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5967,17 +5967,17 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -5995,10 +5995,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131860683</v>
+        <v>131860691</v>
       </c>
       <c r="B52" t="n">
-        <v>80306</v>
+        <v>92493</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6006,21 +6006,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6457</v>
+        <v>1339</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6030,10 +6030,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>669167</v>
+        <v>669198</v>
       </c>
       <c r="R52" t="n">
-        <v>6692763</v>
+        <v>6692600</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6079,17 +6079,17 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131860622</v>
       </c>
       <c r="B2" t="n">
-        <v>92298</v>
+        <v>92301</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131860688</v>
+        <v>131860605</v>
       </c>
       <c r="B3" t="n">
-        <v>92493</v>
+        <v>96387</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1339</v>
+        <v>2818</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>669177</v>
+        <v>668988</v>
       </c>
       <c r="R3" t="n">
-        <v>6692736</v>
+        <v>6692259</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -868,21 +868,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -899,32 +884,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131860591</v>
+        <v>131860688</v>
       </c>
       <c r="B4" t="n">
-        <v>91838</v>
+        <v>92496</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>669198</v>
+        <v>669177</v>
       </c>
       <c r="R4" t="n">
-        <v>6692769</v>
+        <v>6692736</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -980,6 +965,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -996,32 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131860605</v>
+        <v>131860591</v>
       </c>
       <c r="B5" t="n">
-        <v>96384</v>
+        <v>91841</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2818</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668988</v>
+        <v>669198</v>
       </c>
       <c r="R5" t="n">
-        <v>6692259</v>
+        <v>6692769</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1096,7 +1096,7 @@
         <v>131860653</v>
       </c>
       <c r="B6" t="n">
-        <v>4780</v>
+        <v>4781</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>131860608</v>
       </c>
       <c r="B7" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131860695</v>
+        <v>131860656</v>
       </c>
       <c r="B8" t="n">
-        <v>101249</v>
+        <v>4781</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>669270</v>
+        <v>669149</v>
       </c>
       <c r="R8" t="n">
-        <v>6692768</v>
+        <v>6692521</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,6 +1389,21 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
@@ -1397,17 +1412,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Åsa Nordling, Ingemar Södergren, Tove Widén</t>
+          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131860656</v>
+        <v>131860695</v>
       </c>
       <c r="B9" t="n">
-        <v>4780</v>
+        <v>101252</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1415,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>669149</v>
+        <v>669270</v>
       </c>
       <c r="R9" t="n">
-        <v>6692521</v>
+        <v>6692768</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1485,21 +1500,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1516,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131860684</v>
+        <v>131860649</v>
       </c>
       <c r="B10" t="n">
-        <v>80306</v>
+        <v>96483</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1527,21 +1527,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6457</v>
+        <v>210</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>669173</v>
+        <v>669159</v>
       </c>
       <c r="R10" t="n">
-        <v>6692783</v>
+        <v>6692588</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1597,21 +1597,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1628,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131860637</v>
+        <v>131860684</v>
       </c>
       <c r="B11" t="n">
-        <v>80331</v>
+        <v>80309</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1639,21 +1624,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229497</v>
+        <v>6457</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>669335</v>
+        <v>669173</v>
       </c>
       <c r="R11" t="n">
-        <v>6692778</v>
+        <v>6692783</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1740,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131860649</v>
+        <v>131860637</v>
       </c>
       <c r="B12" t="n">
-        <v>96480</v>
+        <v>80334</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,21 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>210</v>
+        <v>229497</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>669159</v>
+        <v>669335</v>
       </c>
       <c r="R12" t="n">
-        <v>6692588</v>
+        <v>6692778</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1821,6 +1806,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1840,7 +1840,7 @@
         <v>131860660</v>
       </c>
       <c r="B13" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1949,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131860697</v>
+        <v>131860614</v>
       </c>
       <c r="B14" t="n">
-        <v>101249</v>
+        <v>80278</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1960,21 +1960,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>669157</v>
+        <v>669229</v>
       </c>
       <c r="R14" t="n">
-        <v>6692556</v>
+        <v>6692600</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2030,6 +2030,21 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2046,10 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131860614</v>
+        <v>131860697</v>
       </c>
       <c r="B15" t="n">
-        <v>80275</v>
+        <v>101252</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2057,21 +2072,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2081,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>669229</v>
+        <v>669157</v>
       </c>
       <c r="R15" t="n">
-        <v>6692600</v>
+        <v>6692556</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2127,21 +2142,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2161,7 +2161,7 @@
         <v>131860603</v>
       </c>
       <c r="B16" t="n">
-        <v>96384</v>
+        <v>96387</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>131860604</v>
       </c>
       <c r="B17" t="n">
-        <v>96384</v>
+        <v>96387</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>131860616</v>
       </c>
       <c r="B18" t="n">
-        <v>80275</v>
+        <v>80278</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>131860595</v>
       </c>
       <c r="B19" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131860635</v>
+        <v>131860618</v>
       </c>
       <c r="B20" t="n">
-        <v>80331</v>
+        <v>80278</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2612,21 +2612,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>669236</v>
+        <v>669202</v>
       </c>
       <c r="R20" t="n">
-        <v>6692814</v>
+        <v>6692608</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2713,32 +2713,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131860702</v>
+        <v>131860589</v>
       </c>
       <c r="B21" t="n">
-        <v>101249</v>
+        <v>91841</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2748,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>669289</v>
+        <v>669210</v>
       </c>
       <c r="R21" t="n">
-        <v>6692778</v>
+        <v>6692779</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2810,10 +2810,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131860589</v>
+        <v>131860588</v>
       </c>
       <c r="B22" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>669210</v>
+        <v>669143</v>
       </c>
       <c r="R22" t="n">
-        <v>6692779</v>
+        <v>6692724</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2907,32 +2907,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131860588</v>
+        <v>131860635</v>
       </c>
       <c r="B23" t="n">
-        <v>91838</v>
+        <v>80334</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>669143</v>
+        <v>669236</v>
       </c>
       <c r="R23" t="n">
-        <v>6692724</v>
+        <v>6692814</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2988,6 +2988,21 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3004,10 +3019,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131860618</v>
+        <v>131860702</v>
       </c>
       <c r="B24" t="n">
-        <v>80275</v>
+        <v>101252</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3015,21 +3030,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6456</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3039,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>669202</v>
+        <v>669289</v>
       </c>
       <c r="R24" t="n">
-        <v>6692608</v>
+        <v>6692778</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3085,21 +3100,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3116,10 +3116,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131860692</v>
+        <v>131860617</v>
       </c>
       <c r="B25" t="n">
-        <v>101249</v>
+        <v>80278</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3127,21 +3127,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>6456</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>669245</v>
+        <v>669355</v>
       </c>
       <c r="R25" t="n">
-        <v>6692828</v>
+        <v>6692827</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3197,6 +3197,21 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3213,10 +3228,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131860617</v>
+        <v>131860692</v>
       </c>
       <c r="B26" t="n">
-        <v>80275</v>
+        <v>101252</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3224,21 +3239,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6456</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3248,10 +3263,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>669355</v>
+        <v>669245</v>
       </c>
       <c r="R26" t="n">
-        <v>6692827</v>
+        <v>6692828</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3294,21 +3309,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3325,45 +3325,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131860690</v>
+        <v>131860609</v>
       </c>
       <c r="B27" t="n">
-        <v>92493</v>
+        <v>57904</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>669205</v>
+        <v>669095</v>
       </c>
       <c r="R27" t="n">
-        <v>6692610</v>
+        <v>6692372</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3406,21 +3411,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3437,10 +3427,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131860696</v>
+        <v>131860694</v>
       </c>
       <c r="B28" t="n">
-        <v>101249</v>
+        <v>101252</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3472,10 +3462,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>669141</v>
+        <v>669321</v>
       </c>
       <c r="R28" t="n">
-        <v>6692607</v>
+        <v>6692768</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3534,10 +3524,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131860694</v>
+        <v>131860690</v>
       </c>
       <c r="B29" t="n">
-        <v>101249</v>
+        <v>92496</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3545,21 +3535,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>1339</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3569,10 +3559,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>669321</v>
+        <v>669205</v>
       </c>
       <c r="R29" t="n">
-        <v>6692768</v>
+        <v>6692610</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3615,6 +3605,21 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3631,50 +3636,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131860609</v>
+        <v>131860696</v>
       </c>
       <c r="B30" t="n">
-        <v>57901</v>
+        <v>101252</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>669095</v>
+        <v>669141</v>
       </c>
       <c r="R30" t="n">
-        <v>6692372</v>
+        <v>6692607</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3733,10 +3733,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131860687</v>
+        <v>131860689</v>
       </c>
       <c r="B31" t="n">
-        <v>5178</v>
+        <v>92496</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3744,21 +3744,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100526</v>
+        <v>1339</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>669223</v>
+        <v>669316</v>
       </c>
       <c r="R31" t="n">
-        <v>6692603</v>
+        <v>6692776</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3845,10 +3845,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131860689</v>
+        <v>131860687</v>
       </c>
       <c r="B32" t="n">
-        <v>92493</v>
+        <v>5179</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3856,21 +3856,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1339</v>
+        <v>100526</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3880,10 +3880,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>669316</v>
+        <v>669223</v>
       </c>
       <c r="R32" t="n">
-        <v>6692776</v>
+        <v>6692603</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3957,10 +3957,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131860613</v>
+        <v>131860615</v>
       </c>
       <c r="B33" t="n">
-        <v>80275</v>
+        <v>80278</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3992,10 +3992,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>669232</v>
+        <v>669217</v>
       </c>
       <c r="R33" t="n">
-        <v>6692800</v>
+        <v>6692612</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4069,32 +4069,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131860615</v>
+        <v>131860662</v>
       </c>
       <c r="B34" t="n">
-        <v>80275</v>
+        <v>79269</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>669217</v>
+        <v>669203</v>
       </c>
       <c r="R34" t="n">
-        <v>6692612</v>
+        <v>6692759</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4153,17 +4153,17 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4181,32 +4181,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131860662</v>
+        <v>131860613</v>
       </c>
       <c r="B35" t="n">
-        <v>79266</v>
+        <v>80278</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4216,10 +4216,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>669203</v>
+        <v>669232</v>
       </c>
       <c r="R35" t="n">
-        <v>6692759</v>
+        <v>6692800</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4265,17 +4265,17 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4296,7 +4296,7 @@
         <v>131860661</v>
       </c>
       <c r="B36" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         <v>131860698</v>
       </c>
       <c r="B37" t="n">
-        <v>101249</v>
+        <v>101252</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>131860593</v>
       </c>
       <c r="B38" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>131860607</v>
       </c>
       <c r="B39" t="n">
-        <v>96384</v>
+        <v>96387</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>131860700</v>
       </c>
       <c r="B40" t="n">
-        <v>101249</v>
+        <v>101252</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         <v>131860699</v>
       </c>
       <c r="B41" t="n">
-        <v>101249</v>
+        <v>101252</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4890,10 +4890,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131860655</v>
+        <v>131860654</v>
       </c>
       <c r="B42" t="n">
-        <v>4780</v>
+        <v>4781</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4925,10 +4925,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>669222</v>
+        <v>669197</v>
       </c>
       <c r="R42" t="n">
-        <v>6692642</v>
+        <v>6692720</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5002,10 +5002,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131860654</v>
+        <v>131860655</v>
       </c>
       <c r="B43" t="n">
-        <v>4780</v>
+        <v>4781</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5037,10 +5037,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>669197</v>
+        <v>669222</v>
       </c>
       <c r="R43" t="n">
-        <v>6692720</v>
+        <v>6692642</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5114,10 +5114,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131860652</v>
+        <v>131860642</v>
       </c>
       <c r="B44" t="n">
-        <v>96480</v>
+        <v>80334</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5125,21 +5125,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>210</v>
+        <v>229497</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5149,10 +5149,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>668992</v>
+        <v>669212</v>
       </c>
       <c r="R44" t="n">
-        <v>6692504</v>
+        <v>6692609</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5198,17 +5198,17 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5226,10 +5226,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131860620</v>
+        <v>131860639</v>
       </c>
       <c r="B45" t="n">
-        <v>80275</v>
+        <v>80334</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5237,21 +5237,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>669176</v>
+        <v>669215</v>
       </c>
       <c r="R45" t="n">
-        <v>6692603</v>
+        <v>6692608</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5338,10 +5338,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131860648</v>
+        <v>131860652</v>
       </c>
       <c r="B46" t="n">
-        <v>75372</v>
+        <v>96483</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5349,21 +5349,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6426</v>
+        <v>210</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>669219</v>
+        <v>668992</v>
       </c>
       <c r="R46" t="n">
-        <v>6692641</v>
+        <v>6692504</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5419,6 +5419,21 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5435,10 +5450,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131860642</v>
+        <v>131860648</v>
       </c>
       <c r="B47" t="n">
-        <v>80331</v>
+        <v>75375</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5446,21 +5461,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229497</v>
+        <v>6426</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5470,10 +5485,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>669212</v>
+        <v>669219</v>
       </c>
       <c r="R47" t="n">
-        <v>6692609</v>
+        <v>6692641</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5516,21 +5531,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5547,10 +5547,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131860639</v>
+        <v>131860620</v>
       </c>
       <c r="B48" t="n">
-        <v>80331</v>
+        <v>80278</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5558,21 +5558,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5582,10 +5582,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>669215</v>
+        <v>669176</v>
       </c>
       <c r="R48" t="n">
-        <v>6692608</v>
+        <v>6692603</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5662,7 +5662,7 @@
         <v>131860685</v>
       </c>
       <c r="B49" t="n">
-        <v>80306</v>
+        <v>80309</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>131860634</v>
       </c>
       <c r="B50" t="n">
-        <v>80331</v>
+        <v>80334</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>131860683</v>
       </c>
       <c r="B51" t="n">
-        <v>80306</v>
+        <v>80309</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5998,7 +5998,7 @@
         <v>131860691</v>
       </c>
       <c r="B52" t="n">
-        <v>92493</v>
+        <v>92496</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6107,10 +6107,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131860651</v>
+        <v>131860641</v>
       </c>
       <c r="B53" t="n">
-        <v>96480</v>
+        <v>80334</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6118,21 +6118,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>210</v>
+        <v>229497</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6142,10 +6142,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>669305</v>
+        <v>669218</v>
       </c>
       <c r="R53" t="n">
-        <v>6692798</v>
+        <v>6692611</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6191,17 +6191,17 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6219,10 +6219,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131860641</v>
+        <v>131860643</v>
       </c>
       <c r="B54" t="n">
-        <v>80331</v>
+        <v>80334</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6254,10 +6254,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>669218</v>
+        <v>669201</v>
       </c>
       <c r="R54" t="n">
-        <v>6692611</v>
+        <v>6692608</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6331,10 +6331,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131860643</v>
+        <v>131860651</v>
       </c>
       <c r="B55" t="n">
-        <v>80331</v>
+        <v>96483</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6342,21 +6342,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>229497</v>
+        <v>210</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6366,10 +6366,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>669201</v>
+        <v>669305</v>
       </c>
       <c r="R55" t="n">
-        <v>6692608</v>
+        <v>6692798</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6415,17 +6415,17 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6446,7 +6446,7 @@
         <v>131860701</v>
       </c>
       <c r="B56" t="n">
-        <v>101249</v>
+        <v>101252</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6540,10 +6540,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132019922</v>
+        <v>132019904</v>
       </c>
       <c r="B57" t="n">
-        <v>101251</v>
+        <v>91262</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6551,21 +6551,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222498</v>
+        <v>4189</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Pers., nom.sanct</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6575,10 +6575,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>669218</v>
+        <v>669298</v>
       </c>
       <c r="R57" t="n">
-        <v>6692730</v>
+        <v>6692803</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6611,6 +6611,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Kalkrik granskog, under gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6637,10 +6642,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132019904</v>
+        <v>132019922</v>
       </c>
       <c r="B58" t="n">
-        <v>91261</v>
+        <v>101252</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6648,21 +6653,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4189</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6672,10 +6677,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>669298</v>
+        <v>669218</v>
       </c>
       <c r="R58" t="n">
-        <v>6692803</v>
+        <v>6692730</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6708,11 +6713,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Kalkrik granskog, under gran</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6742,7 +6742,7 @@
         <v>132019892</v>
       </c>
       <c r="B59" t="n">
-        <v>58065</v>
+        <v>58066</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>132019907</v>
       </c>
       <c r="B60" t="n">
-        <v>4780</v>
+        <v>4781</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>132019900</v>
       </c>
       <c r="B61" t="n">
-        <v>58278</v>
+        <v>58279</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
         <v>132019905</v>
       </c>
       <c r="B62" t="n">
-        <v>96482</v>
+        <v>96483</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7142,50 +7142,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132019895</v>
+        <v>132019919</v>
       </c>
       <c r="B63" t="n">
-        <v>58065</v>
+        <v>80309</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>6457</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>669191</v>
+        <v>669113</v>
       </c>
       <c r="R63" t="n">
-        <v>6692693</v>
+        <v>6692721</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7228,6 +7223,11 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>Populas tremula</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -7244,45 +7244,50 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132019919</v>
+        <v>132019895</v>
       </c>
       <c r="B64" t="n">
-        <v>80308</v>
+        <v>58066</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6457</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>669113</v>
+        <v>669191</v>
       </c>
       <c r="R64" t="n">
-        <v>6692721</v>
+        <v>6692693</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7325,11 +7330,6 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>Populas tremula</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -7349,7 +7349,7 @@
         <v>132019920</v>
       </c>
       <c r="B65" t="n">
-        <v>101251</v>
+        <v>101252</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7443,32 +7443,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132019897</v>
+        <v>132019889</v>
       </c>
       <c r="B66" t="n">
-        <v>80277</v>
+        <v>91841</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7478,10 +7478,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>669126</v>
+        <v>669241</v>
       </c>
       <c r="R66" t="n">
-        <v>6692721</v>
+        <v>6692784</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7525,9 +7525,19 @@
       <c r="AG66" t="b">
         <v>0</v>
       </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>Populas tremula</t>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -7545,32 +7555,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132019889</v>
+        <v>132019897</v>
       </c>
       <c r="B67" t="n">
-        <v>91840</v>
+        <v>80278</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7580,10 +7590,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>669241</v>
+        <v>669126</v>
       </c>
       <c r="R67" t="n">
-        <v>6692784</v>
+        <v>6692721</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7627,19 +7637,9 @@
       <c r="AG67" t="b">
         <v>0</v>
       </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>Populas tremula</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -7657,32 +7657,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132019903</v>
+        <v>132019888</v>
       </c>
       <c r="B68" t="n">
-        <v>75374</v>
+        <v>91841</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7692,10 +7692,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>669148</v>
+        <v>669198</v>
       </c>
       <c r="R68" t="n">
-        <v>6692645</v>
+        <v>6692759</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7739,9 +7739,19 @@
       <c r="AG68" t="b">
         <v>0</v>
       </c>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>Gran</t>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -7759,10 +7769,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132019898</v>
+        <v>132019903</v>
       </c>
       <c r="B69" t="n">
-        <v>80277</v>
+        <v>75375</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7770,21 +7780,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6456</v>
+        <v>6426</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7794,10 +7804,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>669154</v>
+        <v>669148</v>
       </c>
       <c r="R69" t="n">
-        <v>6692684</v>
+        <v>6692645</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7843,7 +7853,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Populas tremula</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -7861,32 +7871,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132019888</v>
+        <v>132019898</v>
       </c>
       <c r="B70" t="n">
-        <v>91840</v>
+        <v>80278</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7896,10 +7906,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>669198</v>
+        <v>669154</v>
       </c>
       <c r="R70" t="n">
-        <v>6692759</v>
+        <v>6692684</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7943,19 +7953,9 @@
       <c r="AG70" t="b">
         <v>0</v>
       </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>Populas tremula</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -7976,7 +7976,7 @@
         <v>132019901</v>
       </c>
       <c r="B71" t="n">
-        <v>75374</v>
+        <v>75375</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>132019918</v>
       </c>
       <c r="B72" t="n">
-        <v>80308</v>
+        <v>80309</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8177,32 +8177,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132019921</v>
+        <v>132019887</v>
       </c>
       <c r="B73" t="n">
-        <v>101251</v>
+        <v>91841</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8212,10 +8212,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>669204</v>
+        <v>669285</v>
       </c>
       <c r="R73" t="n">
-        <v>6692803</v>
+        <v>6692776</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8258,6 +8258,21 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -8274,32 +8289,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132019887</v>
+        <v>132019921</v>
       </c>
       <c r="B74" t="n">
-        <v>91840</v>
+        <v>101252</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8309,10 +8324,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>669285</v>
+        <v>669204</v>
       </c>
       <c r="R74" t="n">
-        <v>6692776</v>
+        <v>6692803</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8355,21 +8370,6 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -8389,7 +8389,7 @@
         <v>132019896</v>
       </c>
       <c r="B75" t="n">
-        <v>57903</v>
+        <v>57904</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>132019886</v>
       </c>
       <c r="B76" t="n">
-        <v>91840</v>
+        <v>91841</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         <v>132019899</v>
       </c>
       <c r="B77" t="n">
-        <v>80277</v>
+        <v>80278</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>132019906</v>
       </c>
       <c r="B78" t="n">
-        <v>4780</v>
+        <v>4781</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         <v>132019908</v>
       </c>
       <c r="B79" t="n">
-        <v>79268</v>
+        <v>79269</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         <v>132019894</v>
       </c>
       <c r="B80" t="n">
-        <v>58065</v>
+        <v>58066</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>132019893</v>
       </c>
       <c r="B81" t="n">
-        <v>58065</v>
+        <v>58066</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131860622</v>
       </c>
       <c r="B2" t="n">
-        <v>92301</v>
+        <v>92306</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131860605</v>
+        <v>131860688</v>
       </c>
       <c r="B3" t="n">
-        <v>96387</v>
+        <v>92501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2818</v>
+        <v>1339</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>668988</v>
+        <v>669177</v>
       </c>
       <c r="R3" t="n">
-        <v>6692259</v>
+        <v>6692736</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -868,6 +868,21 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -884,32 +899,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131860688</v>
+        <v>131860591</v>
       </c>
       <c r="B4" t="n">
-        <v>92496</v>
+        <v>91846</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>669177</v>
+        <v>669198</v>
       </c>
       <c r="R4" t="n">
-        <v>6692736</v>
+        <v>6692769</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -965,21 +980,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -996,32 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131860591</v>
+        <v>131860605</v>
       </c>
       <c r="B5" t="n">
-        <v>91841</v>
+        <v>96392</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>2818</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>669198</v>
+        <v>668988</v>
       </c>
       <c r="R5" t="n">
-        <v>6692769</v>
+        <v>6692259</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1208,7 +1208,7 @@
         <v>131860608</v>
       </c>
       <c r="B7" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131860656</v>
+        <v>131860695</v>
       </c>
       <c r="B8" t="n">
-        <v>4781</v>
+        <v>101257</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>669149</v>
+        <v>669270</v>
       </c>
       <c r="R8" t="n">
-        <v>6692521</v>
+        <v>6692768</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1388,21 +1388,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1419,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131860695</v>
+        <v>131860656</v>
       </c>
       <c r="B9" t="n">
-        <v>101252</v>
+        <v>4781</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1430,21 +1415,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>669270</v>
+        <v>669149</v>
       </c>
       <c r="R9" t="n">
-        <v>6692768</v>
+        <v>6692521</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1500,6 +1485,21 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1516,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131860649</v>
+        <v>131860684</v>
       </c>
       <c r="B10" t="n">
-        <v>96483</v>
+        <v>80314</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1527,21 +1527,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>210</v>
+        <v>6457</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>669159</v>
+        <v>669173</v>
       </c>
       <c r="R10" t="n">
-        <v>6692588</v>
+        <v>6692783</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1597,6 +1597,21 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1613,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131860684</v>
+        <v>131860649</v>
       </c>
       <c r="B11" t="n">
-        <v>80309</v>
+        <v>96488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1624,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6457</v>
+        <v>210</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>669173</v>
+        <v>669159</v>
       </c>
       <c r="R11" t="n">
-        <v>6692783</v>
+        <v>6692588</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1694,21 +1709,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1728,7 +1728,7 @@
         <v>131860637</v>
       </c>
       <c r="B12" t="n">
-        <v>80334</v>
+        <v>80339</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>131860660</v>
       </c>
       <c r="B13" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1949,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131860614</v>
+        <v>131860697</v>
       </c>
       <c r="B14" t="n">
-        <v>80278</v>
+        <v>101257</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1960,21 +1960,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>669229</v>
+        <v>669157</v>
       </c>
       <c r="R14" t="n">
-        <v>6692600</v>
+        <v>6692556</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2030,21 +2030,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2061,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131860697</v>
+        <v>131860614</v>
       </c>
       <c r="B15" t="n">
-        <v>101252</v>
+        <v>80283</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2072,21 +2057,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2096,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>669157</v>
+        <v>669229</v>
       </c>
       <c r="R15" t="n">
-        <v>6692556</v>
+        <v>6692600</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2142,6 +2127,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2158,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131860603</v>
+        <v>131860604</v>
       </c>
       <c r="B16" t="n">
-        <v>96387</v>
+        <v>96392</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2187,16 +2187,20 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>669306</v>
+        <v>669204</v>
       </c>
       <c r="R16" t="n">
-        <v>6692797</v>
+        <v>6692601</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2237,22 +2241,23 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2270,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131860604</v>
+        <v>131860616</v>
       </c>
       <c r="B17" t="n">
-        <v>96387</v>
+        <v>80283</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2281,38 +2286,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2818</v>
+        <v>6456</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>669204</v>
+        <v>669151</v>
       </c>
       <c r="R17" t="n">
-        <v>6692601</v>
+        <v>6692600</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2347,29 +2348,33 @@
           <t>2026-03-22</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2387,10 +2392,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131860616</v>
+        <v>131860603</v>
       </c>
       <c r="B18" t="n">
-        <v>80278</v>
+        <v>96392</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2398,21 +2403,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6456</v>
+        <v>2818</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>669151</v>
+        <v>669306</v>
       </c>
       <c r="R18" t="n">
-        <v>6692600</v>
+        <v>6692797</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2460,11 +2465,6 @@
           <t>2026-03-22</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2476,17 +2476,17 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2507,7 +2507,7 @@
         <v>131860595</v>
       </c>
       <c r="B19" t="n">
-        <v>91841</v>
+        <v>91846</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131860618</v>
+        <v>131860702</v>
       </c>
       <c r="B20" t="n">
-        <v>80278</v>
+        <v>101257</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2612,21 +2612,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6456</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>669202</v>
+        <v>669289</v>
       </c>
       <c r="R20" t="n">
-        <v>6692608</v>
+        <v>6692778</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2682,21 +2682,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2713,32 +2698,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131860589</v>
+        <v>131860635</v>
       </c>
       <c r="B21" t="n">
-        <v>91841</v>
+        <v>80339</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2748,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>669210</v>
+        <v>669236</v>
       </c>
       <c r="R21" t="n">
-        <v>6692779</v>
+        <v>6692814</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2794,6 +2779,21 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2810,10 +2810,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131860588</v>
+        <v>131860589</v>
       </c>
       <c r="B22" t="n">
-        <v>91841</v>
+        <v>91846</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>669143</v>
+        <v>669210</v>
       </c>
       <c r="R22" t="n">
-        <v>6692724</v>
+        <v>6692779</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2907,32 +2907,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131860635</v>
+        <v>131860588</v>
       </c>
       <c r="B23" t="n">
-        <v>80334</v>
+        <v>91846</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>669236</v>
+        <v>669143</v>
       </c>
       <c r="R23" t="n">
-        <v>6692814</v>
+        <v>6692724</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2988,21 +2988,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3019,10 +3004,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131860702</v>
+        <v>131860618</v>
       </c>
       <c r="B24" t="n">
-        <v>101252</v>
+        <v>80283</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3030,21 +3015,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>6456</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3054,10 +3039,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>669289</v>
+        <v>669202</v>
       </c>
       <c r="R24" t="n">
-        <v>6692778</v>
+        <v>6692608</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3100,6 +3085,21 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3119,7 +3119,7 @@
         <v>131860617</v>
       </c>
       <c r="B25" t="n">
-        <v>80278</v>
+        <v>80283</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>131860692</v>
       </c>
       <c r="B26" t="n">
-        <v>101252</v>
+        <v>101257</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3325,50 +3325,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131860609</v>
+        <v>131860690</v>
       </c>
       <c r="B27" t="n">
-        <v>57904</v>
+        <v>92501</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>669095</v>
+        <v>669205</v>
       </c>
       <c r="R27" t="n">
-        <v>6692372</v>
+        <v>6692610</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3411,6 +3406,21 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3427,45 +3437,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131860694</v>
+        <v>131860609</v>
       </c>
       <c r="B28" t="n">
-        <v>101252</v>
+        <v>57909</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>669321</v>
+        <v>669095</v>
       </c>
       <c r="R28" t="n">
-        <v>6692768</v>
+        <v>6692372</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3524,10 +3539,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131860690</v>
+        <v>131860696</v>
       </c>
       <c r="B29" t="n">
-        <v>92496</v>
+        <v>101257</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3535,21 +3550,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3559,10 +3574,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>669205</v>
+        <v>669141</v>
       </c>
       <c r="R29" t="n">
-        <v>6692610</v>
+        <v>6692607</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3605,21 +3620,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3636,10 +3636,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131860696</v>
+        <v>131860694</v>
       </c>
       <c r="B30" t="n">
-        <v>101252</v>
+        <v>101257</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3671,10 +3671,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>669141</v>
+        <v>669321</v>
       </c>
       <c r="R30" t="n">
-        <v>6692607</v>
+        <v>6692768</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3736,7 +3736,7 @@
         <v>131860689</v>
       </c>
       <c r="B31" t="n">
-        <v>92496</v>
+        <v>92501</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3845,10 +3845,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131860687</v>
+        <v>131860615</v>
       </c>
       <c r="B32" t="n">
-        <v>5179</v>
+        <v>80283</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3856,21 +3856,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100526</v>
+        <v>6456</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3880,10 +3880,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>669223</v>
+        <v>669217</v>
       </c>
       <c r="R32" t="n">
-        <v>6692603</v>
+        <v>6692612</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3929,17 +3929,17 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -3957,32 +3957,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131860615</v>
+        <v>131860662</v>
       </c>
       <c r="B33" t="n">
-        <v>80278</v>
+        <v>79274</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3992,10 +3992,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>669217</v>
+        <v>669203</v>
       </c>
       <c r="R33" t="n">
-        <v>6692612</v>
+        <v>6692759</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4041,17 +4041,17 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4069,32 +4069,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131860662</v>
+        <v>131860613</v>
       </c>
       <c r="B34" t="n">
-        <v>79269</v>
+        <v>80283</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>669203</v>
+        <v>669232</v>
       </c>
       <c r="R34" t="n">
-        <v>6692759</v>
+        <v>6692800</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4153,17 +4153,17 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4181,32 +4181,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131860613</v>
+        <v>131860661</v>
       </c>
       <c r="B35" t="n">
-        <v>80278</v>
+        <v>79274</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4216,10 +4216,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>669232</v>
+        <v>669202</v>
       </c>
       <c r="R35" t="n">
-        <v>6692800</v>
+        <v>6692764</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4265,17 +4265,17 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4293,32 +4293,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131860661</v>
+        <v>131860687</v>
       </c>
       <c r="B36" t="n">
-        <v>79269</v>
+        <v>5179</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4328,10 +4328,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>669202</v>
+        <v>669223</v>
       </c>
       <c r="R36" t="n">
-        <v>6692764</v>
+        <v>6692603</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4408,7 +4408,7 @@
         <v>131860698</v>
       </c>
       <c r="B37" t="n">
-        <v>101252</v>
+        <v>101257</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>131860593</v>
       </c>
       <c r="B38" t="n">
-        <v>91841</v>
+        <v>91846</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>131860607</v>
       </c>
       <c r="B39" t="n">
-        <v>96387</v>
+        <v>96392</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>131860700</v>
       </c>
       <c r="B40" t="n">
-        <v>101252</v>
+        <v>101257</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         <v>131860699</v>
       </c>
       <c r="B41" t="n">
-        <v>101252</v>
+        <v>101257</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5114,10 +5114,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131860642</v>
+        <v>131860652</v>
       </c>
       <c r="B44" t="n">
-        <v>80334</v>
+        <v>96488</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5125,21 +5125,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229497</v>
+        <v>210</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5149,10 +5149,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>669212</v>
+        <v>668992</v>
       </c>
       <c r="R44" t="n">
-        <v>6692609</v>
+        <v>6692504</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5198,17 +5198,17 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5226,10 +5226,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131860639</v>
+        <v>131860648</v>
       </c>
       <c r="B45" t="n">
-        <v>80334</v>
+        <v>75380</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5237,21 +5237,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229497</v>
+        <v>6426</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>669215</v>
+        <v>669219</v>
       </c>
       <c r="R45" t="n">
-        <v>6692608</v>
+        <v>6692641</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5307,21 +5307,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5338,10 +5323,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131860652</v>
+        <v>131860620</v>
       </c>
       <c r="B46" t="n">
-        <v>96483</v>
+        <v>80283</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5349,21 +5334,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>210</v>
+        <v>6456</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5373,10 +5358,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>668992</v>
+        <v>669176</v>
       </c>
       <c r="R46" t="n">
-        <v>6692504</v>
+        <v>6692603</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5422,17 +5407,17 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5450,10 +5435,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131860648</v>
+        <v>131860642</v>
       </c>
       <c r="B47" t="n">
-        <v>75375</v>
+        <v>80339</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5461,21 +5446,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6426</v>
+        <v>229497</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5485,10 +5470,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>669219</v>
+        <v>669212</v>
       </c>
       <c r="R47" t="n">
-        <v>6692641</v>
+        <v>6692609</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5531,6 +5516,21 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5547,10 +5547,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131860620</v>
+        <v>131860639</v>
       </c>
       <c r="B48" t="n">
-        <v>80278</v>
+        <v>80339</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5558,21 +5558,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5582,10 +5582,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>669176</v>
+        <v>669215</v>
       </c>
       <c r="R48" t="n">
-        <v>6692603</v>
+        <v>6692608</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5662,7 +5662,7 @@
         <v>131860685</v>
       </c>
       <c r="B49" t="n">
-        <v>80309</v>
+        <v>80314</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>131860634</v>
       </c>
       <c r="B50" t="n">
-        <v>80334</v>
+        <v>80339</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131860683</v>
+        <v>131860691</v>
       </c>
       <c r="B51" t="n">
-        <v>80309</v>
+        <v>92501</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5894,21 +5894,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6457</v>
+        <v>1339</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5918,10 +5918,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>669167</v>
+        <v>669198</v>
       </c>
       <c r="R51" t="n">
-        <v>6692763</v>
+        <v>6692600</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5967,17 +5967,17 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -5995,10 +5995,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131860691</v>
+        <v>131860683</v>
       </c>
       <c r="B52" t="n">
-        <v>92496</v>
+        <v>80314</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6006,21 +6006,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1339</v>
+        <v>6457</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6030,10 +6030,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>669198</v>
+        <v>669167</v>
       </c>
       <c r="R52" t="n">
-        <v>6692600</v>
+        <v>6692763</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6079,17 +6079,17 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6107,10 +6107,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131860641</v>
+        <v>131860651</v>
       </c>
       <c r="B53" t="n">
-        <v>80334</v>
+        <v>96488</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6118,21 +6118,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229497</v>
+        <v>210</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6142,10 +6142,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>669218</v>
+        <v>669305</v>
       </c>
       <c r="R53" t="n">
-        <v>6692611</v>
+        <v>6692798</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6191,17 +6191,17 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6219,10 +6219,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131860643</v>
+        <v>131860641</v>
       </c>
       <c r="B54" t="n">
-        <v>80334</v>
+        <v>80339</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6254,10 +6254,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>669201</v>
+        <v>669218</v>
       </c>
       <c r="R54" t="n">
-        <v>6692608</v>
+        <v>6692611</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6331,10 +6331,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131860651</v>
+        <v>131860643</v>
       </c>
       <c r="B55" t="n">
-        <v>96483</v>
+        <v>80339</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6342,21 +6342,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>210</v>
+        <v>229497</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6366,10 +6366,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>669305</v>
+        <v>669201</v>
       </c>
       <c r="R55" t="n">
-        <v>6692798</v>
+        <v>6692608</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6415,17 +6415,17 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6446,7 +6446,7 @@
         <v>131860701</v>
       </c>
       <c r="B56" t="n">
-        <v>101252</v>
+        <v>101257</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6543,7 +6543,7 @@
         <v>132019904</v>
       </c>
       <c r="B57" t="n">
-        <v>91262</v>
+        <v>91267</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         <v>132019922</v>
       </c>
       <c r="B58" t="n">
-        <v>101252</v>
+        <v>101257</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6739,50 +6739,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132019892</v>
+        <v>132019907</v>
       </c>
       <c r="B59" t="n">
-        <v>58066</v>
+        <v>4781</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>102306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>669331</v>
+        <v>669141</v>
       </c>
       <c r="R59" t="n">
-        <v>6692814</v>
+        <v>6692648</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6825,6 +6820,11 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -6841,45 +6841,50 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132019907</v>
+        <v>132019892</v>
       </c>
       <c r="B60" t="n">
-        <v>4781</v>
+        <v>58071</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>102306</v>
+        <v>103021</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>669141</v>
+        <v>669331</v>
       </c>
       <c r="R60" t="n">
-        <v>6692648</v>
+        <v>6692814</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6922,11 +6927,6 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AI60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -6946,7 +6946,7 @@
         <v>132019900</v>
       </c>
       <c r="B61" t="n">
-        <v>58279</v>
+        <v>58284</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
         <v>132019905</v>
       </c>
       <c r="B62" t="n">
-        <v>96483</v>
+        <v>96488</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7142,45 +7142,50 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132019919</v>
+        <v>132019895</v>
       </c>
       <c r="B63" t="n">
-        <v>80309</v>
+        <v>58071</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6457</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>669113</v>
+        <v>669191</v>
       </c>
       <c r="R63" t="n">
-        <v>6692721</v>
+        <v>6692693</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7223,11 +7228,6 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>Populas tremula</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -7244,50 +7244,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132019895</v>
+        <v>132019919</v>
       </c>
       <c r="B64" t="n">
-        <v>58066</v>
+        <v>80314</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>6457</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>669191</v>
+        <v>669113</v>
       </c>
       <c r="R64" t="n">
-        <v>6692693</v>
+        <v>6692721</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7330,6 +7325,11 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>Populas tremula</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -7346,32 +7346,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132019920</v>
+        <v>132019889</v>
       </c>
       <c r="B65" t="n">
-        <v>101252</v>
+        <v>91846</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7381,10 +7381,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>669116</v>
+        <v>669241</v>
       </c>
       <c r="R65" t="n">
-        <v>6692739</v>
+        <v>6692784</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7427,6 +7427,21 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -7443,32 +7458,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132019889</v>
+        <v>132019897</v>
       </c>
       <c r="B66" t="n">
-        <v>91841</v>
+        <v>80283</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7478,10 +7493,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>669241</v>
+        <v>669126</v>
       </c>
       <c r="R66" t="n">
-        <v>6692784</v>
+        <v>6692721</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7525,19 +7540,9 @@
       <c r="AG66" t="b">
         <v>0</v>
       </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>Populas tremula</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -7555,10 +7560,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132019897</v>
+        <v>132019920</v>
       </c>
       <c r="B67" t="n">
-        <v>80278</v>
+        <v>101257</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7566,21 +7571,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6456</v>
+        <v>222498</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7590,10 +7595,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>669126</v>
+        <v>669116</v>
       </c>
       <c r="R67" t="n">
-        <v>6692721</v>
+        <v>6692739</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7636,11 +7641,6 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>Populas tremula</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -7657,32 +7657,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132019888</v>
+        <v>132019903</v>
       </c>
       <c r="B68" t="n">
-        <v>91841</v>
+        <v>75380</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7692,10 +7692,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>669198</v>
+        <v>669148</v>
       </c>
       <c r="R68" t="n">
-        <v>6692759</v>
+        <v>6692645</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7739,19 +7739,9 @@
       <c r="AG68" t="b">
         <v>0</v>
       </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -7769,10 +7759,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132019903</v>
+        <v>132019898</v>
       </c>
       <c r="B69" t="n">
-        <v>75375</v>
+        <v>80283</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7780,21 +7770,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6426</v>
+        <v>6456</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7804,10 +7794,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>669148</v>
+        <v>669154</v>
       </c>
       <c r="R69" t="n">
-        <v>6692645</v>
+        <v>6692684</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7853,7 +7843,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Populas tremula</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -7871,10 +7861,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132019898</v>
+        <v>132019901</v>
       </c>
       <c r="B70" t="n">
-        <v>80278</v>
+        <v>75380</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7882,21 +7872,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6456</v>
+        <v>6426</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7906,7 +7896,7 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>669154</v>
+        <v>669196</v>
       </c>
       <c r="R70" t="n">
         <v>6692684</v>
@@ -7955,7 +7945,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Populas tremula</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -7973,32 +7963,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132019901</v>
+        <v>132019888</v>
       </c>
       <c r="B71" t="n">
-        <v>75375</v>
+        <v>91846</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8008,10 +7998,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>669196</v>
+        <v>669198</v>
       </c>
       <c r="R71" t="n">
-        <v>6692684</v>
+        <v>6692759</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8055,9 +8045,19 @@
       <c r="AG71" t="b">
         <v>0</v>
       </c>
-      <c r="AI71" t="inlineStr">
+      <c r="AJ71" t="inlineStr">
         <is>
           <t>gran</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8078,7 +8078,7 @@
         <v>132019918</v>
       </c>
       <c r="B72" t="n">
-        <v>80309</v>
+        <v>80314</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8180,7 +8180,7 @@
         <v>132019887</v>
       </c>
       <c r="B73" t="n">
-        <v>91841</v>
+        <v>91846</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8292,7 +8292,7 @@
         <v>132019921</v>
       </c>
       <c r="B74" t="n">
-        <v>101252</v>
+        <v>101257</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8389,7 +8389,7 @@
         <v>132019896</v>
       </c>
       <c r="B75" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>132019886</v>
       </c>
       <c r="B76" t="n">
-        <v>91841</v>
+        <v>91846</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         <v>132019899</v>
       </c>
       <c r="B77" t="n">
-        <v>80278</v>
+        <v>80283</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         <v>132019908</v>
       </c>
       <c r="B79" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         <v>132019894</v>
       </c>
       <c r="B80" t="n">
-        <v>58066</v>
+        <v>58071</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>132019893</v>
       </c>
       <c r="B81" t="n">
-        <v>58066</v>
+        <v>58071</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -2158,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131860604</v>
+        <v>131860616</v>
       </c>
       <c r="B16" t="n">
-        <v>96392</v>
+        <v>80283</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2169,38 +2169,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2818</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>669204</v>
+        <v>669151</v>
       </c>
       <c r="R16" t="n">
-        <v>6692601</v>
+        <v>6692600</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2235,29 +2231,33 @@
           <t>2026-03-22</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2275,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131860616</v>
+        <v>131860603</v>
       </c>
       <c r="B17" t="n">
-        <v>80283</v>
+        <v>96392</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2286,21 +2286,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6456</v>
+        <v>2818</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>669151</v>
+        <v>669306</v>
       </c>
       <c r="R17" t="n">
-        <v>6692600</v>
+        <v>6692797</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2348,11 +2348,6 @@
           <t>2026-03-22</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2364,17 +2359,17 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2392,7 +2387,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131860603</v>
+        <v>131860604</v>
       </c>
       <c r="B18" t="n">
         <v>96392</v>
@@ -2421,16 +2416,20 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>669306</v>
+        <v>669204</v>
       </c>
       <c r="R18" t="n">
-        <v>6692797</v>
+        <v>6692601</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2471,22 +2470,23 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2698,32 +2698,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131860635</v>
+        <v>131860589</v>
       </c>
       <c r="B21" t="n">
-        <v>80339</v>
+        <v>91846</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>669236</v>
+        <v>669210</v>
       </c>
       <c r="R21" t="n">
-        <v>6692814</v>
+        <v>6692779</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2779,21 +2779,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2810,7 +2795,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131860589</v>
+        <v>131860588</v>
       </c>
       <c r="B22" t="n">
         <v>91846</v>
@@ -2845,10 +2830,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>669210</v>
+        <v>669143</v>
       </c>
       <c r="R22" t="n">
-        <v>6692779</v>
+        <v>6692724</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2907,32 +2892,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131860588</v>
+        <v>131860618</v>
       </c>
       <c r="B23" t="n">
-        <v>91846</v>
+        <v>80283</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2942,10 +2927,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>669143</v>
+        <v>669202</v>
       </c>
       <c r="R23" t="n">
-        <v>6692724</v>
+        <v>6692608</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2988,6 +2973,21 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3004,10 +3004,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131860618</v>
+        <v>131860635</v>
       </c>
       <c r="B24" t="n">
-        <v>80283</v>
+        <v>80339</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3015,21 +3015,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3039,10 +3039,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>669202</v>
+        <v>669236</v>
       </c>
       <c r="R24" t="n">
-        <v>6692608</v>
+        <v>6692814</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3116,10 +3116,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131860617</v>
+        <v>131860692</v>
       </c>
       <c r="B25" t="n">
-        <v>80283</v>
+        <v>101257</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3127,21 +3127,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6456</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>669355</v>
+        <v>669245</v>
       </c>
       <c r="R25" t="n">
-        <v>6692827</v>
+        <v>6692828</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3197,21 +3197,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3228,10 +3213,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131860692</v>
+        <v>131860617</v>
       </c>
       <c r="B26" t="n">
-        <v>101257</v>
+        <v>80283</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3239,21 +3224,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>6456</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3263,10 +3248,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>669245</v>
+        <v>669355</v>
       </c>
       <c r="R26" t="n">
-        <v>6692828</v>
+        <v>6692827</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3309,6 +3294,21 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3325,45 +3325,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131860690</v>
+        <v>131860609</v>
       </c>
       <c r="B27" t="n">
-        <v>92501</v>
+        <v>57909</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>669205</v>
+        <v>669095</v>
       </c>
       <c r="R27" t="n">
-        <v>6692610</v>
+        <v>6692372</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3406,21 +3411,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3437,50 +3427,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131860609</v>
+        <v>131860696</v>
       </c>
       <c r="B28" t="n">
-        <v>57909</v>
+        <v>101257</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>669095</v>
+        <v>669141</v>
       </c>
       <c r="R28" t="n">
-        <v>6692372</v>
+        <v>6692607</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3539,7 +3524,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131860696</v>
+        <v>131860694</v>
       </c>
       <c r="B29" t="n">
         <v>101257</v>
@@ -3574,10 +3559,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>669141</v>
+        <v>669321</v>
       </c>
       <c r="R29" t="n">
-        <v>6692607</v>
+        <v>6692768</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3636,10 +3621,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131860694</v>
+        <v>131860690</v>
       </c>
       <c r="B30" t="n">
-        <v>101257</v>
+        <v>92501</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3647,21 +3632,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>1339</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3671,10 +3656,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>669321</v>
+        <v>669205</v>
       </c>
       <c r="R30" t="n">
-        <v>6692768</v>
+        <v>6692610</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3717,6 +3702,21 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -5659,10 +5659,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131860685</v>
+        <v>131860634</v>
       </c>
       <c r="B49" t="n">
-        <v>80314</v>
+        <v>80339</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5670,21 +5670,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6457</v>
+        <v>229497</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>669242</v>
+        <v>669233</v>
       </c>
       <c r="R49" t="n">
-        <v>6692625</v>
+        <v>6692806</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5771,10 +5771,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131860634</v>
+        <v>131860685</v>
       </c>
       <c r="B50" t="n">
-        <v>80339</v>
+        <v>80314</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5782,21 +5782,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>229497</v>
+        <v>6457</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5806,10 +5806,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>669233</v>
+        <v>669242</v>
       </c>
       <c r="R50" t="n">
-        <v>6692806</v>
+        <v>6692625</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6540,10 +6540,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132019904</v>
+        <v>132019922</v>
       </c>
       <c r="B57" t="n">
-        <v>91267</v>
+        <v>101257</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6551,21 +6551,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4189</v>
+        <v>222498</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6575,10 +6575,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>669298</v>
+        <v>669218</v>
       </c>
       <c r="R57" t="n">
-        <v>6692803</v>
+        <v>6692730</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6611,11 +6611,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Kalkrik granskog, under gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6642,10 +6637,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132019922</v>
+        <v>132019904</v>
       </c>
       <c r="B58" t="n">
-        <v>101257</v>
+        <v>91267</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6653,21 +6648,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>4189</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Pers., nom.sanct</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6677,10 +6672,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>669218</v>
+        <v>669298</v>
       </c>
       <c r="R58" t="n">
-        <v>6692730</v>
+        <v>6692803</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6713,6 +6708,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Kalkrik granskog, under gran</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7657,32 +7657,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132019903</v>
+        <v>132019888</v>
       </c>
       <c r="B68" t="n">
-        <v>75380</v>
+        <v>91846</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7692,10 +7692,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>669148</v>
+        <v>669198</v>
       </c>
       <c r="R68" t="n">
-        <v>6692645</v>
+        <v>6692759</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7739,9 +7739,19 @@
       <c r="AG68" t="b">
         <v>0</v>
       </c>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>Gran</t>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -7759,10 +7769,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132019898</v>
+        <v>132019903</v>
       </c>
       <c r="B69" t="n">
-        <v>80283</v>
+        <v>75380</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7770,21 +7780,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6456</v>
+        <v>6426</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7794,10 +7804,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>669154</v>
+        <v>669148</v>
       </c>
       <c r="R69" t="n">
-        <v>6692684</v>
+        <v>6692645</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7843,7 +7853,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Populas tremula</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -7861,10 +7871,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132019901</v>
+        <v>132019898</v>
       </c>
       <c r="B70" t="n">
-        <v>75380</v>
+        <v>80283</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7872,21 +7882,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6426</v>
+        <v>6456</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7896,7 +7906,7 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>669196</v>
+        <v>669154</v>
       </c>
       <c r="R70" t="n">
         <v>6692684</v>
@@ -7945,7 +7955,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>Populas tremula</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -7963,32 +7973,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132019888</v>
+        <v>132019901</v>
       </c>
       <c r="B71" t="n">
-        <v>91846</v>
+        <v>75380</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7998,10 +8008,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>669198</v>
+        <v>669196</v>
       </c>
       <c r="R71" t="n">
-        <v>6692759</v>
+        <v>6692684</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8045,19 +8055,9 @@
       <c r="AG71" t="b">
         <v>0</v>
       </c>
-      <c r="AJ71" t="inlineStr">
+      <c r="AI71" t="inlineStr">
         <is>
           <t>gran</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8488,32 +8488,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132019886</v>
+        <v>132019899</v>
       </c>
       <c r="B76" t="n">
-        <v>91846</v>
+        <v>80283</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8523,10 +8523,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>669131</v>
+        <v>669151</v>
       </c>
       <c r="R76" t="n">
-        <v>6692781</v>
+        <v>6692676</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8570,19 +8570,9 @@
       <c r="AG76" t="b">
         <v>0</v>
       </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>Populas tremula</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -8600,32 +8590,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132019899</v>
+        <v>132019886</v>
       </c>
       <c r="B77" t="n">
-        <v>80283</v>
+        <v>91846</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8635,10 +8625,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>669151</v>
+        <v>669131</v>
       </c>
       <c r="R77" t="n">
-        <v>6692676</v>
+        <v>6692781</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8682,9 +8672,19 @@
       <c r="AG77" t="b">
         <v>0</v>
       </c>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>Populas tremula</t>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131860622</v>
       </c>
       <c r="B2" t="n">
-        <v>92306</v>
+        <v>92308</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>131860688</v>
       </c>
       <c r="B3" t="n">
-        <v>92501</v>
+        <v>92503</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
+          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -902,7 +902,7 @@
         <v>131860591</v>
       </c>
       <c r="B4" t="n">
-        <v>91846</v>
+        <v>91848</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>131860605</v>
       </c>
       <c r="B5" t="n">
-        <v>96392</v>
+        <v>96394</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,32 +1093,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131860653</v>
+        <v>131860608</v>
       </c>
       <c r="B6" t="n">
-        <v>4781</v>
+        <v>57911</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>669179</v>
+        <v>669103</v>
       </c>
       <c r="R6" t="n">
-        <v>6692717</v>
+        <v>6692390</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1166,6 +1166,11 @@
           <t>2026-03-22</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Flög in i skogen och satte sig ett träd.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1174,21 +1179,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1205,32 +1195,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131860608</v>
+        <v>131860653</v>
       </c>
       <c r="B7" t="n">
-        <v>57909</v>
+        <v>4781</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>669103</v>
+        <v>669179</v>
       </c>
       <c r="R7" t="n">
-        <v>6692390</v>
+        <v>6692717</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1278,11 +1268,6 @@
           <t>2026-03-22</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Flög in i skogen och satte sig ett träd.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1291,6 +1276,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131860695</v>
+        <v>131860656</v>
       </c>
       <c r="B8" t="n">
-        <v>101257</v>
+        <v>4781</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>669270</v>
+        <v>669149</v>
       </c>
       <c r="R8" t="n">
-        <v>6692768</v>
+        <v>6692521</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1388,6 +1388,21 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1404,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131860656</v>
+        <v>131860695</v>
       </c>
       <c r="B9" t="n">
-        <v>4781</v>
+        <v>101260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1415,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>669149</v>
+        <v>669270</v>
       </c>
       <c r="R9" t="n">
-        <v>6692521</v>
+        <v>6692768</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1486,21 +1501,6 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
@@ -1509,17 +1509,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
+          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131860684</v>
+        <v>131860649</v>
       </c>
       <c r="B10" t="n">
-        <v>80314</v>
+        <v>96490</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1527,21 +1527,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6457</v>
+        <v>210</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>669173</v>
+        <v>669159</v>
       </c>
       <c r="R10" t="n">
-        <v>6692783</v>
+        <v>6692588</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1597,21 +1597,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1628,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131860649</v>
+        <v>131860684</v>
       </c>
       <c r="B11" t="n">
-        <v>96488</v>
+        <v>80316</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1639,21 +1624,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>210</v>
+        <v>6457</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>669159</v>
+        <v>669173</v>
       </c>
       <c r="R11" t="n">
-        <v>6692588</v>
+        <v>6692783</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1710,6 +1695,21 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
+          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1728,7 +1728,7 @@
         <v>131860637</v>
       </c>
       <c r="B12" t="n">
-        <v>80339</v>
+        <v>80341</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>131860660</v>
       </c>
       <c r="B13" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1949,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131860697</v>
+        <v>131860614</v>
       </c>
       <c r="B14" t="n">
-        <v>101257</v>
+        <v>80285</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1960,21 +1960,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>669157</v>
+        <v>669229</v>
       </c>
       <c r="R14" t="n">
-        <v>6692556</v>
+        <v>6692600</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2030,6 +2030,21 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2046,10 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131860614</v>
+        <v>131860697</v>
       </c>
       <c r="B15" t="n">
-        <v>80283</v>
+        <v>101260</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2057,21 +2072,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2081,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>669229</v>
+        <v>669157</v>
       </c>
       <c r="R15" t="n">
-        <v>6692600</v>
+        <v>6692556</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2127,21 +2142,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2161,7 +2161,7 @@
         <v>131860616</v>
       </c>
       <c r="B16" t="n">
-        <v>80283</v>
+        <v>80285</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>131860603</v>
       </c>
       <c r="B17" t="n">
-        <v>96392</v>
+        <v>96394</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>131860604</v>
       </c>
       <c r="B18" t="n">
-        <v>96392</v>
+        <v>96394</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>131860595</v>
       </c>
       <c r="B19" t="n">
-        <v>91846</v>
+        <v>91848</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,32 +2601,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131860702</v>
+        <v>131860589</v>
       </c>
       <c r="B20" t="n">
-        <v>101257</v>
+        <v>91848</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>669289</v>
+        <v>669210</v>
       </c>
       <c r="R20" t="n">
-        <v>6692778</v>
+        <v>6692779</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2698,10 +2698,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131860589</v>
+        <v>131860588</v>
       </c>
       <c r="B21" t="n">
-        <v>91846</v>
+        <v>91848</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>669210</v>
+        <v>669143</v>
       </c>
       <c r="R21" t="n">
-        <v>6692779</v>
+        <v>6692724</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2795,32 +2795,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131860588</v>
+        <v>131860618</v>
       </c>
       <c r="B22" t="n">
-        <v>91846</v>
+        <v>80285</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>669143</v>
+        <v>669202</v>
       </c>
       <c r="R22" t="n">
-        <v>6692724</v>
+        <v>6692608</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2876,6 +2876,21 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2892,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131860618</v>
+        <v>131860635</v>
       </c>
       <c r="B23" t="n">
-        <v>80283</v>
+        <v>80341</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2903,21 +2918,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2927,10 +2942,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>669202</v>
+        <v>669236</v>
       </c>
       <c r="R23" t="n">
-        <v>6692608</v>
+        <v>6692814</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3004,10 +3019,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131860635</v>
+        <v>131860702</v>
       </c>
       <c r="B24" t="n">
-        <v>80339</v>
+        <v>101260</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3015,21 +3030,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3039,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>669236</v>
+        <v>669289</v>
       </c>
       <c r="R24" t="n">
-        <v>6692814</v>
+        <v>6692778</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3085,21 +3100,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3116,10 +3116,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131860692</v>
+        <v>131860617</v>
       </c>
       <c r="B25" t="n">
-        <v>101257</v>
+        <v>80285</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3127,21 +3127,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>6456</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>669245</v>
+        <v>669355</v>
       </c>
       <c r="R25" t="n">
-        <v>6692828</v>
+        <v>6692827</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3197,6 +3197,21 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3213,10 +3228,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131860617</v>
+        <v>131860692</v>
       </c>
       <c r="B26" t="n">
-        <v>80283</v>
+        <v>101260</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3224,21 +3239,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6456</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3248,10 +3263,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>669355</v>
+        <v>669245</v>
       </c>
       <c r="R26" t="n">
-        <v>6692827</v>
+        <v>6692828</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3295,21 +3310,6 @@
       <c r="AG26" t="b">
         <v>0</v>
       </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
+          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3328,7 +3328,7 @@
         <v>131860609</v>
       </c>
       <c r="B27" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3427,10 +3427,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131860696</v>
+        <v>131860694</v>
       </c>
       <c r="B28" t="n">
-        <v>101257</v>
+        <v>101260</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3462,10 +3462,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>669141</v>
+        <v>669321</v>
       </c>
       <c r="R28" t="n">
-        <v>6692607</v>
+        <v>6692768</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3517,17 +3517,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
+          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131860694</v>
+        <v>131860696</v>
       </c>
       <c r="B29" t="n">
-        <v>101257</v>
+        <v>101260</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>669321</v>
+        <v>669141</v>
       </c>
       <c r="R29" t="n">
-        <v>6692768</v>
+        <v>6692607</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3624,7 +3624,7 @@
         <v>131860690</v>
       </c>
       <c r="B30" t="n">
-        <v>92501</v>
+        <v>92503</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
+          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3736,7 +3736,7 @@
         <v>131860689</v>
       </c>
       <c r="B31" t="n">
-        <v>92501</v>
+        <v>92503</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3838,17 +3838,17 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
+          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131860615</v>
+        <v>131860687</v>
       </c>
       <c r="B32" t="n">
-        <v>80283</v>
+        <v>5179</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3856,21 +3856,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6456</v>
+        <v>100526</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3880,10 +3880,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>669217</v>
+        <v>669223</v>
       </c>
       <c r="R32" t="n">
-        <v>6692612</v>
+        <v>6692603</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3929,17 +3929,17 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -3950,39 +3950,39 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
+          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131860662</v>
+        <v>131860615</v>
       </c>
       <c r="B33" t="n">
-        <v>79274</v>
+        <v>80285</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3992,10 +3992,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>669203</v>
+        <v>669217</v>
       </c>
       <c r="R33" t="n">
-        <v>6692759</v>
+        <v>6692612</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4041,17 +4041,17 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4069,32 +4069,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131860613</v>
+        <v>131860662</v>
       </c>
       <c r="B34" t="n">
-        <v>80283</v>
+        <v>79276</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>669232</v>
+        <v>669203</v>
       </c>
       <c r="R34" t="n">
-        <v>6692800</v>
+        <v>6692759</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4153,17 +4153,17 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4181,32 +4181,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131860661</v>
+        <v>131860613</v>
       </c>
       <c r="B35" t="n">
-        <v>79274</v>
+        <v>80285</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4216,10 +4216,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>669202</v>
+        <v>669232</v>
       </c>
       <c r="R35" t="n">
-        <v>6692764</v>
+        <v>6692800</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4265,17 +4265,17 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4293,32 +4293,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131860687</v>
+        <v>131860661</v>
       </c>
       <c r="B36" t="n">
-        <v>5179</v>
+        <v>79276</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4328,10 +4328,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>669223</v>
+        <v>669202</v>
       </c>
       <c r="R36" t="n">
-        <v>6692603</v>
+        <v>6692764</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4408,7 +4408,7 @@
         <v>131860698</v>
       </c>
       <c r="B37" t="n">
-        <v>101257</v>
+        <v>101260</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>131860593</v>
       </c>
       <c r="B38" t="n">
-        <v>91846</v>
+        <v>91848</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>131860607</v>
       </c>
       <c r="B39" t="n">
-        <v>96392</v>
+        <v>96394</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4696,10 +4696,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131860700</v>
+        <v>131860654</v>
       </c>
       <c r="B40" t="n">
-        <v>101257</v>
+        <v>4781</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4707,21 +4707,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4731,10 +4731,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>668963</v>
+        <v>669197</v>
       </c>
       <c r="R40" t="n">
-        <v>6692271</v>
+        <v>6692720</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4777,6 +4777,21 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4793,10 +4808,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131860699</v>
+        <v>131860655</v>
       </c>
       <c r="B41" t="n">
-        <v>101257</v>
+        <v>4781</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4804,21 +4819,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4828,10 +4843,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>668997</v>
+        <v>669222</v>
       </c>
       <c r="R41" t="n">
-        <v>6692214</v>
+        <v>6692642</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4874,6 +4889,21 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -4890,10 +4920,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131860654</v>
+        <v>131860700</v>
       </c>
       <c r="B42" t="n">
-        <v>4781</v>
+        <v>101260</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4901,21 +4931,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4925,10 +4955,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>669197</v>
+        <v>668963</v>
       </c>
       <c r="R42" t="n">
-        <v>6692720</v>
+        <v>6692271</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4971,21 +5001,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5002,10 +5017,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131860655</v>
+        <v>131860699</v>
       </c>
       <c r="B43" t="n">
-        <v>4781</v>
+        <v>101260</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5013,21 +5028,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5037,10 +5052,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>669222</v>
+        <v>668997</v>
       </c>
       <c r="R43" t="n">
-        <v>6692642</v>
+        <v>6692214</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5083,21 +5098,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5114,10 +5114,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131860652</v>
+        <v>131860648</v>
       </c>
       <c r="B44" t="n">
-        <v>96488</v>
+        <v>75382</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5125,21 +5125,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>210</v>
+        <v>6426</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5149,10 +5149,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>668992</v>
+        <v>669219</v>
       </c>
       <c r="R44" t="n">
-        <v>6692504</v>
+        <v>6692641</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5195,21 +5195,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5226,10 +5211,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131860648</v>
+        <v>131860620</v>
       </c>
       <c r="B45" t="n">
-        <v>75380</v>
+        <v>80285</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5237,21 +5222,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6426</v>
+        <v>6456</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5261,10 +5246,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>669219</v>
+        <v>669176</v>
       </c>
       <c r="R45" t="n">
-        <v>6692641</v>
+        <v>6692603</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5307,6 +5292,21 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5323,10 +5323,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131860620</v>
+        <v>131860639</v>
       </c>
       <c r="B46" t="n">
-        <v>80283</v>
+        <v>80341</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5334,21 +5334,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5358,10 +5358,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>669176</v>
+        <v>669215</v>
       </c>
       <c r="R46" t="n">
-        <v>6692603</v>
+        <v>6692608</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5438,7 +5438,7 @@
         <v>131860642</v>
       </c>
       <c r="B47" t="n">
-        <v>80339</v>
+        <v>80341</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5547,10 +5547,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131860639</v>
+        <v>131860652</v>
       </c>
       <c r="B48" t="n">
-        <v>80339</v>
+        <v>96490</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5558,21 +5558,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229497</v>
+        <v>210</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5582,10 +5582,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>669215</v>
+        <v>668992</v>
       </c>
       <c r="R48" t="n">
-        <v>6692608</v>
+        <v>6692504</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5631,17 +5631,17 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5659,10 +5659,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131860634</v>
+        <v>131860685</v>
       </c>
       <c r="B49" t="n">
-        <v>80339</v>
+        <v>80316</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5670,21 +5670,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229497</v>
+        <v>6457</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>669233</v>
+        <v>669242</v>
       </c>
       <c r="R49" t="n">
-        <v>6692806</v>
+        <v>6692625</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5764,17 +5764,17 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
+          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131860685</v>
+        <v>131860634</v>
       </c>
       <c r="B50" t="n">
-        <v>80314</v>
+        <v>80341</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5782,21 +5782,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6457</v>
+        <v>229497</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5806,10 +5806,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>669242</v>
+        <v>669233</v>
       </c>
       <c r="R50" t="n">
-        <v>6692625</v>
+        <v>6692806</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5886,7 +5886,7 @@
         <v>131860691</v>
       </c>
       <c r="B51" t="n">
-        <v>92501</v>
+        <v>92503</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
+          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -5998,7 +5998,7 @@
         <v>131860683</v>
       </c>
       <c r="B52" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
+          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6110,7 +6110,7 @@
         <v>131860651</v>
       </c>
       <c r="B53" t="n">
-        <v>96488</v>
+        <v>96490</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6219,10 +6219,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131860641</v>
+        <v>131860643</v>
       </c>
       <c r="B54" t="n">
-        <v>80339</v>
+        <v>80341</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6254,10 +6254,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>669218</v>
+        <v>669201</v>
       </c>
       <c r="R54" t="n">
-        <v>6692611</v>
+        <v>6692608</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6331,10 +6331,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131860643</v>
+        <v>131860641</v>
       </c>
       <c r="B55" t="n">
-        <v>80339</v>
+        <v>80341</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6366,10 +6366,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>669201</v>
+        <v>669218</v>
       </c>
       <c r="R55" t="n">
-        <v>6692608</v>
+        <v>6692611</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6446,7 +6446,7 @@
         <v>131860701</v>
       </c>
       <c r="B56" t="n">
-        <v>101257</v>
+        <v>101260</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6540,10 +6540,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132019922</v>
+        <v>132019904</v>
       </c>
       <c r="B57" t="n">
-        <v>101257</v>
+        <v>91269</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6551,21 +6551,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222498</v>
+        <v>4189</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Pers., nom.sanct</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6575,10 +6575,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>669218</v>
+        <v>669298</v>
       </c>
       <c r="R57" t="n">
-        <v>6692730</v>
+        <v>6692803</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6611,6 +6611,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Kalkrik granskog, under gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6637,10 +6642,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132019904</v>
+        <v>132019922</v>
       </c>
       <c r="B58" t="n">
-        <v>91267</v>
+        <v>101260</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6648,21 +6653,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4189</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6672,10 +6677,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>669298</v>
+        <v>669218</v>
       </c>
       <c r="R58" t="n">
-        <v>6692803</v>
+        <v>6692730</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6708,11 +6713,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Kalkrik granskog, under gran</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6844,7 +6844,7 @@
         <v>132019892</v>
       </c>
       <c r="B60" t="n">
-        <v>58071</v>
+        <v>58073</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>132019900</v>
       </c>
       <c r="B61" t="n">
-        <v>58284</v>
+        <v>58286</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
         <v>132019905</v>
       </c>
       <c r="B62" t="n">
-        <v>96488</v>
+        <v>96490</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
         <v>132019895</v>
       </c>
       <c r="B63" t="n">
-        <v>58071</v>
+        <v>58073</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>132019919</v>
       </c>
       <c r="B64" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7349,7 +7349,7 @@
         <v>132019889</v>
       </c>
       <c r="B65" t="n">
-        <v>91846</v>
+        <v>91848</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
         <v>132019897</v>
       </c>
       <c r="B66" t="n">
-        <v>80283</v>
+        <v>80285</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>132019920</v>
       </c>
       <c r="B67" t="n">
-        <v>101257</v>
+        <v>101260</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>132019888</v>
       </c>
       <c r="B68" t="n">
-        <v>91846</v>
+        <v>91848</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>132019903</v>
       </c>
       <c r="B69" t="n">
-        <v>75380</v>
+        <v>75382</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>132019898</v>
       </c>
       <c r="B70" t="n">
-        <v>80283</v>
+        <v>80285</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7976,7 +7976,7 @@
         <v>132019901</v>
       </c>
       <c r="B71" t="n">
-        <v>75380</v>
+        <v>75382</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>132019918</v>
       </c>
       <c r="B72" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8180,7 +8180,7 @@
         <v>132019887</v>
       </c>
       <c r="B73" t="n">
-        <v>91846</v>
+        <v>91848</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8292,7 +8292,7 @@
         <v>132019921</v>
       </c>
       <c r="B74" t="n">
-        <v>101257</v>
+        <v>101260</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8389,7 +8389,7 @@
         <v>132019896</v>
       </c>
       <c r="B75" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>132019899</v>
       </c>
       <c r="B76" t="n">
-        <v>80283</v>
+        <v>80285</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8593,7 +8593,7 @@
         <v>132019886</v>
       </c>
       <c r="B77" t="n">
-        <v>91846</v>
+        <v>91848</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         <v>132019908</v>
       </c>
       <c r="B79" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         <v>132019894</v>
       </c>
       <c r="B80" t="n">
-        <v>58071</v>
+        <v>58073</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>132019893</v>
       </c>
       <c r="B81" t="n">
-        <v>58071</v>
+        <v>58073</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131860656</v>
+        <v>131860695</v>
       </c>
       <c r="B8" t="n">
-        <v>4781</v>
+        <v>101260</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>669149</v>
+        <v>669270</v>
       </c>
       <c r="R8" t="n">
-        <v>6692521</v>
+        <v>6692768</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,21 +1389,6 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
@@ -1412,17 +1397,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
+          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131860695</v>
+        <v>131860656</v>
       </c>
       <c r="B9" t="n">
-        <v>101260</v>
+        <v>4781</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1430,21 +1415,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>669270</v>
+        <v>669149</v>
       </c>
       <c r="R9" t="n">
-        <v>6692768</v>
+        <v>6692521</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1501,6 +1486,21 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
+          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -3325,50 +3325,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131860609</v>
+        <v>131860690</v>
       </c>
       <c r="B27" t="n">
-        <v>57911</v>
+        <v>92503</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>669095</v>
+        <v>669205</v>
       </c>
       <c r="R27" t="n">
-        <v>6692372</v>
+        <v>6692610</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3412,6 +3407,21 @@
       <c r="AG27" t="b">
         <v>0</v>
       </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
@@ -3420,52 +3430,57 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
+          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131860694</v>
+        <v>131860609</v>
       </c>
       <c r="B28" t="n">
-        <v>101260</v>
+        <v>57911</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>669321</v>
+        <v>669095</v>
       </c>
       <c r="R28" t="n">
-        <v>6692768</v>
+        <v>6692372</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3517,14 +3532,14 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
+          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131860696</v>
+        <v>131860694</v>
       </c>
       <c r="B29" t="n">
         <v>101260</v>
@@ -3559,10 +3574,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>669141</v>
+        <v>669321</v>
       </c>
       <c r="R29" t="n">
-        <v>6692607</v>
+        <v>6692768</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3614,17 +3629,17 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
+          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131860690</v>
+        <v>131860696</v>
       </c>
       <c r="B30" t="n">
-        <v>92503</v>
+        <v>101260</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3632,21 +3647,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3656,10 +3671,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>669205</v>
+        <v>669141</v>
       </c>
       <c r="R30" t="n">
-        <v>6692610</v>
+        <v>6692607</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3703,21 +3718,6 @@
       <c r="AG30" t="b">
         <v>0</v>
       </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
@@ -3726,17 +3726,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
+          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131860689</v>
+        <v>131860615</v>
       </c>
       <c r="B31" t="n">
-        <v>92503</v>
+        <v>80285</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3744,21 +3744,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1339</v>
+        <v>6456</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>669316</v>
+        <v>669217</v>
       </c>
       <c r="R31" t="n">
-        <v>6692776</v>
+        <v>6692612</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3817,17 +3817,17 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -3838,39 +3838,39 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
+          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131860687</v>
+        <v>131860662</v>
       </c>
       <c r="B32" t="n">
-        <v>5179</v>
+        <v>79276</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3880,10 +3880,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>669223</v>
+        <v>669203</v>
       </c>
       <c r="R32" t="n">
-        <v>6692603</v>
+        <v>6692759</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3950,14 +3950,14 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
+          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131860615</v>
+        <v>131860613</v>
       </c>
       <c r="B33" t="n">
         <v>80285</v>
@@ -3992,10 +3992,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>669217</v>
+        <v>669232</v>
       </c>
       <c r="R33" t="n">
-        <v>6692612</v>
+        <v>6692800</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4069,7 +4069,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131860662</v>
+        <v>131860661</v>
       </c>
       <c r="B34" t="n">
         <v>79276</v>
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>669203</v>
+        <v>669202</v>
       </c>
       <c r="R34" t="n">
-        <v>6692759</v>
+        <v>6692764</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4181,10 +4181,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131860613</v>
+        <v>131860687</v>
       </c>
       <c r="B35" t="n">
-        <v>80285</v>
+        <v>5179</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4192,21 +4192,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6456</v>
+        <v>100526</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4216,10 +4216,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>669232</v>
+        <v>669223</v>
       </c>
       <c r="R35" t="n">
-        <v>6692800</v>
+        <v>6692603</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4265,17 +4265,17 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4286,39 +4286,39 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
+          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131860661</v>
+        <v>131860689</v>
       </c>
       <c r="B36" t="n">
-        <v>79276</v>
+        <v>92503</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1339</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4328,10 +4328,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>669202</v>
+        <v>669316</v>
       </c>
       <c r="R36" t="n">
-        <v>6692764</v>
+        <v>6692776</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
+          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -6739,45 +6739,50 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132019907</v>
+        <v>132019892</v>
       </c>
       <c r="B59" t="n">
-        <v>4781</v>
+        <v>58073</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>102306</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>669141</v>
+        <v>669331</v>
       </c>
       <c r="R59" t="n">
-        <v>6692648</v>
+        <v>6692814</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6820,11 +6825,6 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -6841,50 +6841,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132019892</v>
+        <v>132019907</v>
       </c>
       <c r="B60" t="n">
-        <v>58073</v>
+        <v>4781</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>102306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>669331</v>
+        <v>669141</v>
       </c>
       <c r="R60" t="n">
-        <v>6692814</v>
+        <v>6692648</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6927,6 +6922,11 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7142,50 +7142,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132019895</v>
+        <v>132019919</v>
       </c>
       <c r="B63" t="n">
-        <v>58073</v>
+        <v>80316</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>6457</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>669191</v>
+        <v>669113</v>
       </c>
       <c r="R63" t="n">
-        <v>6692693</v>
+        <v>6692721</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7228,6 +7223,11 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>Populas tremula</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -7244,45 +7244,50 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132019919</v>
+        <v>132019895</v>
       </c>
       <c r="B64" t="n">
-        <v>80316</v>
+        <v>58073</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6457</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>669113</v>
+        <v>669191</v>
       </c>
       <c r="R64" t="n">
-        <v>6692721</v>
+        <v>6692693</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7325,11 +7330,6 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>Populas tremula</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131860688</v>
+        <v>131860605</v>
       </c>
       <c r="B3" t="n">
-        <v>92503</v>
+        <v>96394</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1339</v>
+        <v>2818</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>669177</v>
+        <v>668988</v>
       </c>
       <c r="R3" t="n">
-        <v>6692736</v>
+        <v>6692259</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,21 +869,6 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -892,39 +877,39 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
+          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131860591</v>
+        <v>131860688</v>
       </c>
       <c r="B4" t="n">
-        <v>91848</v>
+        <v>92503</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>669198</v>
+        <v>669177</v>
       </c>
       <c r="R4" t="n">
-        <v>6692769</v>
+        <v>6692736</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -980,6 +965,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -996,32 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131860605</v>
+        <v>131860591</v>
       </c>
       <c r="B5" t="n">
-        <v>96394</v>
+        <v>91848</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2818</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668988</v>
+        <v>669198</v>
       </c>
       <c r="R5" t="n">
-        <v>6692259</v>
+        <v>6692769</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131860695</v>
+        <v>131860656</v>
       </c>
       <c r="B8" t="n">
-        <v>101260</v>
+        <v>4781</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>669270</v>
+        <v>669149</v>
       </c>
       <c r="R8" t="n">
-        <v>6692768</v>
+        <v>6692521</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,6 +1389,21 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
@@ -1397,17 +1412,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
+          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131860656</v>
+        <v>131860695</v>
       </c>
       <c r="B9" t="n">
-        <v>4781</v>
+        <v>101260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1415,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>669149</v>
+        <v>669270</v>
       </c>
       <c r="R9" t="n">
-        <v>6692521</v>
+        <v>6692768</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1485,21 +1500,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1613,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131860684</v>
+        <v>131860637</v>
       </c>
       <c r="B11" t="n">
-        <v>80316</v>
+        <v>80341</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1624,21 +1624,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6457</v>
+        <v>229497</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>669173</v>
+        <v>669335</v>
       </c>
       <c r="R11" t="n">
-        <v>6692783</v>
+        <v>6692778</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
+          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131860637</v>
+        <v>131860684</v>
       </c>
       <c r="B12" t="n">
-        <v>80341</v>
+        <v>80316</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1736,21 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229497</v>
+        <v>6457</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>669335</v>
+        <v>669173</v>
       </c>
       <c r="R12" t="n">
-        <v>6692778</v>
+        <v>6692783</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -2795,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131860618</v>
+        <v>131860635</v>
       </c>
       <c r="B22" t="n">
-        <v>80285</v>
+        <v>80341</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2806,21 +2806,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>669202</v>
+        <v>669236</v>
       </c>
       <c r="R22" t="n">
-        <v>6692608</v>
+        <v>6692814</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2907,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131860635</v>
+        <v>131860702</v>
       </c>
       <c r="B23" t="n">
-        <v>80341</v>
+        <v>101260</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2918,21 +2918,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>669236</v>
+        <v>669289</v>
       </c>
       <c r="R23" t="n">
-        <v>6692814</v>
+        <v>6692778</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2988,21 +2988,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3019,10 +3004,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131860702</v>
+        <v>131860618</v>
       </c>
       <c r="B24" t="n">
-        <v>101260</v>
+        <v>80285</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3030,21 +3015,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>6456</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3054,10 +3039,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>669289</v>
+        <v>669202</v>
       </c>
       <c r="R24" t="n">
-        <v>6692778</v>
+        <v>6692608</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3100,6 +3085,21 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3318,52 +3318,57 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
+          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131860690</v>
+        <v>131860609</v>
       </c>
       <c r="B27" t="n">
-        <v>92503</v>
+        <v>57911</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>669205</v>
+        <v>669095</v>
       </c>
       <c r="R27" t="n">
-        <v>6692610</v>
+        <v>6692372</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3407,21 +3412,6 @@
       <c r="AG27" t="b">
         <v>0</v>
       </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
@@ -3430,57 +3420,52 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
+          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131860609</v>
+        <v>131860690</v>
       </c>
       <c r="B28" t="n">
-        <v>57911</v>
+        <v>92503</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>669095</v>
+        <v>669205</v>
       </c>
       <c r="R28" t="n">
-        <v>6692372</v>
+        <v>6692610</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3523,6 +3508,21 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3539,7 +3539,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131860694</v>
+        <v>131860696</v>
       </c>
       <c r="B29" t="n">
         <v>101260</v>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>669321</v>
+        <v>669141</v>
       </c>
       <c r="R29" t="n">
-        <v>6692768</v>
+        <v>6692607</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3629,14 +3629,14 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
+          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131860696</v>
+        <v>131860694</v>
       </c>
       <c r="B30" t="n">
         <v>101260</v>
@@ -3671,10 +3671,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>669141</v>
+        <v>669321</v>
       </c>
       <c r="R30" t="n">
-        <v>6692607</v>
+        <v>6692768</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3733,10 +3733,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131860615</v>
+        <v>131860689</v>
       </c>
       <c r="B31" t="n">
-        <v>80285</v>
+        <v>92503</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3744,21 +3744,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6456</v>
+        <v>1339</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>669217</v>
+        <v>669316</v>
       </c>
       <c r="R31" t="n">
-        <v>6692612</v>
+        <v>6692776</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3817,17 +3817,17 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -3845,32 +3845,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131860662</v>
+        <v>131860615</v>
       </c>
       <c r="B32" t="n">
-        <v>79276</v>
+        <v>80285</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3880,10 +3880,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>669203</v>
+        <v>669217</v>
       </c>
       <c r="R32" t="n">
-        <v>6692759</v>
+        <v>6692612</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3929,17 +3929,17 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4069,32 +4069,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131860661</v>
+        <v>131860687</v>
       </c>
       <c r="B34" t="n">
-        <v>79276</v>
+        <v>5179</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>669202</v>
+        <v>669223</v>
       </c>
       <c r="R34" t="n">
-        <v>6692764</v>
+        <v>6692603</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4181,32 +4181,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131860687</v>
+        <v>131860662</v>
       </c>
       <c r="B35" t="n">
-        <v>5179</v>
+        <v>79276</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4216,10 +4216,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>669223</v>
+        <v>669203</v>
       </c>
       <c r="R35" t="n">
-        <v>6692603</v>
+        <v>6692759</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4286,39 +4286,39 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
+          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131860689</v>
+        <v>131860661</v>
       </c>
       <c r="B36" t="n">
-        <v>92503</v>
+        <v>79276</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1339</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4328,10 +4328,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>669316</v>
+        <v>669202</v>
       </c>
       <c r="R36" t="n">
-        <v>6692776</v>
+        <v>6692764</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
+          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4502,32 +4502,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131860593</v>
+        <v>131860607</v>
       </c>
       <c r="B38" t="n">
-        <v>91848</v>
+        <v>96394</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>2818</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4537,10 +4537,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>669198</v>
+        <v>668968</v>
       </c>
       <c r="R38" t="n">
-        <v>6692763</v>
+        <v>6692265</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4599,32 +4599,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131860607</v>
+        <v>131860593</v>
       </c>
       <c r="B39" t="n">
-        <v>96394</v>
+        <v>91848</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2818</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4634,10 +4634,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>668968</v>
+        <v>669198</v>
       </c>
       <c r="R39" t="n">
-        <v>6692265</v>
+        <v>6692763</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4696,7 +4696,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131860654</v>
+        <v>131860655</v>
       </c>
       <c r="B40" t="n">
         <v>4781</v>
@@ -4731,10 +4731,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>669197</v>
+        <v>669222</v>
       </c>
       <c r="R40" t="n">
-        <v>6692720</v>
+        <v>6692642</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4808,7 +4808,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131860655</v>
+        <v>131860654</v>
       </c>
       <c r="B41" t="n">
         <v>4781</v>
@@ -4843,10 +4843,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>669222</v>
+        <v>669197</v>
       </c>
       <c r="R41" t="n">
-        <v>6692642</v>
+        <v>6692720</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5114,10 +5114,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131860648</v>
+        <v>131860620</v>
       </c>
       <c r="B44" t="n">
-        <v>75382</v>
+        <v>80285</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5125,21 +5125,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6426</v>
+        <v>6456</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5149,10 +5149,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>669219</v>
+        <v>669176</v>
       </c>
       <c r="R44" t="n">
-        <v>6692641</v>
+        <v>6692603</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5195,6 +5195,21 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5211,10 +5226,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131860620</v>
+        <v>131860642</v>
       </c>
       <c r="B45" t="n">
-        <v>80285</v>
+        <v>80341</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5222,21 +5237,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5246,10 +5261,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>669176</v>
+        <v>669212</v>
       </c>
       <c r="R45" t="n">
-        <v>6692603</v>
+        <v>6692609</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5435,10 +5450,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131860642</v>
+        <v>131860648</v>
       </c>
       <c r="B47" t="n">
-        <v>80341</v>
+        <v>75382</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5446,21 +5461,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229497</v>
+        <v>6426</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5470,10 +5485,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>669212</v>
+        <v>669219</v>
       </c>
       <c r="R47" t="n">
-        <v>6692609</v>
+        <v>6692641</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5516,21 +5531,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5764,7 +5764,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
+          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5883,10 +5883,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131860691</v>
+        <v>131860683</v>
       </c>
       <c r="B51" t="n">
-        <v>92503</v>
+        <v>80316</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5894,21 +5894,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1339</v>
+        <v>6457</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5918,10 +5918,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>669198</v>
+        <v>669167</v>
       </c>
       <c r="R51" t="n">
-        <v>6692600</v>
+        <v>6692763</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5967,17 +5967,17 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -5988,17 +5988,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
+          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131860683</v>
+        <v>131860691</v>
       </c>
       <c r="B52" t="n">
-        <v>80316</v>
+        <v>92503</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6006,21 +6006,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6457</v>
+        <v>1339</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6030,10 +6030,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>669167</v>
+        <v>669198</v>
       </c>
       <c r="R52" t="n">
-        <v>6692763</v>
+        <v>6692600</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6079,17 +6079,17 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
+          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6219,7 +6219,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131860643</v>
+        <v>131860641</v>
       </c>
       <c r="B54" t="n">
         <v>80341</v>
@@ -6254,10 +6254,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>669201</v>
+        <v>669218</v>
       </c>
       <c r="R54" t="n">
-        <v>6692608</v>
+        <v>6692611</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6331,7 +6331,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131860641</v>
+        <v>131860643</v>
       </c>
       <c r="B55" t="n">
         <v>80341</v>
@@ -6366,10 +6366,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>669218</v>
+        <v>669201</v>
       </c>
       <c r="R55" t="n">
-        <v>6692611</v>
+        <v>6692608</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6540,10 +6540,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132019904</v>
+        <v>132019922</v>
       </c>
       <c r="B57" t="n">
-        <v>91269</v>
+        <v>101260</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6551,21 +6551,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4189</v>
+        <v>222498</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6575,10 +6575,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>669298</v>
+        <v>669218</v>
       </c>
       <c r="R57" t="n">
-        <v>6692803</v>
+        <v>6692730</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6611,11 +6611,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Kalkrik granskog, under gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6642,10 +6637,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132019922</v>
+        <v>132019904</v>
       </c>
       <c r="B58" t="n">
-        <v>101260</v>
+        <v>91269</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6653,21 +6648,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>4189</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Pers., nom.sanct</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6677,10 +6672,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>669218</v>
+        <v>669298</v>
       </c>
       <c r="R58" t="n">
-        <v>6692730</v>
+        <v>6692803</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6713,6 +6708,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Kalkrik granskog, under gran</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6739,50 +6739,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132019892</v>
+        <v>132019907</v>
       </c>
       <c r="B59" t="n">
-        <v>58073</v>
+        <v>4781</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>102306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>669331</v>
+        <v>669141</v>
       </c>
       <c r="R59" t="n">
-        <v>6692814</v>
+        <v>6692648</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6825,6 +6820,11 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -6841,45 +6841,50 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132019907</v>
+        <v>132019892</v>
       </c>
       <c r="B60" t="n">
-        <v>4781</v>
+        <v>58073</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>102306</v>
+        <v>103021</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>669141</v>
+        <v>669331</v>
       </c>
       <c r="R60" t="n">
-        <v>6692648</v>
+        <v>6692814</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6922,11 +6927,6 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AI60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7346,32 +7346,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132019889</v>
+        <v>132019920</v>
       </c>
       <c r="B65" t="n">
-        <v>91848</v>
+        <v>101260</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7381,10 +7381,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>669241</v>
+        <v>669116</v>
       </c>
       <c r="R65" t="n">
-        <v>6692784</v>
+        <v>6692739</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7427,21 +7427,6 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -7458,32 +7443,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132019897</v>
+        <v>132019889</v>
       </c>
       <c r="B66" t="n">
-        <v>80285</v>
+        <v>91848</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7493,10 +7478,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>669126</v>
+        <v>669241</v>
       </c>
       <c r="R66" t="n">
-        <v>6692721</v>
+        <v>6692784</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7540,9 +7525,19 @@
       <c r="AG66" t="b">
         <v>0</v>
       </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>Populas tremula</t>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -7560,10 +7555,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132019920</v>
+        <v>132019897</v>
       </c>
       <c r="B67" t="n">
-        <v>101260</v>
+        <v>80285</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7571,21 +7566,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>222498</v>
+        <v>6456</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7595,10 +7590,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>669116</v>
+        <v>669126</v>
       </c>
       <c r="R67" t="n">
-        <v>6692739</v>
+        <v>6692721</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7641,6 +7636,11 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>Populas tremula</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -8488,32 +8488,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132019899</v>
+        <v>132019886</v>
       </c>
       <c r="B76" t="n">
-        <v>80285</v>
+        <v>91848</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8523,10 +8523,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>669151</v>
+        <v>669131</v>
       </c>
       <c r="R76" t="n">
-        <v>6692676</v>
+        <v>6692781</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8570,9 +8570,19 @@
       <c r="AG76" t="b">
         <v>0</v>
       </c>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>Populas tremula</t>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -8590,32 +8600,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132019886</v>
+        <v>132019899</v>
       </c>
       <c r="B77" t="n">
-        <v>91848</v>
+        <v>80285</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8625,10 +8635,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>669131</v>
+        <v>669151</v>
       </c>
       <c r="R77" t="n">
-        <v>6692781</v>
+        <v>6692676</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8672,19 +8682,9 @@
       <c r="AG77" t="b">
         <v>0</v>
       </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>Populas tremula</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -8804,10 +8804,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132019908</v>
+        <v>132019894</v>
       </c>
       <c r="B79" t="n">
-        <v>79276</v>
+        <v>58073</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8815,34 +8815,39 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>669179</v>
+        <v>669208</v>
       </c>
       <c r="R79" t="n">
-        <v>6692672</v>
+        <v>6692665</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8885,11 +8890,6 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
-      </c>
-      <c r="AI79" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -8906,10 +8906,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132019894</v>
+        <v>132019908</v>
       </c>
       <c r="B80" t="n">
-        <v>58073</v>
+        <v>79276</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8917,39 +8917,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>669208</v>
+        <v>669179</v>
       </c>
       <c r="R80" t="n">
-        <v>6692665</v>
+        <v>6692672</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8992,6 +8987,11 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131860605</v>
+        <v>131860591</v>
       </c>
       <c r="B3" t="n">
-        <v>96394</v>
+        <v>91848</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2818</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>668988</v>
+        <v>669198</v>
       </c>
       <c r="R3" t="n">
-        <v>6692259</v>
+        <v>6692769</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131860688</v>
+        <v>131860605</v>
       </c>
       <c r="B4" t="n">
-        <v>92503</v>
+        <v>96394</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1339</v>
+        <v>2818</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>669177</v>
+        <v>668988</v>
       </c>
       <c r="R4" t="n">
-        <v>6692736</v>
+        <v>6692259</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -965,21 +965,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -996,32 +981,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131860591</v>
+        <v>131860688</v>
       </c>
       <c r="B5" t="n">
-        <v>91848</v>
+        <v>92503</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>669198</v>
+        <v>669177</v>
       </c>
       <c r="R5" t="n">
-        <v>6692769</v>
+        <v>6692736</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1077,6 +1062,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1516,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131860649</v>
+        <v>131860637</v>
       </c>
       <c r="B10" t="n">
-        <v>96490</v>
+        <v>80341</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1527,21 +1527,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>210</v>
+        <v>229497</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>669159</v>
+        <v>669335</v>
       </c>
       <c r="R10" t="n">
-        <v>6692588</v>
+        <v>6692778</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1597,6 +1597,21 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1613,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131860637</v>
+        <v>131860649</v>
       </c>
       <c r="B11" t="n">
-        <v>80341</v>
+        <v>96490</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1624,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229497</v>
+        <v>210</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>669335</v>
+        <v>669159</v>
       </c>
       <c r="R11" t="n">
-        <v>6692778</v>
+        <v>6692588</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1694,21 +1709,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1949,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131860614</v>
+        <v>131860697</v>
       </c>
       <c r="B14" t="n">
-        <v>80285</v>
+        <v>101260</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1960,21 +1960,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>669229</v>
+        <v>669157</v>
       </c>
       <c r="R14" t="n">
-        <v>6692600</v>
+        <v>6692556</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2030,21 +2030,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2061,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131860697</v>
+        <v>131860614</v>
       </c>
       <c r="B15" t="n">
-        <v>101260</v>
+        <v>80285</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2072,21 +2057,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2096,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>669157</v>
+        <v>669229</v>
       </c>
       <c r="R15" t="n">
-        <v>6692556</v>
+        <v>6692600</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2142,6 +2127,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2158,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131860616</v>
+        <v>131860603</v>
       </c>
       <c r="B16" t="n">
-        <v>80285</v>
+        <v>96394</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2169,21 +2169,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6456</v>
+        <v>2818</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>669151</v>
+        <v>669306</v>
       </c>
       <c r="R16" t="n">
-        <v>6692600</v>
+        <v>6692797</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2231,11 +2231,6 @@
           <t>2026-03-22</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2247,17 +2242,17 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2275,7 +2270,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131860603</v>
+        <v>131860604</v>
       </c>
       <c r="B17" t="n">
         <v>96394</v>
@@ -2304,16 +2299,20 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>669306</v>
+        <v>669204</v>
       </c>
       <c r="R17" t="n">
-        <v>6692797</v>
+        <v>6692601</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2354,22 +2353,23 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2387,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131860604</v>
+        <v>131860616</v>
       </c>
       <c r="B18" t="n">
-        <v>96394</v>
+        <v>80285</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2398,38 +2398,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2818</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>669204</v>
+        <v>669151</v>
       </c>
       <c r="R18" t="n">
-        <v>6692601</v>
+        <v>6692600</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2464,29 +2460,33 @@
           <t>2026-03-22</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2601,32 +2601,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131860589</v>
+        <v>131860618</v>
       </c>
       <c r="B20" t="n">
-        <v>91848</v>
+        <v>80285</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>669210</v>
+        <v>669202</v>
       </c>
       <c r="R20" t="n">
-        <v>6692779</v>
+        <v>6692608</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2682,6 +2682,21 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2698,32 +2713,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131860588</v>
+        <v>131860702</v>
       </c>
       <c r="B21" t="n">
-        <v>91848</v>
+        <v>101260</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2733,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>669143</v>
+        <v>669289</v>
       </c>
       <c r="R21" t="n">
-        <v>6692724</v>
+        <v>6692778</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2907,32 +2922,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131860702</v>
+        <v>131860589</v>
       </c>
       <c r="B23" t="n">
-        <v>101260</v>
+        <v>91848</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2942,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>669289</v>
+        <v>669210</v>
       </c>
       <c r="R23" t="n">
-        <v>6692778</v>
+        <v>6692779</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3004,32 +3019,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131860618</v>
+        <v>131860588</v>
       </c>
       <c r="B24" t="n">
-        <v>80285</v>
+        <v>91848</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3039,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>669202</v>
+        <v>669143</v>
       </c>
       <c r="R24" t="n">
-        <v>6692608</v>
+        <v>6692724</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3085,21 +3100,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3116,10 +3116,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131860617</v>
+        <v>131860692</v>
       </c>
       <c r="B25" t="n">
-        <v>80285</v>
+        <v>101260</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3127,21 +3127,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6456</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>669355</v>
+        <v>669245</v>
       </c>
       <c r="R25" t="n">
-        <v>6692827</v>
+        <v>6692828</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3197,21 +3197,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3228,10 +3213,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131860692</v>
+        <v>131860617</v>
       </c>
       <c r="B26" t="n">
-        <v>101260</v>
+        <v>80285</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3239,21 +3224,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>6456</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3263,10 +3248,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>669245</v>
+        <v>669355</v>
       </c>
       <c r="R26" t="n">
-        <v>6692828</v>
+        <v>6692827</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3309,6 +3294,21 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3325,50 +3325,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131860609</v>
+        <v>131860690</v>
       </c>
       <c r="B27" t="n">
-        <v>57911</v>
+        <v>92503</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>669095</v>
+        <v>669205</v>
       </c>
       <c r="R27" t="n">
-        <v>6692372</v>
+        <v>6692610</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3411,6 +3406,21 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3427,45 +3437,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131860690</v>
+        <v>131860609</v>
       </c>
       <c r="B28" t="n">
-        <v>92503</v>
+        <v>57911</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>669205</v>
+        <v>669095</v>
       </c>
       <c r="R28" t="n">
-        <v>6692610</v>
+        <v>6692372</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3508,21 +3523,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3845,32 +3845,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131860615</v>
+        <v>131860662</v>
       </c>
       <c r="B32" t="n">
-        <v>80285</v>
+        <v>79276</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3880,10 +3880,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>669217</v>
+        <v>669203</v>
       </c>
       <c r="R32" t="n">
-        <v>6692612</v>
+        <v>6692759</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3929,17 +3929,17 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -3957,32 +3957,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131860613</v>
+        <v>131860661</v>
       </c>
       <c r="B33" t="n">
-        <v>80285</v>
+        <v>79276</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3992,10 +3992,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>669232</v>
+        <v>669202</v>
       </c>
       <c r="R33" t="n">
-        <v>6692800</v>
+        <v>6692764</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4041,17 +4041,17 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4069,10 +4069,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131860687</v>
+        <v>131860615</v>
       </c>
       <c r="B34" t="n">
-        <v>5179</v>
+        <v>80285</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4080,21 +4080,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100526</v>
+        <v>6456</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>669223</v>
+        <v>669217</v>
       </c>
       <c r="R34" t="n">
-        <v>6692603</v>
+        <v>6692612</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4153,17 +4153,17 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4181,32 +4181,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131860662</v>
+        <v>131860613</v>
       </c>
       <c r="B35" t="n">
-        <v>79276</v>
+        <v>80285</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4216,10 +4216,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>669203</v>
+        <v>669232</v>
       </c>
       <c r="R35" t="n">
-        <v>6692759</v>
+        <v>6692800</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4265,17 +4265,17 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4293,32 +4293,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131860661</v>
+        <v>131860687</v>
       </c>
       <c r="B36" t="n">
-        <v>79276</v>
+        <v>5179</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4328,10 +4328,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>669202</v>
+        <v>669223</v>
       </c>
       <c r="R36" t="n">
-        <v>6692764</v>
+        <v>6692603</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4502,32 +4502,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131860607</v>
+        <v>131860593</v>
       </c>
       <c r="B38" t="n">
-        <v>96394</v>
+        <v>91848</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2818</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4537,10 +4537,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>668968</v>
+        <v>669198</v>
       </c>
       <c r="R38" t="n">
-        <v>6692265</v>
+        <v>6692763</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4599,32 +4599,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131860593</v>
+        <v>131860607</v>
       </c>
       <c r="B39" t="n">
-        <v>91848</v>
+        <v>96394</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>2818</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4634,10 +4634,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>669198</v>
+        <v>668968</v>
       </c>
       <c r="R39" t="n">
-        <v>6692763</v>
+        <v>6692265</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4696,10 +4696,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131860655</v>
+        <v>131860700</v>
       </c>
       <c r="B40" t="n">
-        <v>4781</v>
+        <v>101260</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4707,21 +4707,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4731,10 +4731,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>669222</v>
+        <v>668963</v>
       </c>
       <c r="R40" t="n">
-        <v>6692642</v>
+        <v>6692271</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4777,21 +4777,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4808,10 +4793,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131860654</v>
+        <v>131860699</v>
       </c>
       <c r="B41" t="n">
-        <v>4781</v>
+        <v>101260</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4819,21 +4804,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4843,10 +4828,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>669197</v>
+        <v>668997</v>
       </c>
       <c r="R41" t="n">
-        <v>6692720</v>
+        <v>6692214</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4889,21 +4874,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -4920,10 +4890,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131860700</v>
+        <v>131860655</v>
       </c>
       <c r="B42" t="n">
-        <v>101260</v>
+        <v>4781</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4931,21 +4901,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4955,10 +4925,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>668963</v>
+        <v>669222</v>
       </c>
       <c r="R42" t="n">
-        <v>6692271</v>
+        <v>6692642</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5001,6 +4971,21 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5017,10 +5002,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131860699</v>
+        <v>131860654</v>
       </c>
       <c r="B43" t="n">
-        <v>101260</v>
+        <v>4781</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5028,21 +5013,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5052,10 +5037,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>668997</v>
+        <v>669197</v>
       </c>
       <c r="R43" t="n">
-        <v>6692214</v>
+        <v>6692720</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5098,6 +5083,21 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5114,10 +5114,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131860620</v>
+        <v>131860652</v>
       </c>
       <c r="B44" t="n">
-        <v>80285</v>
+        <v>96490</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5125,21 +5125,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6456</v>
+        <v>210</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5149,10 +5149,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>669176</v>
+        <v>668992</v>
       </c>
       <c r="R44" t="n">
-        <v>6692603</v>
+        <v>6692504</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5198,17 +5198,17 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5226,10 +5226,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131860642</v>
+        <v>131860648</v>
       </c>
       <c r="B45" t="n">
-        <v>80341</v>
+        <v>75382</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5237,21 +5237,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229497</v>
+        <v>6426</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>669212</v>
+        <v>669219</v>
       </c>
       <c r="R45" t="n">
-        <v>6692609</v>
+        <v>6692641</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5307,21 +5307,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5338,10 +5323,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131860639</v>
+        <v>131860620</v>
       </c>
       <c r="B46" t="n">
-        <v>80341</v>
+        <v>80285</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5349,21 +5334,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5373,10 +5358,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>669215</v>
+        <v>669176</v>
       </c>
       <c r="R46" t="n">
-        <v>6692608</v>
+        <v>6692603</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5450,10 +5435,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131860648</v>
+        <v>131860639</v>
       </c>
       <c r="B47" t="n">
-        <v>75382</v>
+        <v>80341</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5461,21 +5446,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6426</v>
+        <v>229497</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5485,10 +5470,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>669219</v>
+        <v>669215</v>
       </c>
       <c r="R47" t="n">
-        <v>6692641</v>
+        <v>6692608</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5531,6 +5516,21 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5547,10 +5547,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131860652</v>
+        <v>131860642</v>
       </c>
       <c r="B48" t="n">
-        <v>96490</v>
+        <v>80341</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5558,21 +5558,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>210</v>
+        <v>229497</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5582,10 +5582,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>668992</v>
+        <v>669212</v>
       </c>
       <c r="R48" t="n">
-        <v>6692504</v>
+        <v>6692609</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5631,17 +5631,17 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5883,10 +5883,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131860683</v>
+        <v>131860691</v>
       </c>
       <c r="B51" t="n">
-        <v>80316</v>
+        <v>92503</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5894,21 +5894,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6457</v>
+        <v>1339</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5918,10 +5918,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>669167</v>
+        <v>669198</v>
       </c>
       <c r="R51" t="n">
-        <v>6692763</v>
+        <v>6692600</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5967,17 +5967,17 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -5995,10 +5995,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131860691</v>
+        <v>131860683</v>
       </c>
       <c r="B52" t="n">
-        <v>92503</v>
+        <v>80316</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6006,21 +6006,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1339</v>
+        <v>6457</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6030,10 +6030,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>669198</v>
+        <v>669167</v>
       </c>
       <c r="R52" t="n">
-        <v>6692600</v>
+        <v>6692763</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6079,17 +6079,17 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6107,10 +6107,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131860651</v>
+        <v>131860643</v>
       </c>
       <c r="B53" t="n">
-        <v>96490</v>
+        <v>80341</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6118,21 +6118,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>210</v>
+        <v>229497</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6142,10 +6142,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>669305</v>
+        <v>669201</v>
       </c>
       <c r="R53" t="n">
-        <v>6692798</v>
+        <v>6692608</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6191,17 +6191,17 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6331,10 +6331,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131860643</v>
+        <v>131860651</v>
       </c>
       <c r="B55" t="n">
-        <v>80341</v>
+        <v>96490</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6342,21 +6342,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>229497</v>
+        <v>210</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6366,10 +6366,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>669201</v>
+        <v>669305</v>
       </c>
       <c r="R55" t="n">
-        <v>6692608</v>
+        <v>6692798</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6415,17 +6415,17 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6540,10 +6540,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132019922</v>
+        <v>132019904</v>
       </c>
       <c r="B57" t="n">
-        <v>101260</v>
+        <v>91269</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6551,21 +6551,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222498</v>
+        <v>4189</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Pers., nom.sanct</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6575,10 +6575,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>669218</v>
+        <v>669298</v>
       </c>
       <c r="R57" t="n">
-        <v>6692730</v>
+        <v>6692803</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6611,6 +6611,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Kalkrik granskog, under gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6637,10 +6642,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132019904</v>
+        <v>132019922</v>
       </c>
       <c r="B58" t="n">
-        <v>91269</v>
+        <v>101260</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6648,21 +6653,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4189</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6672,10 +6677,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>669298</v>
+        <v>669218</v>
       </c>
       <c r="R58" t="n">
-        <v>6692803</v>
+        <v>6692730</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6708,11 +6713,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Kalkrik granskog, under gran</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6739,45 +6739,50 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132019907</v>
+        <v>132019892</v>
       </c>
       <c r="B59" t="n">
-        <v>4781</v>
+        <v>58073</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>102306</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>669141</v>
+        <v>669331</v>
       </c>
       <c r="R59" t="n">
-        <v>6692648</v>
+        <v>6692814</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6820,11 +6825,6 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -6841,50 +6841,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132019892</v>
+        <v>132019907</v>
       </c>
       <c r="B60" t="n">
-        <v>58073</v>
+        <v>4781</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>102306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>669331</v>
+        <v>669141</v>
       </c>
       <c r="R60" t="n">
-        <v>6692814</v>
+        <v>6692648</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6927,6 +6922,11 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7443,32 +7443,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132019889</v>
+        <v>132019897</v>
       </c>
       <c r="B66" t="n">
-        <v>91848</v>
+        <v>80285</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7478,10 +7478,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>669241</v>
+        <v>669126</v>
       </c>
       <c r="R66" t="n">
-        <v>6692784</v>
+        <v>6692721</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7525,19 +7525,9 @@
       <c r="AG66" t="b">
         <v>0</v>
       </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>Populas tremula</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -7555,32 +7545,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132019897</v>
+        <v>132019889</v>
       </c>
       <c r="B67" t="n">
-        <v>80285</v>
+        <v>91848</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7590,10 +7580,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>669126</v>
+        <v>669241</v>
       </c>
       <c r="R67" t="n">
-        <v>6692721</v>
+        <v>6692784</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7637,9 +7627,19 @@
       <c r="AG67" t="b">
         <v>0</v>
       </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>Populas tremula</t>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8804,10 +8804,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132019894</v>
+        <v>132019908</v>
       </c>
       <c r="B79" t="n">
-        <v>58073</v>
+        <v>79276</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8815,39 +8815,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>669208</v>
+        <v>669179</v>
       </c>
       <c r="R79" t="n">
-        <v>6692665</v>
+        <v>6692672</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8890,6 +8885,11 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -8906,10 +8906,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132019908</v>
+        <v>132019894</v>
       </c>
       <c r="B80" t="n">
-        <v>79276</v>
+        <v>58073</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8917,34 +8917,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>669179</v>
+        <v>669208</v>
       </c>
       <c r="R80" t="n">
-        <v>6692672</v>
+        <v>6692665</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8987,11 +8992,6 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AI80" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131860622</v>
+        <v>131860688</v>
       </c>
       <c r="B2" t="n">
-        <v>92308</v>
+        <v>92503</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>669211</v>
+        <v>669177</v>
       </c>
       <c r="R2" t="n">
-        <v>6692779</v>
+        <v>6692736</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131860591</v>
+        <v>131860622</v>
       </c>
       <c r="B3" t="n">
-        <v>91848</v>
+        <v>92308</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>669198</v>
+        <v>669211</v>
       </c>
       <c r="R3" t="n">
-        <v>6692769</v>
+        <v>6692779</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -868,6 +868,21 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -884,32 +899,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131860605</v>
+        <v>131860591</v>
       </c>
       <c r="B4" t="n">
-        <v>96394</v>
+        <v>91848</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2818</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668988</v>
+        <v>669198</v>
       </c>
       <c r="R4" t="n">
-        <v>6692259</v>
+        <v>6692769</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131860688</v>
+        <v>131860605</v>
       </c>
       <c r="B5" t="n">
-        <v>92503</v>
+        <v>96394</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1339</v>
+        <v>2818</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>669177</v>
+        <v>668988</v>
       </c>
       <c r="R5" t="n">
-        <v>6692736</v>
+        <v>6692259</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1062,21 +1077,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131860656</v>
+        <v>131860695</v>
       </c>
       <c r="B8" t="n">
-        <v>4781</v>
+        <v>101260</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>669149</v>
+        <v>669270</v>
       </c>
       <c r="R8" t="n">
-        <v>6692521</v>
+        <v>6692768</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1388,21 +1388,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1419,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131860695</v>
+        <v>131860656</v>
       </c>
       <c r="B9" t="n">
-        <v>101260</v>
+        <v>4781</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1430,21 +1415,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>669270</v>
+        <v>669149</v>
       </c>
       <c r="R9" t="n">
-        <v>6692768</v>
+        <v>6692521</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1500,6 +1485,21 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1949,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131860697</v>
+        <v>131860614</v>
       </c>
       <c r="B14" t="n">
-        <v>101260</v>
+        <v>80285</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1960,21 +1960,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>669157</v>
+        <v>669229</v>
       </c>
       <c r="R14" t="n">
-        <v>6692556</v>
+        <v>6692600</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2030,6 +2030,21 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2046,10 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131860614</v>
+        <v>131860697</v>
       </c>
       <c r="B15" t="n">
-        <v>80285</v>
+        <v>101260</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2057,21 +2072,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2081,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>669229</v>
+        <v>669157</v>
       </c>
       <c r="R15" t="n">
-        <v>6692600</v>
+        <v>6692556</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2127,21 +2142,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2601,32 +2601,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131860618</v>
+        <v>131860588</v>
       </c>
       <c r="B20" t="n">
-        <v>80285</v>
+        <v>91848</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>669202</v>
+        <v>669143</v>
       </c>
       <c r="R20" t="n">
-        <v>6692608</v>
+        <v>6692724</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2682,21 +2682,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2713,10 +2698,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131860702</v>
+        <v>131860618</v>
       </c>
       <c r="B21" t="n">
-        <v>101260</v>
+        <v>80285</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2724,21 +2709,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>6456</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2748,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>669289</v>
+        <v>669202</v>
       </c>
       <c r="R21" t="n">
-        <v>6692778</v>
+        <v>6692608</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2794,6 +2779,21 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2810,10 +2810,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131860635</v>
+        <v>131860702</v>
       </c>
       <c r="B22" t="n">
-        <v>80341</v>
+        <v>101260</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2821,21 +2821,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>669236</v>
+        <v>669289</v>
       </c>
       <c r="R22" t="n">
-        <v>6692814</v>
+        <v>6692778</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2891,21 +2891,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2922,32 +2907,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131860589</v>
+        <v>131860635</v>
       </c>
       <c r="B23" t="n">
-        <v>91848</v>
+        <v>80341</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2957,10 +2942,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>669210</v>
+        <v>669236</v>
       </c>
       <c r="R23" t="n">
-        <v>6692779</v>
+        <v>6692814</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3003,6 +2988,21 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3019,7 +3019,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131860588</v>
+        <v>131860589</v>
       </c>
       <c r="B24" t="n">
         <v>91848</v>
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>669143</v>
+        <v>669210</v>
       </c>
       <c r="R24" t="n">
-        <v>6692724</v>
+        <v>6692779</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3733,10 +3733,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131860689</v>
+        <v>131860615</v>
       </c>
       <c r="B31" t="n">
-        <v>92503</v>
+        <v>80285</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3744,21 +3744,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1339</v>
+        <v>6456</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>669316</v>
+        <v>669217</v>
       </c>
       <c r="R31" t="n">
-        <v>6692776</v>
+        <v>6692612</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3817,17 +3817,17 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -3845,32 +3845,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131860662</v>
+        <v>131860613</v>
       </c>
       <c r="B32" t="n">
-        <v>79276</v>
+        <v>80285</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3880,10 +3880,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>669203</v>
+        <v>669232</v>
       </c>
       <c r="R32" t="n">
-        <v>6692759</v>
+        <v>6692800</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3929,17 +3929,17 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -3957,32 +3957,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131860661</v>
+        <v>131860689</v>
       </c>
       <c r="B33" t="n">
-        <v>79276</v>
+        <v>92503</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1339</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3992,10 +3992,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>669202</v>
+        <v>669316</v>
       </c>
       <c r="R33" t="n">
-        <v>6692764</v>
+        <v>6692776</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4069,32 +4069,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131860615</v>
+        <v>131860662</v>
       </c>
       <c r="B34" t="n">
-        <v>80285</v>
+        <v>79276</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>669217</v>
+        <v>669203</v>
       </c>
       <c r="R34" t="n">
-        <v>6692612</v>
+        <v>6692759</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4153,17 +4153,17 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4181,32 +4181,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131860613</v>
+        <v>131860661</v>
       </c>
       <c r="B35" t="n">
-        <v>80285</v>
+        <v>79276</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4216,10 +4216,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>669232</v>
+        <v>669202</v>
       </c>
       <c r="R35" t="n">
-        <v>6692800</v>
+        <v>6692764</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4265,17 +4265,17 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4696,10 +4696,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131860700</v>
+        <v>131860654</v>
       </c>
       <c r="B40" t="n">
-        <v>101260</v>
+        <v>4781</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4707,21 +4707,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4731,10 +4731,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>668963</v>
+        <v>669197</v>
       </c>
       <c r="R40" t="n">
-        <v>6692271</v>
+        <v>6692720</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4777,6 +4777,21 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4793,7 +4808,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131860699</v>
+        <v>131860700</v>
       </c>
       <c r="B41" t="n">
         <v>101260</v>
@@ -4828,10 +4843,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>668997</v>
+        <v>668963</v>
       </c>
       <c r="R41" t="n">
-        <v>6692214</v>
+        <v>6692271</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4890,10 +4905,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131860655</v>
+        <v>131860699</v>
       </c>
       <c r="B42" t="n">
-        <v>4781</v>
+        <v>101260</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4901,21 +4916,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4925,10 +4940,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>669222</v>
+        <v>668997</v>
       </c>
       <c r="R42" t="n">
-        <v>6692642</v>
+        <v>6692214</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4971,21 +4986,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5002,7 +5002,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131860654</v>
+        <v>131860655</v>
       </c>
       <c r="B43" t="n">
         <v>4781</v>
@@ -5037,10 +5037,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>669197</v>
+        <v>669222</v>
       </c>
       <c r="R43" t="n">
-        <v>6692720</v>
+        <v>6692642</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -6739,50 +6739,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132019892</v>
+        <v>132019907</v>
       </c>
       <c r="B59" t="n">
-        <v>58073</v>
+        <v>4781</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>102306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>669331</v>
+        <v>669141</v>
       </c>
       <c r="R59" t="n">
-        <v>6692814</v>
+        <v>6692648</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6825,6 +6820,11 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -6841,45 +6841,50 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132019907</v>
+        <v>132019892</v>
       </c>
       <c r="B60" t="n">
-        <v>4781</v>
+        <v>58073</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>102306</v>
+        <v>103021</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>669141</v>
+        <v>669331</v>
       </c>
       <c r="R60" t="n">
-        <v>6692648</v>
+        <v>6692814</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6922,11 +6927,6 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AI60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131860688</v>
+        <v>131860622</v>
       </c>
       <c r="B2" t="n">
-        <v>92503</v>
+        <v>92308</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1339</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>669177</v>
+        <v>669211</v>
       </c>
       <c r="R2" t="n">
-        <v>6692736</v>
+        <v>6692779</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131860622</v>
+        <v>131860591</v>
       </c>
       <c r="B3" t="n">
-        <v>92308</v>
+        <v>91848</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>669211</v>
+        <v>669198</v>
       </c>
       <c r="R3" t="n">
-        <v>6692779</v>
+        <v>6692769</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -868,21 +868,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -899,32 +884,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131860591</v>
+        <v>131860605</v>
       </c>
       <c r="B4" t="n">
-        <v>91848</v>
+        <v>96394</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>2818</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>669198</v>
+        <v>668988</v>
       </c>
       <c r="R4" t="n">
-        <v>6692769</v>
+        <v>6692259</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -996,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131860605</v>
+        <v>131860688</v>
       </c>
       <c r="B5" t="n">
-        <v>96394</v>
+        <v>92503</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +992,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2818</v>
+        <v>1339</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668988</v>
+        <v>669177</v>
       </c>
       <c r="R5" t="n">
-        <v>6692259</v>
+        <v>6692736</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1077,6 +1062,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131860695</v>
+        <v>131860656</v>
       </c>
       <c r="B8" t="n">
-        <v>101260</v>
+        <v>4781</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>669270</v>
+        <v>669149</v>
       </c>
       <c r="R8" t="n">
-        <v>6692768</v>
+        <v>6692521</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1388,6 +1388,21 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1404,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131860656</v>
+        <v>131860695</v>
       </c>
       <c r="B9" t="n">
-        <v>4781</v>
+        <v>101260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1415,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>669149</v>
+        <v>669270</v>
       </c>
       <c r="R9" t="n">
-        <v>6692521</v>
+        <v>6692768</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1485,21 +1500,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1949,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131860614</v>
+        <v>131860697</v>
       </c>
       <c r="B14" t="n">
-        <v>80285</v>
+        <v>101260</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1960,21 +1960,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>669229</v>
+        <v>669157</v>
       </c>
       <c r="R14" t="n">
-        <v>6692600</v>
+        <v>6692556</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2030,21 +2030,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2061,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131860697</v>
+        <v>131860614</v>
       </c>
       <c r="B15" t="n">
-        <v>101260</v>
+        <v>80285</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2072,21 +2057,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2096,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>669157</v>
+        <v>669229</v>
       </c>
       <c r="R15" t="n">
-        <v>6692556</v>
+        <v>6692600</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2142,6 +2127,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2601,32 +2601,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131860588</v>
+        <v>131860618</v>
       </c>
       <c r="B20" t="n">
-        <v>91848</v>
+        <v>80285</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>669143</v>
+        <v>669202</v>
       </c>
       <c r="R20" t="n">
-        <v>6692724</v>
+        <v>6692608</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2682,6 +2682,21 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2698,10 +2713,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131860618</v>
+        <v>131860702</v>
       </c>
       <c r="B21" t="n">
-        <v>80285</v>
+        <v>101260</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2709,21 +2724,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6456</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2733,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>669202</v>
+        <v>669289</v>
       </c>
       <c r="R21" t="n">
-        <v>6692608</v>
+        <v>6692778</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2779,21 +2794,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2810,10 +2810,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131860702</v>
+        <v>131860635</v>
       </c>
       <c r="B22" t="n">
-        <v>101260</v>
+        <v>80341</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2821,21 +2821,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>229497</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>669289</v>
+        <v>669236</v>
       </c>
       <c r="R22" t="n">
-        <v>6692778</v>
+        <v>6692814</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2891,6 +2891,21 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2907,32 +2922,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131860635</v>
+        <v>131860589</v>
       </c>
       <c r="B23" t="n">
-        <v>80341</v>
+        <v>91848</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2942,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>669236</v>
+        <v>669210</v>
       </c>
       <c r="R23" t="n">
-        <v>6692814</v>
+        <v>6692779</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2988,21 +3003,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3019,7 +3019,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131860589</v>
+        <v>131860588</v>
       </c>
       <c r="B24" t="n">
         <v>91848</v>
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>669210</v>
+        <v>669143</v>
       </c>
       <c r="R24" t="n">
-        <v>6692779</v>
+        <v>6692724</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3116,10 +3116,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131860692</v>
+        <v>131860617</v>
       </c>
       <c r="B25" t="n">
-        <v>101260</v>
+        <v>80285</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3127,21 +3127,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>6456</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>669245</v>
+        <v>669355</v>
       </c>
       <c r="R25" t="n">
-        <v>6692828</v>
+        <v>6692827</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3197,6 +3197,21 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3213,10 +3228,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131860617</v>
+        <v>131860692</v>
       </c>
       <c r="B26" t="n">
-        <v>80285</v>
+        <v>101260</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3224,21 +3239,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6456</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3248,10 +3263,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>669355</v>
+        <v>669245</v>
       </c>
       <c r="R26" t="n">
-        <v>6692827</v>
+        <v>6692828</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3294,21 +3309,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3733,10 +3733,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131860615</v>
+        <v>131860689</v>
       </c>
       <c r="B31" t="n">
-        <v>80285</v>
+        <v>92503</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3744,21 +3744,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6456</v>
+        <v>1339</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>669217</v>
+        <v>669316</v>
       </c>
       <c r="R31" t="n">
-        <v>6692612</v>
+        <v>6692776</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3817,17 +3817,17 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -3845,32 +3845,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131860613</v>
+        <v>131860662</v>
       </c>
       <c r="B32" t="n">
-        <v>80285</v>
+        <v>79276</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3880,10 +3880,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>669232</v>
+        <v>669203</v>
       </c>
       <c r="R32" t="n">
-        <v>6692800</v>
+        <v>6692759</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3929,17 +3929,17 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -3957,32 +3957,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131860689</v>
+        <v>131860661</v>
       </c>
       <c r="B33" t="n">
-        <v>92503</v>
+        <v>79276</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1339</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3992,10 +3992,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>669316</v>
+        <v>669202</v>
       </c>
       <c r="R33" t="n">
-        <v>6692776</v>
+        <v>6692764</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4069,32 +4069,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131860662</v>
+        <v>131860615</v>
       </c>
       <c r="B34" t="n">
-        <v>79276</v>
+        <v>80285</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>669203</v>
+        <v>669217</v>
       </c>
       <c r="R34" t="n">
-        <v>6692759</v>
+        <v>6692612</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4153,17 +4153,17 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4181,32 +4181,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131860661</v>
+        <v>131860613</v>
       </c>
       <c r="B35" t="n">
-        <v>79276</v>
+        <v>80285</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4216,10 +4216,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>669202</v>
+        <v>669232</v>
       </c>
       <c r="R35" t="n">
-        <v>6692764</v>
+        <v>6692800</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4265,17 +4265,17 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4696,10 +4696,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131860654</v>
+        <v>131860700</v>
       </c>
       <c r="B40" t="n">
-        <v>4781</v>
+        <v>101260</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4707,21 +4707,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4731,10 +4731,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>669197</v>
+        <v>668963</v>
       </c>
       <c r="R40" t="n">
-        <v>6692720</v>
+        <v>6692271</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4777,21 +4777,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4808,7 +4793,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131860700</v>
+        <v>131860699</v>
       </c>
       <c r="B41" t="n">
         <v>101260</v>
@@ -4843,10 +4828,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>668963</v>
+        <v>668997</v>
       </c>
       <c r="R41" t="n">
-        <v>6692271</v>
+        <v>6692214</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4905,10 +4890,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131860699</v>
+        <v>131860655</v>
       </c>
       <c r="B42" t="n">
-        <v>101260</v>
+        <v>4781</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4916,21 +4901,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4940,10 +4925,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>668997</v>
+        <v>669222</v>
       </c>
       <c r="R42" t="n">
-        <v>6692214</v>
+        <v>6692642</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4986,6 +4971,21 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5002,7 +5002,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131860655</v>
+        <v>131860654</v>
       </c>
       <c r="B43" t="n">
         <v>4781</v>
@@ -5037,10 +5037,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>669222</v>
+        <v>669197</v>
       </c>
       <c r="R43" t="n">
-        <v>6692642</v>
+        <v>6692720</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131860591</v>
+        <v>131860688</v>
       </c>
       <c r="B3" t="n">
-        <v>91848</v>
+        <v>92503</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>669198</v>
+        <v>669177</v>
       </c>
       <c r="R3" t="n">
-        <v>6692769</v>
+        <v>6692736</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -868,6 +868,21 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -884,32 +899,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131860605</v>
+        <v>131860591</v>
       </c>
       <c r="B4" t="n">
-        <v>96394</v>
+        <v>91848</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2818</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668988</v>
+        <v>669198</v>
       </c>
       <c r="R4" t="n">
-        <v>6692259</v>
+        <v>6692769</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131860688</v>
+        <v>131860605</v>
       </c>
       <c r="B5" t="n">
-        <v>92503</v>
+        <v>96394</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1339</v>
+        <v>2818</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>669177</v>
+        <v>668988</v>
       </c>
       <c r="R5" t="n">
-        <v>6692736</v>
+        <v>6692259</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1062,21 +1077,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1516,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131860637</v>
+        <v>131860649</v>
       </c>
       <c r="B10" t="n">
-        <v>80341</v>
+        <v>96490</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1527,21 +1527,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229497</v>
+        <v>210</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>669335</v>
+        <v>669159</v>
       </c>
       <c r="R10" t="n">
-        <v>6692778</v>
+        <v>6692588</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1597,21 +1597,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1628,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131860649</v>
+        <v>131860684</v>
       </c>
       <c r="B11" t="n">
-        <v>96490</v>
+        <v>80316</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1639,21 +1624,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>210</v>
+        <v>6457</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>669159</v>
+        <v>669173</v>
       </c>
       <c r="R11" t="n">
-        <v>6692588</v>
+        <v>6692783</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1709,6 +1694,21 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1725,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131860684</v>
+        <v>131860637</v>
       </c>
       <c r="B12" t="n">
-        <v>80316</v>
+        <v>80341</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1736,21 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6457</v>
+        <v>229497</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>669173</v>
+        <v>669335</v>
       </c>
       <c r="R12" t="n">
-        <v>6692783</v>
+        <v>6692778</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -2601,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131860618</v>
+        <v>131860635</v>
       </c>
       <c r="B20" t="n">
-        <v>80285</v>
+        <v>80341</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2612,21 +2612,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>669202</v>
+        <v>669236</v>
       </c>
       <c r="R20" t="n">
-        <v>6692608</v>
+        <v>6692814</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2810,32 +2810,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131860635</v>
+        <v>131860589</v>
       </c>
       <c r="B22" t="n">
-        <v>80341</v>
+        <v>91848</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>669236</v>
+        <v>669210</v>
       </c>
       <c r="R22" t="n">
-        <v>6692814</v>
+        <v>6692779</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2891,21 +2891,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2922,7 +2907,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131860589</v>
+        <v>131860588</v>
       </c>
       <c r="B23" t="n">
         <v>91848</v>
@@ -2957,10 +2942,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>669210</v>
+        <v>669143</v>
       </c>
       <c r="R23" t="n">
-        <v>6692779</v>
+        <v>6692724</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3019,32 +3004,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131860588</v>
+        <v>131860618</v>
       </c>
       <c r="B24" t="n">
-        <v>91848</v>
+        <v>80285</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3054,10 +3039,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>669143</v>
+        <v>669202</v>
       </c>
       <c r="R24" t="n">
-        <v>6692724</v>
+        <v>6692608</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3100,6 +3085,21 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3845,32 +3845,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131860662</v>
+        <v>131860613</v>
       </c>
       <c r="B32" t="n">
-        <v>79276</v>
+        <v>80285</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3880,10 +3880,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>669203</v>
+        <v>669232</v>
       </c>
       <c r="R32" t="n">
-        <v>6692759</v>
+        <v>6692800</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3929,17 +3929,17 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -3957,7 +3957,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131860661</v>
+        <v>131860662</v>
       </c>
       <c r="B33" t="n">
         <v>79276</v>
@@ -3992,10 +3992,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>669202</v>
+        <v>669203</v>
       </c>
       <c r="R33" t="n">
-        <v>6692764</v>
+        <v>6692759</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4069,32 +4069,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131860615</v>
+        <v>131860661</v>
       </c>
       <c r="B34" t="n">
-        <v>80285</v>
+        <v>79276</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>669217</v>
+        <v>669202</v>
       </c>
       <c r="R34" t="n">
-        <v>6692612</v>
+        <v>6692764</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4153,17 +4153,17 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4181,7 +4181,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131860613</v>
+        <v>131860615</v>
       </c>
       <c r="B35" t="n">
         <v>80285</v>
@@ -4216,10 +4216,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>669232</v>
+        <v>669217</v>
       </c>
       <c r="R35" t="n">
-        <v>6692800</v>
+        <v>6692612</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4502,32 +4502,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131860593</v>
+        <v>131860607</v>
       </c>
       <c r="B38" t="n">
-        <v>91848</v>
+        <v>96394</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>2818</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4537,10 +4537,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>669198</v>
+        <v>668968</v>
       </c>
       <c r="R38" t="n">
-        <v>6692763</v>
+        <v>6692265</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4599,32 +4599,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131860607</v>
+        <v>131860593</v>
       </c>
       <c r="B39" t="n">
-        <v>96394</v>
+        <v>91848</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2818</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4634,10 +4634,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>668968</v>
+        <v>669198</v>
       </c>
       <c r="R39" t="n">
-        <v>6692265</v>
+        <v>6692763</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4696,10 +4696,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131860700</v>
+        <v>131860655</v>
       </c>
       <c r="B40" t="n">
-        <v>101260</v>
+        <v>4781</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4707,21 +4707,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4731,10 +4731,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>668963</v>
+        <v>669222</v>
       </c>
       <c r="R40" t="n">
-        <v>6692271</v>
+        <v>6692642</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4777,6 +4777,21 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4793,10 +4808,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131860699</v>
+        <v>131860654</v>
       </c>
       <c r="B41" t="n">
-        <v>101260</v>
+        <v>4781</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4804,21 +4819,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4828,10 +4843,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>668997</v>
+        <v>669197</v>
       </c>
       <c r="R41" t="n">
-        <v>6692214</v>
+        <v>6692720</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4874,6 +4889,21 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -4890,10 +4920,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131860655</v>
+        <v>131860700</v>
       </c>
       <c r="B42" t="n">
-        <v>4781</v>
+        <v>101260</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4901,21 +4931,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4925,10 +4955,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>669222</v>
+        <v>668963</v>
       </c>
       <c r="R42" t="n">
-        <v>6692642</v>
+        <v>6692271</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4971,21 +5001,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5002,10 +5017,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131860654</v>
+        <v>131860699</v>
       </c>
       <c r="B43" t="n">
-        <v>4781</v>
+        <v>101260</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5013,21 +5028,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5037,10 +5052,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>669197</v>
+        <v>668997</v>
       </c>
       <c r="R43" t="n">
-        <v>6692720</v>
+        <v>6692214</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5083,21 +5098,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5114,10 +5114,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131860652</v>
+        <v>131860642</v>
       </c>
       <c r="B44" t="n">
-        <v>96490</v>
+        <v>80341</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5125,21 +5125,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>210</v>
+        <v>229497</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5149,10 +5149,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>668992</v>
+        <v>669212</v>
       </c>
       <c r="R44" t="n">
-        <v>6692504</v>
+        <v>6692609</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5198,17 +5198,17 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5226,10 +5226,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131860648</v>
+        <v>131860639</v>
       </c>
       <c r="B45" t="n">
-        <v>75382</v>
+        <v>80341</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5237,21 +5237,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6426</v>
+        <v>229497</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>669219</v>
+        <v>669215</v>
       </c>
       <c r="R45" t="n">
-        <v>6692641</v>
+        <v>6692608</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5307,6 +5307,21 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5323,10 +5338,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131860620</v>
+        <v>131860648</v>
       </c>
       <c r="B46" t="n">
-        <v>80285</v>
+        <v>75382</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5334,21 +5349,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6456</v>
+        <v>6426</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5358,10 +5373,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>669176</v>
+        <v>669219</v>
       </c>
       <c r="R46" t="n">
-        <v>6692603</v>
+        <v>6692641</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5404,21 +5419,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5435,10 +5435,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131860639</v>
+        <v>131860620</v>
       </c>
       <c r="B47" t="n">
-        <v>80341</v>
+        <v>80285</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5446,21 +5446,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5470,10 +5470,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>669215</v>
+        <v>669176</v>
       </c>
       <c r="R47" t="n">
-        <v>6692608</v>
+        <v>6692603</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5547,10 +5547,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131860642</v>
+        <v>131860652</v>
       </c>
       <c r="B48" t="n">
-        <v>80341</v>
+        <v>96490</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5558,21 +5558,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229497</v>
+        <v>210</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5582,10 +5582,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>669212</v>
+        <v>668992</v>
       </c>
       <c r="R48" t="n">
-        <v>6692609</v>
+        <v>6692504</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5631,17 +5631,17 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5659,10 +5659,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131860685</v>
+        <v>131860634</v>
       </c>
       <c r="B49" t="n">
-        <v>80316</v>
+        <v>80341</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5670,21 +5670,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6457</v>
+        <v>229497</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>669242</v>
+        <v>669233</v>
       </c>
       <c r="R49" t="n">
-        <v>6692625</v>
+        <v>6692806</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5771,10 +5771,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131860634</v>
+        <v>131860685</v>
       </c>
       <c r="B50" t="n">
-        <v>80341</v>
+        <v>80316</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5782,21 +5782,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>229497</v>
+        <v>6457</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5806,10 +5806,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>669233</v>
+        <v>669242</v>
       </c>
       <c r="R50" t="n">
-        <v>6692806</v>
+        <v>6692625</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5883,10 +5883,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131860691</v>
+        <v>131860683</v>
       </c>
       <c r="B51" t="n">
-        <v>92503</v>
+        <v>80316</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5894,21 +5894,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1339</v>
+        <v>6457</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5918,10 +5918,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>669198</v>
+        <v>669167</v>
       </c>
       <c r="R51" t="n">
-        <v>6692600</v>
+        <v>6692763</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5967,17 +5967,17 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -5995,10 +5995,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131860683</v>
+        <v>131860691</v>
       </c>
       <c r="B52" t="n">
-        <v>80316</v>
+        <v>92503</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6006,21 +6006,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6457</v>
+        <v>1339</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6030,10 +6030,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>669167</v>
+        <v>669198</v>
       </c>
       <c r="R52" t="n">
-        <v>6692763</v>
+        <v>6692600</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6079,17 +6079,17 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6107,7 +6107,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131860643</v>
+        <v>131860641</v>
       </c>
       <c r="B53" t="n">
         <v>80341</v>
@@ -6142,10 +6142,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>669201</v>
+        <v>669218</v>
       </c>
       <c r="R53" t="n">
-        <v>6692608</v>
+        <v>6692611</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6219,7 +6219,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131860641</v>
+        <v>131860643</v>
       </c>
       <c r="B54" t="n">
         <v>80341</v>
@@ -6254,10 +6254,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>669218</v>
+        <v>669201</v>
       </c>
       <c r="R54" t="n">
-        <v>6692611</v>
+        <v>6692608</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -7142,45 +7142,50 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132019919</v>
+        <v>132019895</v>
       </c>
       <c r="B63" t="n">
-        <v>80316</v>
+        <v>58073</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6457</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>669113</v>
+        <v>669191</v>
       </c>
       <c r="R63" t="n">
-        <v>6692721</v>
+        <v>6692693</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7223,11 +7228,6 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>Populas tremula</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -7244,50 +7244,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132019895</v>
+        <v>132019919</v>
       </c>
       <c r="B64" t="n">
-        <v>58073</v>
+        <v>80316</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>6457</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>669191</v>
+        <v>669113</v>
       </c>
       <c r="R64" t="n">
-        <v>6692693</v>
+        <v>6692721</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7330,6 +7325,11 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>Populas tremula</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -7346,32 +7346,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132019920</v>
+        <v>132019889</v>
       </c>
       <c r="B65" t="n">
-        <v>101260</v>
+        <v>91848</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7381,10 +7381,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>669116</v>
+        <v>669241</v>
       </c>
       <c r="R65" t="n">
-        <v>6692739</v>
+        <v>6692784</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7427,6 +7427,21 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -7545,32 +7560,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132019889</v>
+        <v>132019920</v>
       </c>
       <c r="B67" t="n">
-        <v>91848</v>
+        <v>101260</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7580,10 +7595,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>669241</v>
+        <v>669116</v>
       </c>
       <c r="R67" t="n">
-        <v>6692784</v>
+        <v>6692739</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7626,21 +7641,6 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -8488,32 +8488,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132019886</v>
+        <v>132019899</v>
       </c>
       <c r="B76" t="n">
-        <v>91848</v>
+        <v>80285</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8523,10 +8523,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>669131</v>
+        <v>669151</v>
       </c>
       <c r="R76" t="n">
-        <v>6692781</v>
+        <v>6692676</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8570,19 +8570,9 @@
       <c r="AG76" t="b">
         <v>0</v>
       </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>Populas tremula</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -8600,32 +8590,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132019899</v>
+        <v>132019886</v>
       </c>
       <c r="B77" t="n">
-        <v>80285</v>
+        <v>91848</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8635,10 +8625,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>669151</v>
+        <v>669131</v>
       </c>
       <c r="R77" t="n">
-        <v>6692676</v>
+        <v>6692781</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8682,9 +8672,19 @@
       <c r="AG77" t="b">
         <v>0</v>
       </c>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>Populas tremula</t>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -8804,10 +8804,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132019908</v>
+        <v>132019894</v>
       </c>
       <c r="B79" t="n">
-        <v>79276</v>
+        <v>58073</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8815,34 +8815,39 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>669179</v>
+        <v>669208</v>
       </c>
       <c r="R79" t="n">
-        <v>6692672</v>
+        <v>6692665</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8885,11 +8890,6 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
-      </c>
-      <c r="AI79" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -8906,10 +8906,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132019894</v>
+        <v>132019908</v>
       </c>
       <c r="B80" t="n">
-        <v>58073</v>
+        <v>79276</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8917,39 +8917,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>669208</v>
+        <v>669179</v>
       </c>
       <c r="R80" t="n">
-        <v>6692665</v>
+        <v>6692672</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8992,6 +8987,11 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131860622</v>
       </c>
       <c r="B2" t="n">
-        <v>92308</v>
+        <v>92344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>131860688</v>
       </c>
       <c r="B3" t="n">
-        <v>92503</v>
+        <v>92539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>131860591</v>
       </c>
       <c r="B4" t="n">
-        <v>91848</v>
+        <v>91884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>131860605</v>
       </c>
       <c r="B5" t="n">
-        <v>96394</v>
+        <v>96430</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>131860608</v>
       </c>
       <c r="B6" t="n">
-        <v>57911</v>
+        <v>57945</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131860656</v>
+        <v>131860695</v>
       </c>
       <c r="B8" t="n">
-        <v>4781</v>
+        <v>101296</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>669149</v>
+        <v>669270</v>
       </c>
       <c r="R8" t="n">
-        <v>6692521</v>
+        <v>6692768</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1388,21 +1388,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1419,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131860695</v>
+        <v>131860656</v>
       </c>
       <c r="B9" t="n">
-        <v>101260</v>
+        <v>4781</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1430,21 +1415,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>669270</v>
+        <v>669149</v>
       </c>
       <c r="R9" t="n">
-        <v>6692768</v>
+        <v>6692521</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1500,6 +1485,21 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1519,7 +1519,7 @@
         <v>131860649</v>
       </c>
       <c r="B10" t="n">
-        <v>96490</v>
+        <v>96526</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131860684</v>
+        <v>131860637</v>
       </c>
       <c r="B11" t="n">
-        <v>80316</v>
+        <v>80375</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1624,21 +1624,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6457</v>
+        <v>229497</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>669173</v>
+        <v>669335</v>
       </c>
       <c r="R11" t="n">
-        <v>6692783</v>
+        <v>6692778</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1725,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131860637</v>
+        <v>131860684</v>
       </c>
       <c r="B12" t="n">
-        <v>80341</v>
+        <v>80350</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1736,21 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229497</v>
+        <v>6457</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>669335</v>
+        <v>669173</v>
       </c>
       <c r="R12" t="n">
-        <v>6692778</v>
+        <v>6692783</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1840,7 +1840,7 @@
         <v>131860660</v>
       </c>
       <c r="B13" t="n">
-        <v>79276</v>
+        <v>79310</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1949,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131860697</v>
+        <v>131860614</v>
       </c>
       <c r="B14" t="n">
-        <v>101260</v>
+        <v>80319</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1960,21 +1960,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>669157</v>
+        <v>669229</v>
       </c>
       <c r="R14" t="n">
-        <v>6692556</v>
+        <v>6692600</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2030,6 +2030,21 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2046,10 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131860614</v>
+        <v>131860697</v>
       </c>
       <c r="B15" t="n">
-        <v>80285</v>
+        <v>101296</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2057,21 +2072,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2081,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>669229</v>
+        <v>669157</v>
       </c>
       <c r="R15" t="n">
-        <v>6692600</v>
+        <v>6692556</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2127,21 +2142,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2158,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131860603</v>
+        <v>131860616</v>
       </c>
       <c r="B16" t="n">
-        <v>96394</v>
+        <v>80319</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2169,21 +2169,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2818</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>669306</v>
+        <v>669151</v>
       </c>
       <c r="R16" t="n">
-        <v>6692797</v>
+        <v>6692600</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2231,6 +2231,11 @@
           <t>2026-03-22</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2242,17 +2247,17 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2270,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131860604</v>
+        <v>131860603</v>
       </c>
       <c r="B17" t="n">
-        <v>96394</v>
+        <v>96430</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2299,20 +2304,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>669204</v>
+        <v>669306</v>
       </c>
       <c r="R17" t="n">
-        <v>6692601</v>
+        <v>6692797</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2353,23 +2354,22 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2387,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131860616</v>
+        <v>131860604</v>
       </c>
       <c r="B18" t="n">
-        <v>80285</v>
+        <v>96430</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2398,34 +2398,38 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6456</v>
+        <v>2818</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>669151</v>
+        <v>669204</v>
       </c>
       <c r="R18" t="n">
-        <v>6692600</v>
+        <v>6692601</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2460,33 +2464,29 @@
           <t>2026-03-22</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2507,7 +2507,7 @@
         <v>131860595</v>
       </c>
       <c r="B19" t="n">
-        <v>91848</v>
+        <v>91884</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>131860635</v>
       </c>
       <c r="B20" t="n">
-        <v>80341</v>
+        <v>80375</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>131860702</v>
       </c>
       <c r="B21" t="n">
-        <v>101260</v>
+        <v>101296</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>131860589</v>
       </c>
       <c r="B22" t="n">
-        <v>91848</v>
+        <v>91884</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>131860588</v>
       </c>
       <c r="B23" t="n">
-        <v>91848</v>
+        <v>91884</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         <v>131860618</v>
       </c>
       <c r="B24" t="n">
-        <v>80285</v>
+        <v>80319</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>131860617</v>
       </c>
       <c r="B25" t="n">
-        <v>80285</v>
+        <v>80319</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>131860692</v>
       </c>
       <c r="B26" t="n">
-        <v>101260</v>
+        <v>101296</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3325,10 +3325,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131860690</v>
+        <v>131860696</v>
       </c>
       <c r="B27" t="n">
-        <v>92503</v>
+        <v>101296</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3336,21 +3336,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3360,10 +3360,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>669205</v>
+        <v>669141</v>
       </c>
       <c r="R27" t="n">
-        <v>6692610</v>
+        <v>6692607</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3406,21 +3406,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3437,50 +3422,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131860609</v>
+        <v>131860694</v>
       </c>
       <c r="B28" t="n">
-        <v>57911</v>
+        <v>101296</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>669095</v>
+        <v>669321</v>
       </c>
       <c r="R28" t="n">
-        <v>6692372</v>
+        <v>6692768</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3539,45 +3519,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131860696</v>
+        <v>131860609</v>
       </c>
       <c r="B29" t="n">
-        <v>101260</v>
+        <v>57945</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>669141</v>
+        <v>669095</v>
       </c>
       <c r="R29" t="n">
-        <v>6692607</v>
+        <v>6692372</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3636,10 +3621,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131860694</v>
+        <v>131860690</v>
       </c>
       <c r="B30" t="n">
-        <v>101260</v>
+        <v>92539</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3647,21 +3632,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>1339</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3671,10 +3656,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>669321</v>
+        <v>669205</v>
       </c>
       <c r="R30" t="n">
-        <v>6692768</v>
+        <v>6692610</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3717,6 +3702,21 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3736,7 +3736,7 @@
         <v>131860689</v>
       </c>
       <c r="B31" t="n">
-        <v>92503</v>
+        <v>92539</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3845,32 +3845,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131860613</v>
+        <v>131860662</v>
       </c>
       <c r="B32" t="n">
-        <v>80285</v>
+        <v>79310</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3880,10 +3880,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>669232</v>
+        <v>669203</v>
       </c>
       <c r="R32" t="n">
-        <v>6692800</v>
+        <v>6692759</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3929,17 +3929,17 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -3957,10 +3957,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131860662</v>
+        <v>131860661</v>
       </c>
       <c r="B33" t="n">
-        <v>79276</v>
+        <v>79310</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3992,10 +3992,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>669203</v>
+        <v>669202</v>
       </c>
       <c r="R33" t="n">
-        <v>6692759</v>
+        <v>6692764</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4069,32 +4069,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131860661</v>
+        <v>131860687</v>
       </c>
       <c r="B34" t="n">
-        <v>79276</v>
+        <v>5179</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>669202</v>
+        <v>669223</v>
       </c>
       <c r="R34" t="n">
-        <v>6692764</v>
+        <v>6692603</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4181,10 +4181,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131860615</v>
+        <v>131860613</v>
       </c>
       <c r="B35" t="n">
-        <v>80285</v>
+        <v>80319</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4216,10 +4216,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>669217</v>
+        <v>669232</v>
       </c>
       <c r="R35" t="n">
-        <v>6692612</v>
+        <v>6692800</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4293,10 +4293,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131860687</v>
+        <v>131860615</v>
       </c>
       <c r="B36" t="n">
-        <v>5179</v>
+        <v>80319</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4304,21 +4304,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100526</v>
+        <v>6456</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4328,10 +4328,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>669223</v>
+        <v>669217</v>
       </c>
       <c r="R36" t="n">
-        <v>6692603</v>
+        <v>6692612</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4377,17 +4377,17 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4408,7 +4408,7 @@
         <v>131860698</v>
       </c>
       <c r="B37" t="n">
-        <v>101260</v>
+        <v>101296</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>131860607</v>
       </c>
       <c r="B38" t="n">
-        <v>96394</v>
+        <v>96430</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>131860593</v>
       </c>
       <c r="B39" t="n">
-        <v>91848</v>
+        <v>91884</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>131860700</v>
       </c>
       <c r="B42" t="n">
-        <v>101260</v>
+        <v>101296</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         <v>131860699</v>
       </c>
       <c r="B43" t="n">
-        <v>101260</v>
+        <v>101296</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5114,10 +5114,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131860642</v>
+        <v>131860648</v>
       </c>
       <c r="B44" t="n">
-        <v>80341</v>
+        <v>75416</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5125,21 +5125,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229497</v>
+        <v>6426</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5149,10 +5149,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>669212</v>
+        <v>669219</v>
       </c>
       <c r="R44" t="n">
-        <v>6692609</v>
+        <v>6692641</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5195,21 +5195,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5226,10 +5211,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131860639</v>
+        <v>131860620</v>
       </c>
       <c r="B45" t="n">
-        <v>80341</v>
+        <v>80319</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5237,21 +5222,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5261,10 +5246,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>669215</v>
+        <v>669176</v>
       </c>
       <c r="R45" t="n">
-        <v>6692608</v>
+        <v>6692603</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5338,10 +5323,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131860648</v>
+        <v>131860642</v>
       </c>
       <c r="B46" t="n">
-        <v>75382</v>
+        <v>80375</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5349,21 +5334,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6426</v>
+        <v>229497</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5373,10 +5358,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>669219</v>
+        <v>669212</v>
       </c>
       <c r="R46" t="n">
-        <v>6692641</v>
+        <v>6692609</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5419,6 +5404,21 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5435,10 +5435,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131860620</v>
+        <v>131860639</v>
       </c>
       <c r="B47" t="n">
-        <v>80285</v>
+        <v>80375</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5446,21 +5446,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5470,10 +5470,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>669176</v>
+        <v>669215</v>
       </c>
       <c r="R47" t="n">
-        <v>6692603</v>
+        <v>6692608</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5550,7 +5550,7 @@
         <v>131860652</v>
       </c>
       <c r="B48" t="n">
-        <v>96490</v>
+        <v>96526</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5659,10 +5659,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131860634</v>
+        <v>131860685</v>
       </c>
       <c r="B49" t="n">
-        <v>80341</v>
+        <v>80350</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5670,21 +5670,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229497</v>
+        <v>6457</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>669233</v>
+        <v>669242</v>
       </c>
       <c r="R49" t="n">
-        <v>6692806</v>
+        <v>6692625</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5771,10 +5771,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131860685</v>
+        <v>131860634</v>
       </c>
       <c r="B50" t="n">
-        <v>80316</v>
+        <v>80375</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5782,21 +5782,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6457</v>
+        <v>229497</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5806,10 +5806,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>669242</v>
+        <v>669233</v>
       </c>
       <c r="R50" t="n">
-        <v>6692625</v>
+        <v>6692806</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5883,10 +5883,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131860683</v>
+        <v>131860691</v>
       </c>
       <c r="B51" t="n">
-        <v>80316</v>
+        <v>92539</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5894,21 +5894,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6457</v>
+        <v>1339</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5918,10 +5918,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>669167</v>
+        <v>669198</v>
       </c>
       <c r="R51" t="n">
-        <v>6692763</v>
+        <v>6692600</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5967,17 +5967,17 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -5995,10 +5995,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131860691</v>
+        <v>131860683</v>
       </c>
       <c r="B52" t="n">
-        <v>92503</v>
+        <v>80350</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6006,21 +6006,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1339</v>
+        <v>6457</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6030,10 +6030,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>669198</v>
+        <v>669167</v>
       </c>
       <c r="R52" t="n">
-        <v>6692600</v>
+        <v>6692763</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6079,17 +6079,17 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6110,7 +6110,7 @@
         <v>131860641</v>
       </c>
       <c r="B53" t="n">
-        <v>80341</v>
+        <v>80375</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         <v>131860643</v>
       </c>
       <c r="B54" t="n">
-        <v>80341</v>
+        <v>80375</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>131860651</v>
       </c>
       <c r="B55" t="n">
-        <v>96490</v>
+        <v>96526</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>131860701</v>
       </c>
       <c r="B56" t="n">
-        <v>101260</v>
+        <v>101296</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6543,7 +6543,7 @@
         <v>132019904</v>
       </c>
       <c r="B57" t="n">
-        <v>91269</v>
+        <v>91305</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         <v>132019922</v>
       </c>
       <c r="B58" t="n">
-        <v>101260</v>
+        <v>101296</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>132019892</v>
       </c>
       <c r="B60" t="n">
-        <v>58073</v>
+        <v>58107</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>132019900</v>
       </c>
       <c r="B61" t="n">
-        <v>58286</v>
+        <v>58320</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
         <v>132019905</v>
       </c>
       <c r="B62" t="n">
-        <v>96490</v>
+        <v>96526</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7142,50 +7142,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132019895</v>
+        <v>132019919</v>
       </c>
       <c r="B63" t="n">
-        <v>58073</v>
+        <v>80350</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>6457</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>669191</v>
+        <v>669113</v>
       </c>
       <c r="R63" t="n">
-        <v>6692693</v>
+        <v>6692721</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7228,6 +7223,11 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>Populas tremula</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -7244,45 +7244,50 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132019919</v>
+        <v>132019895</v>
       </c>
       <c r="B64" t="n">
-        <v>80316</v>
+        <v>58107</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6457</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>669113</v>
+        <v>669191</v>
       </c>
       <c r="R64" t="n">
-        <v>6692721</v>
+        <v>6692693</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7325,11 +7330,6 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>Populas tremula</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -7346,32 +7346,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132019889</v>
+        <v>132019897</v>
       </c>
       <c r="B65" t="n">
-        <v>91848</v>
+        <v>80319</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7381,10 +7381,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>669241</v>
+        <v>669126</v>
       </c>
       <c r="R65" t="n">
-        <v>6692784</v>
+        <v>6692721</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7428,19 +7428,9 @@
       <c r="AG65" t="b">
         <v>0</v>
       </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>Populas tremula</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -7458,32 +7448,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132019897</v>
+        <v>132019889</v>
       </c>
       <c r="B66" t="n">
-        <v>80285</v>
+        <v>91884</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7493,10 +7483,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>669126</v>
+        <v>669241</v>
       </c>
       <c r="R66" t="n">
-        <v>6692721</v>
+        <v>6692784</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7540,9 +7530,19 @@
       <c r="AG66" t="b">
         <v>0</v>
       </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>Populas tremula</t>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -7563,7 +7563,7 @@
         <v>132019920</v>
       </c>
       <c r="B67" t="n">
-        <v>101260</v>
+        <v>101296</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>132019888</v>
       </c>
       <c r="B68" t="n">
-        <v>91848</v>
+        <v>91884</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>132019903</v>
       </c>
       <c r="B69" t="n">
-        <v>75382</v>
+        <v>75416</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>132019898</v>
       </c>
       <c r="B70" t="n">
-        <v>80285</v>
+        <v>80319</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7976,7 +7976,7 @@
         <v>132019901</v>
       </c>
       <c r="B71" t="n">
-        <v>75382</v>
+        <v>75416</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>132019918</v>
       </c>
       <c r="B72" t="n">
-        <v>80316</v>
+        <v>80350</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8177,32 +8177,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132019887</v>
+        <v>132019921</v>
       </c>
       <c r="B73" t="n">
-        <v>91848</v>
+        <v>101296</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8212,10 +8212,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>669285</v>
+        <v>669204</v>
       </c>
       <c r="R73" t="n">
-        <v>6692776</v>
+        <v>6692803</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8258,21 +8258,6 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -8289,32 +8274,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132019921</v>
+        <v>132019887</v>
       </c>
       <c r="B74" t="n">
-        <v>101260</v>
+        <v>91884</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8324,10 +8309,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>669204</v>
+        <v>669285</v>
       </c>
       <c r="R74" t="n">
-        <v>6692803</v>
+        <v>6692776</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8370,6 +8355,21 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -8389,7 +8389,7 @@
         <v>132019896</v>
       </c>
       <c r="B75" t="n">
-        <v>57911</v>
+        <v>57945</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>132019899</v>
       </c>
       <c r="B76" t="n">
-        <v>80285</v>
+        <v>80319</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8593,7 +8593,7 @@
         <v>132019886</v>
       </c>
       <c r="B77" t="n">
-        <v>91848</v>
+        <v>91884</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         <v>132019894</v>
       </c>
       <c r="B79" t="n">
-        <v>58073</v>
+        <v>58107</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         <v>132019908</v>
       </c>
       <c r="B80" t="n">
-        <v>79276</v>
+        <v>79310</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>132019893</v>
       </c>
       <c r="B81" t="n">
-        <v>58073</v>
+        <v>58107</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131860605</v>
       </c>
       <c r="B2" t="n">
-        <v>96435</v>
+        <v>96438</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
+          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -775,7 +775,7 @@
         <v>131860622</v>
       </c>
       <c r="B3" t="n">
-        <v>92349</v>
+        <v>92352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>131860688</v>
       </c>
       <c r="B4" t="n">
-        <v>92544</v>
+        <v>92547</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>131860591</v>
       </c>
       <c r="B5" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
+          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
+          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1422,7 +1422,7 @@
         <v>131860695</v>
       </c>
       <c r="B9" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,17 +1509,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
+          <t>Åsa Nordling, Ingemar Södergren, Tove Widén</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131860684</v>
+        <v>131860637</v>
       </c>
       <c r="B10" t="n">
-        <v>80355</v>
+        <v>80382</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1527,21 +1527,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6457</v>
+        <v>229497</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>669173</v>
+        <v>669335</v>
       </c>
       <c r="R10" t="n">
-        <v>6692783</v>
+        <v>6692778</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131860637</v>
+        <v>131860649</v>
       </c>
       <c r="B11" t="n">
-        <v>80380</v>
+        <v>96534</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1639,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229497</v>
+        <v>210</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>669335</v>
+        <v>669159</v>
       </c>
       <c r="R11" t="n">
-        <v>6692778</v>
+        <v>6692588</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1709,21 +1709,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1740,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131860649</v>
+        <v>131860684</v>
       </c>
       <c r="B12" t="n">
-        <v>96531</v>
+        <v>80357</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,21 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>210</v>
+        <v>6457</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>669159</v>
+        <v>669173</v>
       </c>
       <c r="R12" t="n">
-        <v>6692588</v>
+        <v>6692783</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1821,6 +1806,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1840,7 +1840,7 @@
         <v>131860660</v>
       </c>
       <c r="B13" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1949,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131860697</v>
+        <v>131860614</v>
       </c>
       <c r="B14" t="n">
-        <v>101301</v>
+        <v>80326</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1960,21 +1960,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>669157</v>
+        <v>669229</v>
       </c>
       <c r="R14" t="n">
-        <v>6692556</v>
+        <v>6692600</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2031,6 +2031,21 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
@@ -2039,17 +2054,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
+          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131860614</v>
+        <v>131860697</v>
       </c>
       <c r="B15" t="n">
-        <v>80324</v>
+        <v>101304</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2057,21 +2072,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2081,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>669229</v>
+        <v>669157</v>
       </c>
       <c r="R15" t="n">
-        <v>6692600</v>
+        <v>6692556</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2127,21 +2142,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2161,7 +2161,7 @@
         <v>131860616</v>
       </c>
       <c r="B16" t="n">
-        <v>80324</v>
+        <v>80326</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>131860603</v>
       </c>
       <c r="B17" t="n">
-        <v>96435</v>
+        <v>96438</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
+          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2390,7 +2390,7 @@
         <v>131860604</v>
       </c>
       <c r="B18" t="n">
-        <v>96435</v>
+        <v>96438</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
+          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2507,7 +2507,7 @@
         <v>131860595</v>
       </c>
       <c r="B19" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2594,39 +2594,39 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
+          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131860589</v>
+        <v>131860635</v>
       </c>
       <c r="B20" t="n">
-        <v>91889</v>
+        <v>80382</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>669210</v>
+        <v>669236</v>
       </c>
       <c r="R20" t="n">
-        <v>6692779</v>
+        <v>6692814</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2682,6 +2682,21 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2698,32 +2713,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131860588</v>
+        <v>131860702</v>
       </c>
       <c r="B21" t="n">
-        <v>91889</v>
+        <v>101304</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2733,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>669143</v>
+        <v>669289</v>
       </c>
       <c r="R21" t="n">
-        <v>6692724</v>
+        <v>6692778</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2795,32 +2810,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131860618</v>
+        <v>131860589</v>
       </c>
       <c r="B22" t="n">
-        <v>80324</v>
+        <v>91892</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2830,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>669202</v>
+        <v>669210</v>
       </c>
       <c r="R22" t="n">
-        <v>6692608</v>
+        <v>6692779</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2877,21 +2892,6 @@
       <c r="AG22" t="b">
         <v>0</v>
       </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
@@ -2900,39 +2900,39 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
+          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131860635</v>
+        <v>131860588</v>
       </c>
       <c r="B23" t="n">
-        <v>80380</v>
+        <v>91892</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>669236</v>
+        <v>669143</v>
       </c>
       <c r="R23" t="n">
-        <v>6692814</v>
+        <v>6692724</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2989,21 +2989,6 @@
       <c r="AG23" t="b">
         <v>0</v>
       </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
@@ -3012,17 +2997,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
+          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131860702</v>
+        <v>131860618</v>
       </c>
       <c r="B24" t="n">
-        <v>101301</v>
+        <v>80326</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3030,21 +3015,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>6456</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3054,10 +3039,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>669289</v>
+        <v>669202</v>
       </c>
       <c r="R24" t="n">
-        <v>6692778</v>
+        <v>6692608</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3100,6 +3085,21 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3119,7 +3119,7 @@
         <v>131860617</v>
       </c>
       <c r="B25" t="n">
-        <v>80324</v>
+        <v>80326</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>131860692</v>
       </c>
       <c r="B26" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3325,50 +3325,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131860609</v>
+        <v>131860690</v>
       </c>
       <c r="B27" t="n">
-        <v>57945</v>
+        <v>92547</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>669095</v>
+        <v>669205</v>
       </c>
       <c r="R27" t="n">
-        <v>6692372</v>
+        <v>6692610</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3411,6 +3406,21 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3427,10 +3437,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131860690</v>
+        <v>131860696</v>
       </c>
       <c r="B28" t="n">
-        <v>92544</v>
+        <v>101304</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3438,21 +3448,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3462,10 +3472,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>669205</v>
+        <v>669141</v>
       </c>
       <c r="R28" t="n">
-        <v>6692610</v>
+        <v>6692607</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3508,21 +3518,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3539,10 +3534,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131860696</v>
+        <v>131860694</v>
       </c>
       <c r="B29" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3574,10 +3569,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>669141</v>
+        <v>669321</v>
       </c>
       <c r="R29" t="n">
-        <v>6692607</v>
+        <v>6692768</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3636,45 +3631,50 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131860694</v>
+        <v>131860609</v>
       </c>
       <c r="B30" t="n">
-        <v>101301</v>
+        <v>57945</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>669321</v>
+        <v>669095</v>
       </c>
       <c r="R30" t="n">
-        <v>6692768</v>
+        <v>6692372</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
+          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3736,7 +3736,7 @@
         <v>131860615</v>
       </c>
       <c r="B31" t="n">
-        <v>80324</v>
+        <v>80326</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
+          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3848,7 +3848,7 @@
         <v>131860662</v>
       </c>
       <c r="B32" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>131860613</v>
       </c>
       <c r="B33" t="n">
-        <v>80324</v>
+        <v>80326</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
+          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4072,7 +4072,7 @@
         <v>131860661</v>
       </c>
       <c r="B34" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4181,10 +4181,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131860689</v>
+        <v>131860687</v>
       </c>
       <c r="B35" t="n">
-        <v>92544</v>
+        <v>5179</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4192,21 +4192,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1339</v>
+        <v>100526</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4216,10 +4216,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>669316</v>
+        <v>669223</v>
       </c>
       <c r="R35" t="n">
-        <v>6692776</v>
+        <v>6692603</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4293,10 +4293,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131860687</v>
+        <v>131860689</v>
       </c>
       <c r="B36" t="n">
-        <v>5179</v>
+        <v>92547</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4304,21 +4304,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100526</v>
+        <v>1339</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4328,10 +4328,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>669223</v>
+        <v>669316</v>
       </c>
       <c r="R36" t="n">
-        <v>6692603</v>
+        <v>6692776</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4408,7 +4408,7 @@
         <v>131860698</v>
       </c>
       <c r="B37" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>131860593</v>
       </c>
       <c r="B38" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Åsa Nordling, Ingemar Södergren, Tove Widén</t>
+          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4602,7 +4602,7 @@
         <v>131860607</v>
       </c>
       <c r="B39" t="n">
-        <v>96435</v>
+        <v>96438</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4689,17 +4689,17 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
+          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131860655</v>
+        <v>131860700</v>
       </c>
       <c r="B40" t="n">
-        <v>4781</v>
+        <v>101304</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4707,21 +4707,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4731,10 +4731,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>669222</v>
+        <v>668963</v>
       </c>
       <c r="R40" t="n">
-        <v>6692642</v>
+        <v>6692271</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4777,21 +4777,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4808,10 +4793,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131860654</v>
+        <v>131860699</v>
       </c>
       <c r="B41" t="n">
-        <v>4781</v>
+        <v>101304</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4819,21 +4804,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4843,10 +4828,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>669197</v>
+        <v>668997</v>
       </c>
       <c r="R41" t="n">
-        <v>6692720</v>
+        <v>6692214</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4889,21 +4874,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -4920,10 +4890,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131860700</v>
+        <v>131860655</v>
       </c>
       <c r="B42" t="n">
-        <v>101301</v>
+        <v>4781</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4931,21 +4901,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4955,10 +4925,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>668963</v>
+        <v>669222</v>
       </c>
       <c r="R42" t="n">
-        <v>6692271</v>
+        <v>6692642</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5001,6 +4971,21 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5017,10 +5002,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131860699</v>
+        <v>131860654</v>
       </c>
       <c r="B43" t="n">
-        <v>101301</v>
+        <v>4781</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5028,21 +5013,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5052,10 +5037,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>668997</v>
+        <v>669197</v>
       </c>
       <c r="R43" t="n">
-        <v>6692214</v>
+        <v>6692720</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5098,6 +5083,21 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5117,7 +5117,7 @@
         <v>131860642</v>
       </c>
       <c r="B44" t="n">
-        <v>80380</v>
+        <v>80382</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>131860639</v>
       </c>
       <c r="B45" t="n">
-        <v>80380</v>
+        <v>80382</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         <v>131860652</v>
       </c>
       <c r="B46" t="n">
-        <v>96531</v>
+        <v>96534</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5453,7 +5453,7 @@
         <v>131860648</v>
       </c>
       <c r="B47" t="n">
-        <v>75421</v>
+        <v>75423</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         <v>131860620</v>
       </c>
       <c r="B48" t="n">
-        <v>80324</v>
+        <v>80326</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>131860685</v>
       </c>
       <c r="B49" t="n">
-        <v>80355</v>
+        <v>80357</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>131860634</v>
       </c>
       <c r="B50" t="n">
-        <v>80380</v>
+        <v>80382</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131860683</v>
+        <v>131860691</v>
       </c>
       <c r="B51" t="n">
-        <v>80355</v>
+        <v>92547</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5894,21 +5894,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6457</v>
+        <v>1339</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5918,10 +5918,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>669167</v>
+        <v>669198</v>
       </c>
       <c r="R51" t="n">
-        <v>6692763</v>
+        <v>6692600</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5967,17 +5967,17 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -5995,10 +5995,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131860691</v>
+        <v>131860683</v>
       </c>
       <c r="B52" t="n">
-        <v>92544</v>
+        <v>80357</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6006,21 +6006,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1339</v>
+        <v>6457</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6030,10 +6030,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>669198</v>
+        <v>669167</v>
       </c>
       <c r="R52" t="n">
-        <v>6692600</v>
+        <v>6692763</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6079,17 +6079,17 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6107,10 +6107,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131860641</v>
+        <v>131860651</v>
       </c>
       <c r="B53" t="n">
-        <v>80380</v>
+        <v>96534</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6118,21 +6118,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229497</v>
+        <v>210</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6142,10 +6142,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>669218</v>
+        <v>669305</v>
       </c>
       <c r="R53" t="n">
-        <v>6692611</v>
+        <v>6692798</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6191,17 +6191,17 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6219,10 +6219,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131860643</v>
+        <v>131860641</v>
       </c>
       <c r="B54" t="n">
-        <v>80380</v>
+        <v>80382</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6254,10 +6254,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>669201</v>
+        <v>669218</v>
       </c>
       <c r="R54" t="n">
-        <v>6692608</v>
+        <v>6692611</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6331,10 +6331,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131860651</v>
+        <v>131860643</v>
       </c>
       <c r="B55" t="n">
-        <v>96531</v>
+        <v>80382</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6342,21 +6342,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>210</v>
+        <v>229497</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6366,10 +6366,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>669305</v>
+        <v>669201</v>
       </c>
       <c r="R55" t="n">
-        <v>6692798</v>
+        <v>6692608</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6415,17 +6415,17 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6446,7 +6446,7 @@
         <v>131860701</v>
       </c>
       <c r="B56" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6540,10 +6540,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132019922</v>
+        <v>132019904</v>
       </c>
       <c r="B57" t="n">
-        <v>101301</v>
+        <v>91313</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6551,21 +6551,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222498</v>
+        <v>4189</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Pers., nom.sanct</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6575,10 +6575,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>669218</v>
+        <v>669298</v>
       </c>
       <c r="R57" t="n">
-        <v>6692730</v>
+        <v>6692803</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6611,6 +6611,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Kalkrik granskog, under gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6637,10 +6642,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132019904</v>
+        <v>132019922</v>
       </c>
       <c r="B58" t="n">
-        <v>91310</v>
+        <v>101304</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6648,21 +6653,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4189</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6672,10 +6677,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>669298</v>
+        <v>669218</v>
       </c>
       <c r="R58" t="n">
-        <v>6692803</v>
+        <v>6692730</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6708,11 +6713,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Kalkrik granskog, under gran</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6844,7 +6844,7 @@
         <v>132019892</v>
       </c>
       <c r="B60" t="n">
-        <v>58107</v>
+        <v>58109</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>132019900</v>
       </c>
       <c r="B61" t="n">
-        <v>58320</v>
+        <v>58322</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
         <v>132019905</v>
       </c>
       <c r="B62" t="n">
-        <v>96531</v>
+        <v>96534</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7142,50 +7142,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132019895</v>
+        <v>132019919</v>
       </c>
       <c r="B63" t="n">
-        <v>58107</v>
+        <v>80357</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>6457</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>669191</v>
+        <v>669113</v>
       </c>
       <c r="R63" t="n">
-        <v>6692693</v>
+        <v>6692721</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7228,6 +7223,11 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>Populas tremula</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -7244,45 +7244,50 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132019919</v>
+        <v>132019895</v>
       </c>
       <c r="B64" t="n">
-        <v>80355</v>
+        <v>58109</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6457</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>669113</v>
+        <v>669191</v>
       </c>
       <c r="R64" t="n">
-        <v>6692721</v>
+        <v>6692693</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7325,11 +7330,6 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>Populas tremula</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -7346,32 +7346,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132019897</v>
+        <v>132019889</v>
       </c>
       <c r="B65" t="n">
-        <v>80324</v>
+        <v>91892</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7381,10 +7381,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>669126</v>
+        <v>669241</v>
       </c>
       <c r="R65" t="n">
-        <v>6692721</v>
+        <v>6692784</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7428,9 +7428,19 @@
       <c r="AG65" t="b">
         <v>0</v>
       </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>Populas tremula</t>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -7448,32 +7458,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132019889</v>
+        <v>132019897</v>
       </c>
       <c r="B66" t="n">
-        <v>91889</v>
+        <v>80326</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7483,10 +7493,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>669241</v>
+        <v>669126</v>
       </c>
       <c r="R66" t="n">
-        <v>6692784</v>
+        <v>6692721</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7530,19 +7540,9 @@
       <c r="AG66" t="b">
         <v>0</v>
       </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>Populas tremula</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -7563,7 +7563,7 @@
         <v>132019920</v>
       </c>
       <c r="B67" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7657,32 +7657,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132019903</v>
+        <v>132019888</v>
       </c>
       <c r="B68" t="n">
-        <v>75421</v>
+        <v>91892</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7692,10 +7692,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>669148</v>
+        <v>669198</v>
       </c>
       <c r="R68" t="n">
-        <v>6692645</v>
+        <v>6692759</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7739,9 +7739,19 @@
       <c r="AG68" t="b">
         <v>0</v>
       </c>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>Gran</t>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -7759,10 +7769,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132019898</v>
+        <v>132019903</v>
       </c>
       <c r="B69" t="n">
-        <v>80324</v>
+        <v>75423</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7770,21 +7780,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6456</v>
+        <v>6426</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7794,10 +7804,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>669154</v>
+        <v>669148</v>
       </c>
       <c r="R69" t="n">
-        <v>6692684</v>
+        <v>6692645</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7843,7 +7853,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Populas tremula</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -7861,10 +7871,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132019901</v>
+        <v>132019898</v>
       </c>
       <c r="B70" t="n">
-        <v>75421</v>
+        <v>80326</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7872,21 +7882,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6426</v>
+        <v>6456</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7896,7 +7906,7 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>669196</v>
+        <v>669154</v>
       </c>
       <c r="R70" t="n">
         <v>6692684</v>
@@ -7945,7 +7955,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>Populas tremula</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -7963,32 +7973,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132019888</v>
+        <v>132019901</v>
       </c>
       <c r="B71" t="n">
-        <v>91889</v>
+        <v>75423</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7998,10 +8008,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>669198</v>
+        <v>669196</v>
       </c>
       <c r="R71" t="n">
-        <v>6692759</v>
+        <v>6692684</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8045,19 +8055,9 @@
       <c r="AG71" t="b">
         <v>0</v>
       </c>
-      <c r="AJ71" t="inlineStr">
+      <c r="AI71" t="inlineStr">
         <is>
           <t>gran</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8078,7 +8078,7 @@
         <v>132019918</v>
       </c>
       <c r="B72" t="n">
-        <v>80355</v>
+        <v>80357</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8180,7 +8180,7 @@
         <v>132019887</v>
       </c>
       <c r="B73" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8292,7 +8292,7 @@
         <v>132019921</v>
       </c>
       <c r="B74" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>132019886</v>
       </c>
       <c r="B76" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         <v>132019899</v>
       </c>
       <c r="B77" t="n">
-        <v>80324</v>
+        <v>80326</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         <v>132019894</v>
       </c>
       <c r="B79" t="n">
-        <v>58107</v>
+        <v>58109</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         <v>132019908</v>
       </c>
       <c r="B80" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>132019893</v>
       </c>
       <c r="B81" t="n">
-        <v>58107</v>
+        <v>58109</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131860605</v>
+        <v>131860622</v>
       </c>
       <c r="B2" t="n">
-        <v>96438</v>
+        <v>92352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2818</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>668988</v>
+        <v>669211</v>
       </c>
       <c r="R2" t="n">
-        <v>6692259</v>
+        <v>6692779</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -757,6 +757,21 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -765,39 +780,39 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
+          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131860622</v>
+        <v>131860688</v>
       </c>
       <c r="B3" t="n">
-        <v>92352</v>
+        <v>92547</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>1339</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>669211</v>
+        <v>669177</v>
       </c>
       <c r="R3" t="n">
-        <v>6692779</v>
+        <v>6692736</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -884,32 +899,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131860688</v>
+        <v>131860591</v>
       </c>
       <c r="B4" t="n">
-        <v>92547</v>
+        <v>91892</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>669177</v>
+        <v>669198</v>
       </c>
       <c r="R4" t="n">
-        <v>6692736</v>
+        <v>6692769</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -966,21 +981,6 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
@@ -989,39 +989,39 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
+          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131860591</v>
+        <v>131860605</v>
       </c>
       <c r="B5" t="n">
-        <v>91892</v>
+        <v>96438</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>2818</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>669198</v>
+        <v>668988</v>
       </c>
       <c r="R5" t="n">
-        <v>6692769</v>
+        <v>6692259</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1516,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131860637</v>
+        <v>131860649</v>
       </c>
       <c r="B10" t="n">
-        <v>80382</v>
+        <v>96534</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1527,21 +1527,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229497</v>
+        <v>210</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>669335</v>
+        <v>669159</v>
       </c>
       <c r="R10" t="n">
-        <v>6692778</v>
+        <v>6692588</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1597,21 +1597,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1628,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131860649</v>
+        <v>131860684</v>
       </c>
       <c r="B11" t="n">
-        <v>96534</v>
+        <v>80357</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1639,21 +1624,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>210</v>
+        <v>6457</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>669159</v>
+        <v>669173</v>
       </c>
       <c r="R11" t="n">
-        <v>6692588</v>
+        <v>6692783</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1709,6 +1694,21 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1725,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131860684</v>
+        <v>131860637</v>
       </c>
       <c r="B12" t="n">
-        <v>80357</v>
+        <v>80382</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1736,21 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6457</v>
+        <v>229497</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>669173</v>
+        <v>669335</v>
       </c>
       <c r="R12" t="n">
-        <v>6692783</v>
+        <v>6692778</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -3116,10 +3116,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131860617</v>
+        <v>131860692</v>
       </c>
       <c r="B25" t="n">
-        <v>80326</v>
+        <v>101304</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3127,21 +3127,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6456</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>669355</v>
+        <v>669245</v>
       </c>
       <c r="R25" t="n">
-        <v>6692827</v>
+        <v>6692828</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3197,21 +3197,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3228,10 +3213,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131860692</v>
+        <v>131860617</v>
       </c>
       <c r="B26" t="n">
-        <v>101304</v>
+        <v>80326</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3239,21 +3224,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>6456</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3263,10 +3248,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>669245</v>
+        <v>669355</v>
       </c>
       <c r="R26" t="n">
-        <v>6692828</v>
+        <v>6692827</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3309,6 +3294,21 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3733,10 +3733,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131860615</v>
+        <v>131860689</v>
       </c>
       <c r="B31" t="n">
-        <v>80326</v>
+        <v>92547</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3744,21 +3744,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6456</v>
+        <v>1339</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>669217</v>
+        <v>669316</v>
       </c>
       <c r="R31" t="n">
-        <v>6692612</v>
+        <v>6692776</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3817,17 +3817,17 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -3838,39 +3838,39 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
+          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131860662</v>
+        <v>131860615</v>
       </c>
       <c r="B32" t="n">
-        <v>79317</v>
+        <v>80326</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3880,10 +3880,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>669203</v>
+        <v>669217</v>
       </c>
       <c r="R32" t="n">
-        <v>6692759</v>
+        <v>6692612</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3929,17 +3929,17 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -3950,39 +3950,39 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
+          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131860613</v>
+        <v>131860662</v>
       </c>
       <c r="B33" t="n">
-        <v>80326</v>
+        <v>79317</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3992,10 +3992,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>669232</v>
+        <v>669203</v>
       </c>
       <c r="R33" t="n">
-        <v>6692800</v>
+        <v>6692759</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4041,17 +4041,17 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4062,39 +4062,39 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
+          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131860661</v>
+        <v>131860613</v>
       </c>
       <c r="B34" t="n">
-        <v>79317</v>
+        <v>80326</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>669202</v>
+        <v>669232</v>
       </c>
       <c r="R34" t="n">
-        <v>6692764</v>
+        <v>6692800</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4153,17 +4153,17 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4174,39 +4174,39 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
+          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131860687</v>
+        <v>131860661</v>
       </c>
       <c r="B35" t="n">
-        <v>5179</v>
+        <v>79317</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4216,10 +4216,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>669223</v>
+        <v>669202</v>
       </c>
       <c r="R35" t="n">
-        <v>6692603</v>
+        <v>6692764</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4293,10 +4293,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131860689</v>
+        <v>131860687</v>
       </c>
       <c r="B36" t="n">
-        <v>92547</v>
+        <v>5179</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4304,21 +4304,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1339</v>
+        <v>100526</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4328,10 +4328,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>669316</v>
+        <v>669223</v>
       </c>
       <c r="R36" t="n">
-        <v>6692776</v>
+        <v>6692603</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4502,32 +4502,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131860593</v>
+        <v>131860607</v>
       </c>
       <c r="B38" t="n">
-        <v>91892</v>
+        <v>96438</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>2818</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4537,10 +4537,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>669198</v>
+        <v>668968</v>
       </c>
       <c r="R38" t="n">
-        <v>6692763</v>
+        <v>6692265</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4599,32 +4599,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131860607</v>
+        <v>131860593</v>
       </c>
       <c r="B39" t="n">
-        <v>96438</v>
+        <v>91892</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2818</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4634,10 +4634,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>668968</v>
+        <v>669198</v>
       </c>
       <c r="R39" t="n">
-        <v>6692265</v>
+        <v>6692763</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4696,10 +4696,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131860700</v>
+        <v>131860655</v>
       </c>
       <c r="B40" t="n">
-        <v>101304</v>
+        <v>4781</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4707,21 +4707,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4731,10 +4731,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>668963</v>
+        <v>669222</v>
       </c>
       <c r="R40" t="n">
-        <v>6692271</v>
+        <v>6692642</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4777,6 +4777,21 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4793,10 +4808,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131860699</v>
+        <v>131860654</v>
       </c>
       <c r="B41" t="n">
-        <v>101304</v>
+        <v>4781</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4804,21 +4819,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4828,10 +4843,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>668997</v>
+        <v>669197</v>
       </c>
       <c r="R41" t="n">
-        <v>6692214</v>
+        <v>6692720</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4874,6 +4889,21 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -4890,10 +4920,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131860655</v>
+        <v>131860700</v>
       </c>
       <c r="B42" t="n">
-        <v>4781</v>
+        <v>101304</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4901,21 +4931,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4925,10 +4955,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>669222</v>
+        <v>668963</v>
       </c>
       <c r="R42" t="n">
-        <v>6692642</v>
+        <v>6692271</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4971,21 +5001,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5002,10 +5017,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131860654</v>
+        <v>131860699</v>
       </c>
       <c r="B43" t="n">
-        <v>4781</v>
+        <v>101304</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5013,21 +5028,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5037,10 +5052,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>669197</v>
+        <v>668997</v>
       </c>
       <c r="R43" t="n">
-        <v>6692720</v>
+        <v>6692214</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5083,21 +5098,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5883,10 +5883,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131860691</v>
+        <v>131860683</v>
       </c>
       <c r="B51" t="n">
-        <v>92547</v>
+        <v>80357</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5894,21 +5894,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1339</v>
+        <v>6457</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5918,10 +5918,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>669198</v>
+        <v>669167</v>
       </c>
       <c r="R51" t="n">
-        <v>6692600</v>
+        <v>6692763</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5967,17 +5967,17 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -5995,10 +5995,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131860683</v>
+        <v>131860691</v>
       </c>
       <c r="B52" t="n">
-        <v>80357</v>
+        <v>92547</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6006,21 +6006,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6457</v>
+        <v>1339</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6030,10 +6030,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>669167</v>
+        <v>669198</v>
       </c>
       <c r="R52" t="n">
-        <v>6692763</v>
+        <v>6692600</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6079,17 +6079,17 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7346,32 +7346,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132019889</v>
+        <v>132019920</v>
       </c>
       <c r="B65" t="n">
-        <v>91892</v>
+        <v>101304</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7381,10 +7381,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>669241</v>
+        <v>669116</v>
       </c>
       <c r="R65" t="n">
-        <v>6692784</v>
+        <v>6692739</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7427,21 +7427,6 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -7458,32 +7443,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132019897</v>
+        <v>132019889</v>
       </c>
       <c r="B66" t="n">
-        <v>80326</v>
+        <v>91892</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7493,10 +7478,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>669126</v>
+        <v>669241</v>
       </c>
       <c r="R66" t="n">
-        <v>6692721</v>
+        <v>6692784</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7540,9 +7525,19 @@
       <c r="AG66" t="b">
         <v>0</v>
       </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>Populas tremula</t>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -7560,10 +7555,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132019920</v>
+        <v>132019897</v>
       </c>
       <c r="B67" t="n">
-        <v>101304</v>
+        <v>80326</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7571,21 +7566,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>222498</v>
+        <v>6456</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7595,10 +7590,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>669116</v>
+        <v>669126</v>
       </c>
       <c r="R67" t="n">
-        <v>6692739</v>
+        <v>6692721</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7641,6 +7636,11 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>Populas tremula</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -2601,32 +2601,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131860635</v>
+        <v>131860589</v>
       </c>
       <c r="B20" t="n">
-        <v>80382</v>
+        <v>91892</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>669236</v>
+        <v>669210</v>
       </c>
       <c r="R20" t="n">
-        <v>6692814</v>
+        <v>6692779</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2683,21 +2683,6 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
@@ -2706,39 +2691,39 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
+          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131860702</v>
+        <v>131860588</v>
       </c>
       <c r="B21" t="n">
-        <v>101304</v>
+        <v>91892</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2748,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>669289</v>
+        <v>669143</v>
       </c>
       <c r="R21" t="n">
-        <v>6692778</v>
+        <v>6692724</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2803,39 +2788,39 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
+          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131860589</v>
+        <v>131860618</v>
       </c>
       <c r="B22" t="n">
-        <v>91892</v>
+        <v>80326</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2845,10 +2830,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>669210</v>
+        <v>669202</v>
       </c>
       <c r="R22" t="n">
-        <v>6692779</v>
+        <v>6692608</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2892,6 +2877,21 @@
       <c r="AG22" t="b">
         <v>0</v>
       </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
@@ -2900,39 +2900,39 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
+          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131860588</v>
+        <v>131860635</v>
       </c>
       <c r="B23" t="n">
-        <v>91892</v>
+        <v>80382</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>669143</v>
+        <v>669236</v>
       </c>
       <c r="R23" t="n">
-        <v>6692724</v>
+        <v>6692814</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2989,6 +2989,21 @@
       <c r="AG23" t="b">
         <v>0</v>
       </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
@@ -2997,17 +3012,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
+          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131860618</v>
+        <v>131860702</v>
       </c>
       <c r="B24" t="n">
-        <v>80326</v>
+        <v>101304</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3015,21 +3030,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6456</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3039,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>669202</v>
+        <v>669289</v>
       </c>
       <c r="R24" t="n">
-        <v>6692608</v>
+        <v>6692778</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3085,21 +3100,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3733,10 +3733,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131860689</v>
+        <v>131860615</v>
       </c>
       <c r="B31" t="n">
-        <v>92547</v>
+        <v>80326</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3744,21 +3744,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1339</v>
+        <v>6456</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>669316</v>
+        <v>669217</v>
       </c>
       <c r="R31" t="n">
-        <v>6692776</v>
+        <v>6692612</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3817,17 +3817,17 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -3838,39 +3838,39 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
+          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131860615</v>
+        <v>131860662</v>
       </c>
       <c r="B32" t="n">
-        <v>80326</v>
+        <v>79317</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3880,10 +3880,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>669217</v>
+        <v>669203</v>
       </c>
       <c r="R32" t="n">
-        <v>6692612</v>
+        <v>6692759</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3929,17 +3929,17 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -3950,39 +3950,39 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
+          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131860662</v>
+        <v>131860613</v>
       </c>
       <c r="B33" t="n">
-        <v>79317</v>
+        <v>80326</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3992,10 +3992,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>669203</v>
+        <v>669232</v>
       </c>
       <c r="R33" t="n">
-        <v>6692759</v>
+        <v>6692800</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4041,17 +4041,17 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4062,39 +4062,39 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
+          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131860613</v>
+        <v>131860661</v>
       </c>
       <c r="B34" t="n">
-        <v>80326</v>
+        <v>79317</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>669232</v>
+        <v>669202</v>
       </c>
       <c r="R34" t="n">
-        <v>6692800</v>
+        <v>6692764</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4153,17 +4153,17 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4174,39 +4174,39 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
+          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131860661</v>
+        <v>131860687</v>
       </c>
       <c r="B35" t="n">
-        <v>79317</v>
+        <v>5179</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4216,10 +4216,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>669202</v>
+        <v>669223</v>
       </c>
       <c r="R35" t="n">
-        <v>6692764</v>
+        <v>6692603</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4293,10 +4293,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131860687</v>
+        <v>131860689</v>
       </c>
       <c r="B36" t="n">
-        <v>5179</v>
+        <v>92547</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4304,21 +4304,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100526</v>
+        <v>1339</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4328,10 +4328,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>669223</v>
+        <v>669316</v>
       </c>
       <c r="R36" t="n">
-        <v>6692603</v>
+        <v>6692776</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -5114,10 +5114,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131860642</v>
+        <v>131860652</v>
       </c>
       <c r="B44" t="n">
-        <v>80382</v>
+        <v>96534</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5125,21 +5125,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229497</v>
+        <v>210</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5149,10 +5149,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>669212</v>
+        <v>668992</v>
       </c>
       <c r="R44" t="n">
-        <v>6692609</v>
+        <v>6692504</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5198,17 +5198,17 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5226,10 +5226,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131860639</v>
+        <v>131860648</v>
       </c>
       <c r="B45" t="n">
-        <v>80382</v>
+        <v>75423</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5237,21 +5237,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229497</v>
+        <v>6426</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>669215</v>
+        <v>669219</v>
       </c>
       <c r="R45" t="n">
-        <v>6692608</v>
+        <v>6692641</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5307,21 +5307,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5338,10 +5323,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131860652</v>
+        <v>131860620</v>
       </c>
       <c r="B46" t="n">
-        <v>96534</v>
+        <v>80326</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5349,21 +5334,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>210</v>
+        <v>6456</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5373,10 +5358,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>668992</v>
+        <v>669176</v>
       </c>
       <c r="R46" t="n">
-        <v>6692504</v>
+        <v>6692603</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5422,17 +5407,17 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5450,10 +5435,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131860648</v>
+        <v>131860642</v>
       </c>
       <c r="B47" t="n">
-        <v>75423</v>
+        <v>80382</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5461,21 +5446,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6426</v>
+        <v>229497</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5485,10 +5470,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>669219</v>
+        <v>669212</v>
       </c>
       <c r="R47" t="n">
-        <v>6692641</v>
+        <v>6692609</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5531,6 +5516,21 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5547,10 +5547,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131860620</v>
+        <v>131860639</v>
       </c>
       <c r="B48" t="n">
-        <v>80326</v>
+        <v>80382</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5558,21 +5558,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5582,10 +5582,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>669176</v>
+        <v>669215</v>
       </c>
       <c r="R48" t="n">
-        <v>6692603</v>
+        <v>6692608</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -7142,45 +7142,50 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132019919</v>
+        <v>132019895</v>
       </c>
       <c r="B63" t="n">
-        <v>80357</v>
+        <v>58109</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6457</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>669113</v>
+        <v>669191</v>
       </c>
       <c r="R63" t="n">
-        <v>6692721</v>
+        <v>6692693</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7223,11 +7228,6 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>Populas tremula</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -7244,50 +7244,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132019895</v>
+        <v>132019919</v>
       </c>
       <c r="B64" t="n">
-        <v>58109</v>
+        <v>80357</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>6457</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>669191</v>
+        <v>669113</v>
       </c>
       <c r="R64" t="n">
-        <v>6692693</v>
+        <v>6692721</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7330,6 +7325,11 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>Populas tremula</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -8804,10 +8804,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132019894</v>
+        <v>132019908</v>
       </c>
       <c r="B79" t="n">
-        <v>58109</v>
+        <v>79317</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8815,39 +8815,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>669208</v>
+        <v>669179</v>
       </c>
       <c r="R79" t="n">
-        <v>6692665</v>
+        <v>6692672</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8890,6 +8885,11 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -8906,10 +8906,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132019908</v>
+        <v>132019894</v>
       </c>
       <c r="B80" t="n">
-        <v>79317</v>
+        <v>58109</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8917,34 +8917,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>669179</v>
+        <v>669208</v>
       </c>
       <c r="R80" t="n">
-        <v>6692672</v>
+        <v>6692665</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8987,11 +8992,6 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AI80" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131860622</v>
+        <v>131860605</v>
       </c>
       <c r="B2" t="n">
-        <v>92352</v>
+        <v>96438</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>2818</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>669211</v>
+        <v>668988</v>
       </c>
       <c r="R2" t="n">
-        <v>6692779</v>
+        <v>6692259</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -756,21 +756,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -787,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131860688</v>
+        <v>131860622</v>
       </c>
       <c r="B3" t="n">
-        <v>92547</v>
+        <v>92352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1339</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>669177</v>
+        <v>669211</v>
       </c>
       <c r="R3" t="n">
-        <v>6692736</v>
+        <v>6692779</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -899,32 +884,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131860591</v>
+        <v>131860688</v>
       </c>
       <c r="B4" t="n">
-        <v>91892</v>
+        <v>92547</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>669198</v>
+        <v>669177</v>
       </c>
       <c r="R4" t="n">
-        <v>6692769</v>
+        <v>6692736</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,6 +966,21 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
@@ -989,39 +989,39 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
+          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131860605</v>
+        <v>131860591</v>
       </c>
       <c r="B5" t="n">
-        <v>96438</v>
+        <v>91892</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2818</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668988</v>
+        <v>669198</v>
       </c>
       <c r="R5" t="n">
-        <v>6692259</v>
+        <v>6692769</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1086,39 +1086,39 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
+          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131860653</v>
+        <v>131860608</v>
       </c>
       <c r="B6" t="n">
-        <v>4781</v>
+        <v>57945</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>669179</v>
+        <v>669103</v>
       </c>
       <c r="R6" t="n">
-        <v>6692717</v>
+        <v>6692390</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1166,6 +1166,11 @@
           <t>2026-03-22</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Flög in i skogen och satte sig ett träd.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1174,21 +1179,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1205,32 +1195,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131860608</v>
+        <v>131860653</v>
       </c>
       <c r="B7" t="n">
-        <v>57945</v>
+        <v>4781</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>669103</v>
+        <v>669179</v>
       </c>
       <c r="R7" t="n">
-        <v>6692390</v>
+        <v>6692717</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1278,11 +1268,6 @@
           <t>2026-03-22</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Flög in i skogen och satte sig ett träd.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1291,6 +1276,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
+          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Åsa Nordling, Ingemar Södergren, Tove Widén</t>
+          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1613,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131860684</v>
+        <v>131860637</v>
       </c>
       <c r="B11" t="n">
-        <v>80357</v>
+        <v>80382</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1624,21 +1624,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6457</v>
+        <v>229497</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>669173</v>
+        <v>669335</v>
       </c>
       <c r="R11" t="n">
-        <v>6692783</v>
+        <v>6692778</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1725,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131860637</v>
+        <v>131860684</v>
       </c>
       <c r="B12" t="n">
-        <v>80382</v>
+        <v>80357</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1736,21 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229497</v>
+        <v>6457</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>669335</v>
+        <v>669173</v>
       </c>
       <c r="R12" t="n">
-        <v>6692778</v>
+        <v>6692783</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
+          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
+          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
+          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2594,39 +2594,39 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
+          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131860589</v>
+        <v>131860618</v>
       </c>
       <c r="B20" t="n">
-        <v>91892</v>
+        <v>80326</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>669210</v>
+        <v>669202</v>
       </c>
       <c r="R20" t="n">
-        <v>6692779</v>
+        <v>6692608</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2683,6 +2683,21 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
@@ -2691,14 +2706,14 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
+          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131860588</v>
+        <v>131860589</v>
       </c>
       <c r="B21" t="n">
         <v>91892</v>
@@ -2733,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>669143</v>
+        <v>669210</v>
       </c>
       <c r="R21" t="n">
-        <v>6692724</v>
+        <v>6692779</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2788,39 +2803,39 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
+          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131860618</v>
+        <v>131860588</v>
       </c>
       <c r="B22" t="n">
-        <v>80326</v>
+        <v>91892</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2830,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>669202</v>
+        <v>669143</v>
       </c>
       <c r="R22" t="n">
-        <v>6692608</v>
+        <v>6692724</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2876,21 +2891,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3437,45 +3437,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131860696</v>
+        <v>131860609</v>
       </c>
       <c r="B28" t="n">
-        <v>101304</v>
+        <v>57945</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>669141</v>
+        <v>669095</v>
       </c>
       <c r="R28" t="n">
-        <v>6692607</v>
+        <v>6692372</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3534,7 +3539,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131860694</v>
+        <v>131860696</v>
       </c>
       <c r="B29" t="n">
         <v>101304</v>
@@ -3569,10 +3574,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>669321</v>
+        <v>669141</v>
       </c>
       <c r="R29" t="n">
-        <v>6692768</v>
+        <v>6692607</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3631,50 +3636,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131860609</v>
+        <v>131860694</v>
       </c>
       <c r="B30" t="n">
-        <v>57945</v>
+        <v>101304</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>669095</v>
+        <v>669321</v>
       </c>
       <c r="R30" t="n">
-        <v>6692372</v>
+        <v>6692768</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
+          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
+          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
+          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4181,10 +4181,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131860687</v>
+        <v>131860689</v>
       </c>
       <c r="B35" t="n">
-        <v>5179</v>
+        <v>92547</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4192,21 +4192,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100526</v>
+        <v>1339</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4216,10 +4216,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>669223</v>
+        <v>669316</v>
       </c>
       <c r="R35" t="n">
-        <v>6692603</v>
+        <v>6692776</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4293,10 +4293,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131860689</v>
+        <v>131860687</v>
       </c>
       <c r="B36" t="n">
-        <v>92547</v>
+        <v>5179</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4304,21 +4304,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1339</v>
+        <v>100526</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4328,10 +4328,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>669316</v>
+        <v>669223</v>
       </c>
       <c r="R36" t="n">
-        <v>6692776</v>
+        <v>6692603</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4502,32 +4502,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131860607</v>
+        <v>131860593</v>
       </c>
       <c r="B38" t="n">
-        <v>96438</v>
+        <v>91892</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2818</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4537,10 +4537,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>668968</v>
+        <v>669198</v>
       </c>
       <c r="R38" t="n">
-        <v>6692265</v>
+        <v>6692763</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4592,39 +4592,39 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
+          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131860593</v>
+        <v>131860607</v>
       </c>
       <c r="B39" t="n">
-        <v>91892</v>
+        <v>96438</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>2818</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4634,10 +4634,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>669198</v>
+        <v>668968</v>
       </c>
       <c r="R39" t="n">
-        <v>6692763</v>
+        <v>6692265</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Åsa Nordling, Tove Widén, Ingemar Södergren</t>
+          <t>Ingemar Södergren, Tove Widén, Åsa Nordling</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5226,10 +5226,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131860648</v>
+        <v>131860642</v>
       </c>
       <c r="B45" t="n">
-        <v>75423</v>
+        <v>80382</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5237,21 +5237,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6426</v>
+        <v>229497</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>669219</v>
+        <v>669212</v>
       </c>
       <c r="R45" t="n">
-        <v>6692641</v>
+        <v>6692609</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5307,6 +5307,21 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5323,10 +5338,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131860620</v>
+        <v>131860639</v>
       </c>
       <c r="B46" t="n">
-        <v>80326</v>
+        <v>80382</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5334,21 +5349,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5358,10 +5373,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>669176</v>
+        <v>669215</v>
       </c>
       <c r="R46" t="n">
-        <v>6692603</v>
+        <v>6692608</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5435,10 +5450,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131860642</v>
+        <v>131860648</v>
       </c>
       <c r="B47" t="n">
-        <v>80382</v>
+        <v>75423</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5446,21 +5461,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229497</v>
+        <v>6426</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5470,10 +5485,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>669212</v>
+        <v>669219</v>
       </c>
       <c r="R47" t="n">
-        <v>6692609</v>
+        <v>6692641</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5516,21 +5531,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5547,10 +5547,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131860639</v>
+        <v>131860620</v>
       </c>
       <c r="B48" t="n">
-        <v>80382</v>
+        <v>80326</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5558,21 +5558,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5582,10 +5582,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>669215</v>
+        <v>669176</v>
       </c>
       <c r="R48" t="n">
-        <v>6692608</v>
+        <v>6692603</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5883,10 +5883,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131860683</v>
+        <v>131860691</v>
       </c>
       <c r="B51" t="n">
-        <v>80357</v>
+        <v>92547</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5894,21 +5894,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6457</v>
+        <v>1339</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5918,10 +5918,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>669167</v>
+        <v>669198</v>
       </c>
       <c r="R51" t="n">
-        <v>6692763</v>
+        <v>6692600</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5967,17 +5967,17 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -5995,10 +5995,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131860691</v>
+        <v>131860683</v>
       </c>
       <c r="B52" t="n">
-        <v>92547</v>
+        <v>80357</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6006,21 +6006,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1339</v>
+        <v>6457</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6030,10 +6030,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>669198</v>
+        <v>669167</v>
       </c>
       <c r="R52" t="n">
-        <v>6692600</v>
+        <v>6692763</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6079,17 +6079,17 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6540,10 +6540,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132019904</v>
+        <v>132019922</v>
       </c>
       <c r="B57" t="n">
-        <v>91313</v>
+        <v>101304</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6551,21 +6551,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4189</v>
+        <v>222498</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6575,10 +6575,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>669298</v>
+        <v>669218</v>
       </c>
       <c r="R57" t="n">
-        <v>6692803</v>
+        <v>6692730</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6611,11 +6611,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Kalkrik granskog, under gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6642,10 +6637,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132019922</v>
+        <v>132019904</v>
       </c>
       <c r="B58" t="n">
-        <v>101304</v>
+        <v>91313</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6653,21 +6648,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>4189</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Pers., nom.sanct</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6677,10 +6672,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>669218</v>
+        <v>669298</v>
       </c>
       <c r="R58" t="n">
-        <v>6692730</v>
+        <v>6692803</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6713,6 +6708,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Kalkrik granskog, under gran</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7142,50 +7142,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132019895</v>
+        <v>132019919</v>
       </c>
       <c r="B63" t="n">
-        <v>58109</v>
+        <v>80357</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>6457</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>669191</v>
+        <v>669113</v>
       </c>
       <c r="R63" t="n">
-        <v>6692693</v>
+        <v>6692721</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7228,6 +7223,11 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>Populas tremula</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -7244,45 +7244,50 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132019919</v>
+        <v>132019895</v>
       </c>
       <c r="B64" t="n">
-        <v>80357</v>
+        <v>58109</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6457</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>669113</v>
+        <v>669191</v>
       </c>
       <c r="R64" t="n">
-        <v>6692721</v>
+        <v>6692693</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7325,11 +7330,6 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>Populas tremula</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -7443,32 +7443,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132019889</v>
+        <v>132019897</v>
       </c>
       <c r="B66" t="n">
-        <v>91892</v>
+        <v>80326</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7478,10 +7478,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>669241</v>
+        <v>669126</v>
       </c>
       <c r="R66" t="n">
-        <v>6692784</v>
+        <v>6692721</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7525,19 +7525,9 @@
       <c r="AG66" t="b">
         <v>0</v>
       </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>Populas tremula</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -7555,32 +7545,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132019897</v>
+        <v>132019889</v>
       </c>
       <c r="B67" t="n">
-        <v>80326</v>
+        <v>91892</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7590,10 +7580,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>669126</v>
+        <v>669241</v>
       </c>
       <c r="R67" t="n">
-        <v>6692721</v>
+        <v>6692784</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7637,9 +7627,19 @@
       <c r="AG67" t="b">
         <v>0</v>
       </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>Populas tremula</t>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -7657,32 +7657,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132019888</v>
+        <v>132019903</v>
       </c>
       <c r="B68" t="n">
-        <v>91892</v>
+        <v>75423</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7692,10 +7692,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>669198</v>
+        <v>669148</v>
       </c>
       <c r="R68" t="n">
-        <v>6692759</v>
+        <v>6692645</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7739,19 +7739,9 @@
       <c r="AG68" t="b">
         <v>0</v>
       </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -7769,10 +7759,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132019903</v>
+        <v>132019898</v>
       </c>
       <c r="B69" t="n">
-        <v>75423</v>
+        <v>80326</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7780,21 +7770,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6426</v>
+        <v>6456</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7804,10 +7794,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>669148</v>
+        <v>669154</v>
       </c>
       <c r="R69" t="n">
-        <v>6692645</v>
+        <v>6692684</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7853,7 +7843,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Populas tremula</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -7871,10 +7861,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132019898</v>
+        <v>132019901</v>
       </c>
       <c r="B70" t="n">
-        <v>80326</v>
+        <v>75423</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7882,21 +7872,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6456</v>
+        <v>6426</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7906,7 +7896,7 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>669154</v>
+        <v>669196</v>
       </c>
       <c r="R70" t="n">
         <v>6692684</v>
@@ -7955,7 +7945,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Populas tremula</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -7973,32 +7963,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132019901</v>
+        <v>132019888</v>
       </c>
       <c r="B71" t="n">
-        <v>75423</v>
+        <v>91892</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8008,10 +7998,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>669196</v>
+        <v>669198</v>
       </c>
       <c r="R71" t="n">
-        <v>6692684</v>
+        <v>6692759</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8055,9 +8045,19 @@
       <c r="AG71" t="b">
         <v>0</v>
       </c>
-      <c r="AI71" t="inlineStr">
+      <c r="AJ71" t="inlineStr">
         <is>
           <t>gran</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8177,32 +8177,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132019887</v>
+        <v>132019921</v>
       </c>
       <c r="B73" t="n">
-        <v>91892</v>
+        <v>101304</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8212,10 +8212,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>669285</v>
+        <v>669204</v>
       </c>
       <c r="R73" t="n">
-        <v>6692776</v>
+        <v>6692803</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8258,21 +8258,6 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -8289,32 +8274,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132019921</v>
+        <v>132019887</v>
       </c>
       <c r="B74" t="n">
-        <v>101304</v>
+        <v>91892</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8324,10 +8309,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>669204</v>
+        <v>669285</v>
       </c>
       <c r="R74" t="n">
-        <v>6692803</v>
+        <v>6692776</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8370,6 +8355,21 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -8488,32 +8488,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132019886</v>
+        <v>132019899</v>
       </c>
       <c r="B76" t="n">
-        <v>91892</v>
+        <v>80326</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8523,10 +8523,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>669131</v>
+        <v>669151</v>
       </c>
       <c r="R76" t="n">
-        <v>6692781</v>
+        <v>6692676</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8570,19 +8570,9 @@
       <c r="AG76" t="b">
         <v>0</v>
       </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>Populas tremula</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -8600,32 +8590,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132019899</v>
+        <v>132019886</v>
       </c>
       <c r="B77" t="n">
-        <v>80326</v>
+        <v>91892</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8635,10 +8625,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>669151</v>
+        <v>669131</v>
       </c>
       <c r="R77" t="n">
-        <v>6692676</v>
+        <v>6692781</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8682,9 +8672,19 @@
       <c r="AG77" t="b">
         <v>0</v>
       </c>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>Populas tremula</t>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -8804,10 +8804,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132019908</v>
+        <v>132019894</v>
       </c>
       <c r="B79" t="n">
-        <v>79317</v>
+        <v>58109</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8815,34 +8815,39 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>669179</v>
+        <v>669208</v>
       </c>
       <c r="R79" t="n">
-        <v>6692672</v>
+        <v>6692665</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8885,11 +8890,6 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
-      </c>
-      <c r="AI79" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -8906,10 +8906,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132019894</v>
+        <v>132019908</v>
       </c>
       <c r="B80" t="n">
-        <v>58109</v>
+        <v>79317</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8917,39 +8917,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>669208</v>
+        <v>669179</v>
       </c>
       <c r="R80" t="n">
-        <v>6692665</v>
+        <v>6692672</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8992,6 +8987,11 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -1949,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131860614</v>
+        <v>131860697</v>
       </c>
       <c r="B14" t="n">
-        <v>80326</v>
+        <v>101304</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1960,21 +1960,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>669229</v>
+        <v>669157</v>
       </c>
       <c r="R14" t="n">
-        <v>6692600</v>
+        <v>6692556</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2030,21 +2030,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2061,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131860697</v>
+        <v>131860614</v>
       </c>
       <c r="B15" t="n">
-        <v>101304</v>
+        <v>80326</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2072,21 +2057,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2096,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>669157</v>
+        <v>669229</v>
       </c>
       <c r="R15" t="n">
-        <v>6692556</v>
+        <v>6692600</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2142,6 +2127,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -3116,10 +3116,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131860692</v>
+        <v>131860617</v>
       </c>
       <c r="B25" t="n">
-        <v>101304</v>
+        <v>80326</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3127,21 +3127,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>6456</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>669245</v>
+        <v>669355</v>
       </c>
       <c r="R25" t="n">
-        <v>6692828</v>
+        <v>6692827</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3197,6 +3197,21 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3213,10 +3228,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131860617</v>
+        <v>131860692</v>
       </c>
       <c r="B26" t="n">
-        <v>80326</v>
+        <v>101304</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3224,21 +3239,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6456</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3248,10 +3263,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>669355</v>
+        <v>669245</v>
       </c>
       <c r="R26" t="n">
-        <v>6692827</v>
+        <v>6692828</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3294,21 +3309,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3325,10 +3325,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131860690</v>
+        <v>131860696</v>
       </c>
       <c r="B27" t="n">
-        <v>92547</v>
+        <v>101304</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3336,21 +3336,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3360,10 +3360,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>669205</v>
+        <v>669141</v>
       </c>
       <c r="R27" t="n">
-        <v>6692610</v>
+        <v>6692607</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3406,21 +3406,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3437,50 +3422,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131860609</v>
+        <v>131860694</v>
       </c>
       <c r="B28" t="n">
-        <v>57945</v>
+        <v>101304</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>669095</v>
+        <v>669321</v>
       </c>
       <c r="R28" t="n">
-        <v>6692372</v>
+        <v>6692768</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3539,45 +3519,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131860696</v>
+        <v>131860609</v>
       </c>
       <c r="B29" t="n">
-        <v>101304</v>
+        <v>57945</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>669141</v>
+        <v>669095</v>
       </c>
       <c r="R29" t="n">
-        <v>6692607</v>
+        <v>6692372</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3636,10 +3621,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131860694</v>
+        <v>131860690</v>
       </c>
       <c r="B30" t="n">
-        <v>101304</v>
+        <v>92547</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3647,21 +3632,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>1339</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3671,10 +3656,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>669321</v>
+        <v>669205</v>
       </c>
       <c r="R30" t="n">
-        <v>6692768</v>
+        <v>6692610</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3717,6 +3702,21 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -5114,10 +5114,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131860652</v>
+        <v>131860648</v>
       </c>
       <c r="B44" t="n">
-        <v>96534</v>
+        <v>75423</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5125,21 +5125,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>210</v>
+        <v>6426</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5149,10 +5149,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>668992</v>
+        <v>669219</v>
       </c>
       <c r="R44" t="n">
-        <v>6692504</v>
+        <v>6692641</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5195,21 +5195,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5226,10 +5211,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131860642</v>
+        <v>131860620</v>
       </c>
       <c r="B45" t="n">
-        <v>80382</v>
+        <v>80326</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5237,21 +5222,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5261,10 +5246,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>669212</v>
+        <v>669176</v>
       </c>
       <c r="R45" t="n">
-        <v>6692609</v>
+        <v>6692603</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5338,10 +5323,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131860639</v>
+        <v>131860652</v>
       </c>
       <c r="B46" t="n">
-        <v>80382</v>
+        <v>96534</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5349,21 +5334,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229497</v>
+        <v>210</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5373,10 +5358,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>669215</v>
+        <v>668992</v>
       </c>
       <c r="R46" t="n">
-        <v>6692608</v>
+        <v>6692504</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5422,17 +5407,17 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5450,10 +5435,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131860648</v>
+        <v>131860642</v>
       </c>
       <c r="B47" t="n">
-        <v>75423</v>
+        <v>80382</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5461,21 +5446,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6426</v>
+        <v>229497</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5485,10 +5470,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>669219</v>
+        <v>669212</v>
       </c>
       <c r="R47" t="n">
-        <v>6692641</v>
+        <v>6692609</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5531,6 +5516,21 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5547,10 +5547,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131860620</v>
+        <v>131860639</v>
       </c>
       <c r="B48" t="n">
-        <v>80326</v>
+        <v>80382</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5558,21 +5558,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5582,10 +5582,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>669176</v>
+        <v>669215</v>
       </c>
       <c r="R48" t="n">
-        <v>6692603</v>
+        <v>6692608</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -6739,45 +6739,50 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132019907</v>
+        <v>132019892</v>
       </c>
       <c r="B59" t="n">
-        <v>4781</v>
+        <v>58109</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>102306</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>669141</v>
+        <v>669331</v>
       </c>
       <c r="R59" t="n">
-        <v>6692648</v>
+        <v>6692814</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6820,11 +6825,6 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -6841,50 +6841,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132019892</v>
+        <v>132019907</v>
       </c>
       <c r="B60" t="n">
-        <v>58109</v>
+        <v>4781</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>102306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>669331</v>
+        <v>669141</v>
       </c>
       <c r="R60" t="n">
-        <v>6692814</v>
+        <v>6692648</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6927,6 +6922,11 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7142,45 +7142,50 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132019919</v>
+        <v>132019895</v>
       </c>
       <c r="B63" t="n">
-        <v>80357</v>
+        <v>58109</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6457</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>669113</v>
+        <v>669191</v>
       </c>
       <c r="R63" t="n">
-        <v>6692721</v>
+        <v>6692693</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7223,11 +7228,6 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>Populas tremula</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -7244,50 +7244,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132019895</v>
+        <v>132019919</v>
       </c>
       <c r="B64" t="n">
-        <v>58109</v>
+        <v>80357</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>6457</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>669191</v>
+        <v>669113</v>
       </c>
       <c r="R64" t="n">
-        <v>6692693</v>
+        <v>6692721</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7330,6 +7325,11 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>Populas tremula</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -8488,32 +8488,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132019899</v>
+        <v>132019886</v>
       </c>
       <c r="B76" t="n">
-        <v>80326</v>
+        <v>91892</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8523,10 +8523,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>669151</v>
+        <v>669131</v>
       </c>
       <c r="R76" t="n">
-        <v>6692676</v>
+        <v>6692781</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8570,9 +8570,19 @@
       <c r="AG76" t="b">
         <v>0</v>
       </c>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>Populas tremula</t>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -8590,32 +8600,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132019886</v>
+        <v>132019899</v>
       </c>
       <c r="B77" t="n">
-        <v>91892</v>
+        <v>80326</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8625,10 +8635,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>669131</v>
+        <v>669151</v>
       </c>
       <c r="R77" t="n">
-        <v>6692781</v>
+        <v>6692676</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8672,19 +8682,9 @@
       <c r="AG77" t="b">
         <v>0</v>
       </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>Populas tremula</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131860656</v>
+        <v>131860695</v>
       </c>
       <c r="B8" t="n">
-        <v>4781</v>
+        <v>101304</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>669149</v>
+        <v>669270</v>
       </c>
       <c r="R8" t="n">
-        <v>6692521</v>
+        <v>6692768</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1388,21 +1388,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1419,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131860695</v>
+        <v>131860656</v>
       </c>
       <c r="B9" t="n">
-        <v>101304</v>
+        <v>4781</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1430,21 +1415,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>669270</v>
+        <v>669149</v>
       </c>
       <c r="R9" t="n">
-        <v>6692768</v>
+        <v>6692521</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1500,6 +1485,21 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1949,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131860697</v>
+        <v>131860614</v>
       </c>
       <c r="B14" t="n">
-        <v>101304</v>
+        <v>80326</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1960,21 +1960,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>669157</v>
+        <v>669229</v>
       </c>
       <c r="R14" t="n">
-        <v>6692556</v>
+        <v>6692600</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2030,6 +2030,21 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2046,10 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131860614</v>
+        <v>131860697</v>
       </c>
       <c r="B15" t="n">
-        <v>80326</v>
+        <v>101304</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2057,21 +2072,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2081,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>669229</v>
+        <v>669157</v>
       </c>
       <c r="R15" t="n">
-        <v>6692600</v>
+        <v>6692556</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2127,21 +2142,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -3325,10 +3325,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131860696</v>
+        <v>131860690</v>
       </c>
       <c r="B27" t="n">
-        <v>101304</v>
+        <v>92547</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3336,21 +3336,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>1339</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3360,10 +3360,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>669141</v>
+        <v>669205</v>
       </c>
       <c r="R27" t="n">
-        <v>6692607</v>
+        <v>6692610</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3406,6 +3406,21 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3422,45 +3437,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131860694</v>
+        <v>131860609</v>
       </c>
       <c r="B28" t="n">
-        <v>101304</v>
+        <v>57945</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>669321</v>
+        <v>669095</v>
       </c>
       <c r="R28" t="n">
-        <v>6692768</v>
+        <v>6692372</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3519,50 +3539,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131860609</v>
+        <v>131860696</v>
       </c>
       <c r="B29" t="n">
-        <v>57945</v>
+        <v>101304</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>669095</v>
+        <v>669141</v>
       </c>
       <c r="R29" t="n">
-        <v>6692372</v>
+        <v>6692607</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3621,10 +3636,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131860690</v>
+        <v>131860694</v>
       </c>
       <c r="B30" t="n">
-        <v>92547</v>
+        <v>101304</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3632,21 +3647,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3656,10 +3671,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>669205</v>
+        <v>669321</v>
       </c>
       <c r="R30" t="n">
-        <v>6692610</v>
+        <v>6692768</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3702,21 +3717,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -3325,10 +3325,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131860690</v>
+        <v>131860696</v>
       </c>
       <c r="B27" t="n">
-        <v>92547</v>
+        <v>101304</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3336,21 +3336,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3360,10 +3360,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>669205</v>
+        <v>669141</v>
       </c>
       <c r="R27" t="n">
-        <v>6692610</v>
+        <v>6692607</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3406,21 +3406,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3437,50 +3422,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131860609</v>
+        <v>131860694</v>
       </c>
       <c r="B28" t="n">
-        <v>57945</v>
+        <v>101304</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>669095</v>
+        <v>669321</v>
       </c>
       <c r="R28" t="n">
-        <v>6692372</v>
+        <v>6692768</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3539,45 +3519,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131860696</v>
+        <v>131860609</v>
       </c>
       <c r="B29" t="n">
-        <v>101304</v>
+        <v>57945</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>669141</v>
+        <v>669095</v>
       </c>
       <c r="R29" t="n">
-        <v>6692607</v>
+        <v>6692372</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3636,10 +3621,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131860694</v>
+        <v>131860690</v>
       </c>
       <c r="B30" t="n">
-        <v>101304</v>
+        <v>92547</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3647,21 +3632,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>1339</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3671,10 +3656,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>669321</v>
+        <v>669205</v>
       </c>
       <c r="R30" t="n">
-        <v>6692768</v>
+        <v>6692610</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3717,6 +3702,21 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4502,32 +4502,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131860593</v>
+        <v>131860607</v>
       </c>
       <c r="B38" t="n">
-        <v>91892</v>
+        <v>96438</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>2818</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4537,10 +4537,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>669198</v>
+        <v>668968</v>
       </c>
       <c r="R38" t="n">
-        <v>6692763</v>
+        <v>6692265</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4599,32 +4599,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131860607</v>
+        <v>131860593</v>
       </c>
       <c r="B39" t="n">
-        <v>96438</v>
+        <v>91892</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2818</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4634,10 +4634,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>668968</v>
+        <v>669198</v>
       </c>
       <c r="R39" t="n">
-        <v>6692265</v>
+        <v>6692763</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5114,10 +5114,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131860648</v>
+        <v>131860652</v>
       </c>
       <c r="B44" t="n">
-        <v>75423</v>
+        <v>96534</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5125,21 +5125,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6426</v>
+        <v>210</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5149,10 +5149,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>669219</v>
+        <v>668992</v>
       </c>
       <c r="R44" t="n">
-        <v>6692641</v>
+        <v>6692504</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5195,6 +5195,21 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5211,10 +5226,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131860620</v>
+        <v>131860642</v>
       </c>
       <c r="B45" t="n">
-        <v>80326</v>
+        <v>80382</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5222,21 +5237,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5246,10 +5261,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>669176</v>
+        <v>669212</v>
       </c>
       <c r="R45" t="n">
-        <v>6692603</v>
+        <v>6692609</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5323,10 +5338,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131860652</v>
+        <v>131860639</v>
       </c>
       <c r="B46" t="n">
-        <v>96534</v>
+        <v>80382</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5334,21 +5349,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>210</v>
+        <v>229497</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5358,10 +5373,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>668992</v>
+        <v>669215</v>
       </c>
       <c r="R46" t="n">
-        <v>6692504</v>
+        <v>6692608</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5407,17 +5422,17 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5435,10 +5450,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131860642</v>
+        <v>131860648</v>
       </c>
       <c r="B47" t="n">
-        <v>80382</v>
+        <v>75423</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5446,21 +5461,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229497</v>
+        <v>6426</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5470,10 +5485,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>669212</v>
+        <v>669219</v>
       </c>
       <c r="R47" t="n">
-        <v>6692609</v>
+        <v>6692641</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5516,21 +5531,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5547,10 +5547,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131860639</v>
+        <v>131860620</v>
       </c>
       <c r="B48" t="n">
-        <v>80382</v>
+        <v>80326</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5558,21 +5558,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5582,10 +5582,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>669215</v>
+        <v>669176</v>
       </c>
       <c r="R48" t="n">
-        <v>6692608</v>
+        <v>6692603</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5883,10 +5883,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131860691</v>
+        <v>131860683</v>
       </c>
       <c r="B51" t="n">
-        <v>92547</v>
+        <v>80357</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5894,21 +5894,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1339</v>
+        <v>6457</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5918,10 +5918,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>669198</v>
+        <v>669167</v>
       </c>
       <c r="R51" t="n">
-        <v>6692600</v>
+        <v>6692763</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5967,17 +5967,17 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -5995,10 +5995,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131860683</v>
+        <v>131860691</v>
       </c>
       <c r="B52" t="n">
-        <v>80357</v>
+        <v>92547</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6006,21 +6006,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6457</v>
+        <v>1339</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6030,10 +6030,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>669167</v>
+        <v>669198</v>
       </c>
       <c r="R52" t="n">
-        <v>6692763</v>
+        <v>6692600</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6079,17 +6079,17 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6739,50 +6739,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132019892</v>
+        <v>132019907</v>
       </c>
       <c r="B59" t="n">
-        <v>58109</v>
+        <v>4781</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>102306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>669331</v>
+        <v>669141</v>
       </c>
       <c r="R59" t="n">
-        <v>6692814</v>
+        <v>6692648</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6825,6 +6820,11 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -6841,45 +6841,50 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132019907</v>
+        <v>132019892</v>
       </c>
       <c r="B60" t="n">
-        <v>4781</v>
+        <v>58109</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>102306</v>
+        <v>103021</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>669141</v>
+        <v>669331</v>
       </c>
       <c r="R60" t="n">
-        <v>6692648</v>
+        <v>6692814</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6922,11 +6927,6 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AI60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7142,50 +7142,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132019895</v>
+        <v>132019919</v>
       </c>
       <c r="B63" t="n">
-        <v>58109</v>
+        <v>80357</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>6457</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>669191</v>
+        <v>669113</v>
       </c>
       <c r="R63" t="n">
-        <v>6692693</v>
+        <v>6692721</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7228,6 +7223,11 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>Populas tremula</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -7244,45 +7244,50 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132019919</v>
+        <v>132019895</v>
       </c>
       <c r="B64" t="n">
-        <v>80357</v>
+        <v>58109</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6457</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>669113</v>
+        <v>669191</v>
       </c>
       <c r="R64" t="n">
-        <v>6692721</v>
+        <v>6692693</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7325,11 +7330,6 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>Populas tremula</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -8177,32 +8177,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132019921</v>
+        <v>132019887</v>
       </c>
       <c r="B73" t="n">
-        <v>101304</v>
+        <v>91892</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8212,10 +8212,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>669204</v>
+        <v>669285</v>
       </c>
       <c r="R73" t="n">
-        <v>6692803</v>
+        <v>6692776</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8258,6 +8258,21 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -8274,32 +8289,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132019887</v>
+        <v>132019921</v>
       </c>
       <c r="B74" t="n">
-        <v>91892</v>
+        <v>101304</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8309,10 +8324,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>669285</v>
+        <v>669204</v>
       </c>
       <c r="R74" t="n">
-        <v>6692776</v>
+        <v>6692803</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8355,21 +8370,6 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -8488,32 +8488,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132019886</v>
+        <v>132019899</v>
       </c>
       <c r="B76" t="n">
-        <v>91892</v>
+        <v>80326</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8523,10 +8523,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>669131</v>
+        <v>669151</v>
       </c>
       <c r="R76" t="n">
-        <v>6692781</v>
+        <v>6692676</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8570,19 +8570,9 @@
       <c r="AG76" t="b">
         <v>0</v>
       </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>Populas tremula</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -8600,32 +8590,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132019899</v>
+        <v>132019886</v>
       </c>
       <c r="B77" t="n">
-        <v>80326</v>
+        <v>91892</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8635,10 +8625,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>669151</v>
+        <v>669131</v>
       </c>
       <c r="R77" t="n">
-        <v>6692676</v>
+        <v>6692781</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8682,9 +8672,19 @@
       <c r="AG77" t="b">
         <v>0</v>
       </c>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>Populas tremula</t>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -6540,10 +6540,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132019922</v>
+        <v>132019904</v>
       </c>
       <c r="B57" t="n">
-        <v>101304</v>
+        <v>91319</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6551,21 +6551,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222498</v>
+        <v>4189</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Pers., nom.sanct</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6575,10 +6575,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>669218</v>
+        <v>669298</v>
       </c>
       <c r="R57" t="n">
-        <v>6692730</v>
+        <v>6692803</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6611,6 +6611,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Kalkrik granskog, under gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6637,10 +6642,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132019904</v>
+        <v>132019922</v>
       </c>
       <c r="B58" t="n">
-        <v>91313</v>
+        <v>101312</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6648,21 +6653,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4189</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6672,10 +6677,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>669298</v>
+        <v>669218</v>
       </c>
       <c r="R58" t="n">
-        <v>6692803</v>
+        <v>6692730</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6708,11 +6713,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Kalkrik granskog, under gran</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6844,7 +6844,7 @@
         <v>132019892</v>
       </c>
       <c r="B60" t="n">
-        <v>58109</v>
+        <v>58110</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>132019900</v>
       </c>
       <c r="B61" t="n">
-        <v>58322</v>
+        <v>58323</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
         <v>132019905</v>
       </c>
       <c r="B62" t="n">
-        <v>96534</v>
+        <v>96542</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
         <v>132019919</v>
       </c>
       <c r="B63" t="n">
-        <v>80357</v>
+        <v>80359</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>132019895</v>
       </c>
       <c r="B64" t="n">
-        <v>58109</v>
+        <v>58110</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7346,10 +7346,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132019920</v>
+        <v>132019897</v>
       </c>
       <c r="B65" t="n">
-        <v>101304</v>
+        <v>80328</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7357,21 +7357,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222498</v>
+        <v>6456</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7381,10 +7381,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>669116</v>
+        <v>669126</v>
       </c>
       <c r="R65" t="n">
-        <v>6692739</v>
+        <v>6692721</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7427,6 +7427,11 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>Populas tremula</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -7443,10 +7448,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132019897</v>
+        <v>132019920</v>
       </c>
       <c r="B66" t="n">
-        <v>80326</v>
+        <v>101312</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7454,21 +7459,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6456</v>
+        <v>222498</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7478,10 +7483,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>669126</v>
+        <v>669116</v>
       </c>
       <c r="R66" t="n">
-        <v>6692721</v>
+        <v>6692739</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7524,11 +7529,6 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>Populas tremula</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -7548,7 +7548,7 @@
         <v>132019889</v>
       </c>
       <c r="B67" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7657,32 +7657,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132019903</v>
+        <v>132019888</v>
       </c>
       <c r="B68" t="n">
-        <v>75423</v>
+        <v>91898</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7692,10 +7692,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>669148</v>
+        <v>669198</v>
       </c>
       <c r="R68" t="n">
-        <v>6692645</v>
+        <v>6692759</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7739,9 +7739,19 @@
       <c r="AG68" t="b">
         <v>0</v>
       </c>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>Gran</t>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -7759,10 +7769,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132019898</v>
+        <v>132019903</v>
       </c>
       <c r="B69" t="n">
-        <v>80326</v>
+        <v>75424</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7770,21 +7780,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6456</v>
+        <v>6426</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7794,10 +7804,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>669154</v>
+        <v>669148</v>
       </c>
       <c r="R69" t="n">
-        <v>6692684</v>
+        <v>6692645</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7843,7 +7853,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Populas tremula</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -7861,10 +7871,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132019901</v>
+        <v>132019898</v>
       </c>
       <c r="B70" t="n">
-        <v>75423</v>
+        <v>80328</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7872,21 +7882,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6426</v>
+        <v>6456</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7896,7 +7906,7 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>669196</v>
+        <v>669154</v>
       </c>
       <c r="R70" t="n">
         <v>6692684</v>
@@ -7945,7 +7955,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>Populas tremula</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -7963,32 +7973,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132019888</v>
+        <v>132019901</v>
       </c>
       <c r="B71" t="n">
-        <v>91892</v>
+        <v>75424</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7998,10 +8008,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>669198</v>
+        <v>669196</v>
       </c>
       <c r="R71" t="n">
-        <v>6692759</v>
+        <v>6692684</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8045,19 +8055,9 @@
       <c r="AG71" t="b">
         <v>0</v>
       </c>
-      <c r="AJ71" t="inlineStr">
+      <c r="AI71" t="inlineStr">
         <is>
           <t>gran</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8078,7 +8078,7 @@
         <v>132019918</v>
       </c>
       <c r="B72" t="n">
-        <v>80357</v>
+        <v>80359</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8180,7 +8180,7 @@
         <v>132019887</v>
       </c>
       <c r="B73" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8292,7 +8292,7 @@
         <v>132019921</v>
       </c>
       <c r="B74" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8389,7 +8389,7 @@
         <v>132019896</v>
       </c>
       <c r="B75" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8488,32 +8488,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132019899</v>
+        <v>132019886</v>
       </c>
       <c r="B76" t="n">
-        <v>80326</v>
+        <v>91898</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8523,10 +8523,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>669151</v>
+        <v>669131</v>
       </c>
       <c r="R76" t="n">
-        <v>6692676</v>
+        <v>6692781</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8570,9 +8570,19 @@
       <c r="AG76" t="b">
         <v>0</v>
       </c>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>Populas tremula</t>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -8590,32 +8600,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132019886</v>
+        <v>132019899</v>
       </c>
       <c r="B77" t="n">
-        <v>91892</v>
+        <v>80328</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8625,10 +8635,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>669131</v>
+        <v>669151</v>
       </c>
       <c r="R77" t="n">
-        <v>6692781</v>
+        <v>6692676</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8672,19 +8682,9 @@
       <c r="AG77" t="b">
         <v>0</v>
       </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>Populas tremula</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -8804,10 +8804,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132019894</v>
+        <v>132019908</v>
       </c>
       <c r="B79" t="n">
-        <v>58109</v>
+        <v>79319</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8815,39 +8815,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>669208</v>
+        <v>669179</v>
       </c>
       <c r="R79" t="n">
-        <v>6692665</v>
+        <v>6692672</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8890,6 +8885,11 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -8906,10 +8906,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132019908</v>
+        <v>132019894</v>
       </c>
       <c r="B80" t="n">
-        <v>79317</v>
+        <v>58110</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8917,34 +8917,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>669179</v>
+        <v>669208</v>
       </c>
       <c r="R80" t="n">
-        <v>6692672</v>
+        <v>6692665</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8987,11 +8992,6 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AI80" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -9011,7 +9011,7 @@
         <v>132019893</v>
       </c>
       <c r="B81" t="n">
-        <v>58109</v>
+        <v>58110</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -7346,32 +7346,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132019897</v>
+        <v>132019889</v>
       </c>
       <c r="B65" t="n">
-        <v>80328</v>
+        <v>91898</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7381,10 +7381,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>669126</v>
+        <v>669241</v>
       </c>
       <c r="R65" t="n">
-        <v>6692721</v>
+        <v>6692784</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7428,9 +7428,19 @@
       <c r="AG65" t="b">
         <v>0</v>
       </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>Populas tremula</t>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -7448,10 +7458,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132019920</v>
+        <v>132019897</v>
       </c>
       <c r="B66" t="n">
-        <v>101312</v>
+        <v>80328</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7459,21 +7469,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222498</v>
+        <v>6456</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7483,10 +7493,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>669116</v>
+        <v>669126</v>
       </c>
       <c r="R66" t="n">
-        <v>6692739</v>
+        <v>6692721</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7529,6 +7539,11 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>Populas tremula</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -7545,32 +7560,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132019889</v>
+        <v>132019920</v>
       </c>
       <c r="B67" t="n">
-        <v>91898</v>
+        <v>101312</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7580,10 +7595,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>669241</v>
+        <v>669116</v>
       </c>
       <c r="R67" t="n">
-        <v>6692784</v>
+        <v>6692739</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7626,21 +7641,6 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -6540,10 +6540,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132019904</v>
+        <v>132019922</v>
       </c>
       <c r="B57" t="n">
-        <v>91319</v>
+        <v>101323</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6551,21 +6551,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4189</v>
+        <v>222498</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6575,10 +6575,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>669298</v>
+        <v>669218</v>
       </c>
       <c r="R57" t="n">
-        <v>6692803</v>
+        <v>6692730</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6611,11 +6611,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Kalkrik granskog, under gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6642,10 +6637,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132019922</v>
+        <v>132019904</v>
       </c>
       <c r="B58" t="n">
-        <v>101312</v>
+        <v>91329</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6653,21 +6648,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>4189</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Pers., nom.sanct</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6677,10 +6672,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>669218</v>
+        <v>669298</v>
       </c>
       <c r="R58" t="n">
-        <v>6692730</v>
+        <v>6692803</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6713,6 +6708,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Kalkrik granskog, under gran</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6739,45 +6739,50 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132019907</v>
+        <v>132019892</v>
       </c>
       <c r="B59" t="n">
-        <v>4781</v>
+        <v>58114</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>102306</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>669141</v>
+        <v>669331</v>
       </c>
       <c r="R59" t="n">
-        <v>6692648</v>
+        <v>6692814</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6820,11 +6825,6 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -6841,50 +6841,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132019892</v>
+        <v>132019907</v>
       </c>
       <c r="B60" t="n">
-        <v>58110</v>
+        <v>4781</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>102306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>669331</v>
+        <v>669141</v>
       </c>
       <c r="R60" t="n">
-        <v>6692814</v>
+        <v>6692648</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6927,6 +6922,11 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -6946,7 +6946,7 @@
         <v>132019900</v>
       </c>
       <c r="B61" t="n">
-        <v>58323</v>
+        <v>58327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
         <v>132019905</v>
       </c>
       <c r="B62" t="n">
-        <v>96542</v>
+        <v>96552</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
         <v>132019919</v>
       </c>
       <c r="B63" t="n">
-        <v>80359</v>
+        <v>80367</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>132019895</v>
       </c>
       <c r="B64" t="n">
-        <v>58110</v>
+        <v>58114</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7349,7 +7349,7 @@
         <v>132019889</v>
       </c>
       <c r="B65" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
         <v>132019897</v>
       </c>
       <c r="B66" t="n">
-        <v>80328</v>
+        <v>80336</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>132019920</v>
       </c>
       <c r="B67" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7657,32 +7657,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132019888</v>
+        <v>132019903</v>
       </c>
       <c r="B68" t="n">
-        <v>91898</v>
+        <v>75428</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7692,10 +7692,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>669198</v>
+        <v>669148</v>
       </c>
       <c r="R68" t="n">
-        <v>6692759</v>
+        <v>6692645</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7739,19 +7739,9 @@
       <c r="AG68" t="b">
         <v>0</v>
       </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -7769,10 +7759,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132019903</v>
+        <v>132019898</v>
       </c>
       <c r="B69" t="n">
-        <v>75424</v>
+        <v>80336</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7780,21 +7770,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6426</v>
+        <v>6456</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7804,10 +7794,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>669148</v>
+        <v>669154</v>
       </c>
       <c r="R69" t="n">
-        <v>6692645</v>
+        <v>6692684</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7853,7 +7843,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Populas tremula</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -7871,10 +7861,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132019898</v>
+        <v>132019901</v>
       </c>
       <c r="B70" t="n">
-        <v>80328</v>
+        <v>75428</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7882,21 +7872,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6456</v>
+        <v>6426</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7906,7 +7896,7 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>669154</v>
+        <v>669196</v>
       </c>
       <c r="R70" t="n">
         <v>6692684</v>
@@ -7955,7 +7945,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Populas tremula</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -7973,32 +7963,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132019901</v>
+        <v>132019888</v>
       </c>
       <c r="B71" t="n">
-        <v>75424</v>
+        <v>91908</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8008,10 +7998,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>669196</v>
+        <v>669198</v>
       </c>
       <c r="R71" t="n">
-        <v>6692684</v>
+        <v>6692759</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8055,9 +8045,19 @@
       <c r="AG71" t="b">
         <v>0</v>
       </c>
-      <c r="AI71" t="inlineStr">
+      <c r="AJ71" t="inlineStr">
         <is>
           <t>gran</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8078,7 +8078,7 @@
         <v>132019918</v>
       </c>
       <c r="B72" t="n">
-        <v>80359</v>
+        <v>80367</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8177,32 +8177,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132019887</v>
+        <v>132019921</v>
       </c>
       <c r="B73" t="n">
-        <v>91898</v>
+        <v>101323</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8212,10 +8212,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>669285</v>
+        <v>669204</v>
       </c>
       <c r="R73" t="n">
-        <v>6692776</v>
+        <v>6692803</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8258,21 +8258,6 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -8289,32 +8274,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132019921</v>
+        <v>132019887</v>
       </c>
       <c r="B74" t="n">
-        <v>101312</v>
+        <v>91908</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8324,10 +8309,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>669204</v>
+        <v>669285</v>
       </c>
       <c r="R74" t="n">
-        <v>6692803</v>
+        <v>6692776</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8370,6 +8355,21 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -8389,7 +8389,7 @@
         <v>132019896</v>
       </c>
       <c r="B75" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>132019886</v>
       </c>
       <c r="B76" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         <v>132019899</v>
       </c>
       <c r="B77" t="n">
-        <v>80328</v>
+        <v>80336</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         <v>132019908</v>
       </c>
       <c r="B79" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         <v>132019894</v>
       </c>
       <c r="B80" t="n">
-        <v>58110</v>
+        <v>58114</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>132019893</v>
       </c>
       <c r="B81" t="n">
-        <v>58110</v>
+        <v>58114</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -6739,50 +6739,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132019892</v>
+        <v>132019907</v>
       </c>
       <c r="B59" t="n">
-        <v>58114</v>
+        <v>4781</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>102306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>669331</v>
+        <v>669141</v>
       </c>
       <c r="R59" t="n">
-        <v>6692814</v>
+        <v>6692648</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6825,6 +6820,11 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -6841,45 +6841,50 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132019907</v>
+        <v>132019892</v>
       </c>
       <c r="B60" t="n">
-        <v>4781</v>
+        <v>58114</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>102306</v>
+        <v>103021</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>669141</v>
+        <v>669331</v>
       </c>
       <c r="R60" t="n">
-        <v>6692648</v>
+        <v>6692814</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6922,11 +6927,6 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AI60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7346,32 +7346,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132019889</v>
+        <v>132019897</v>
       </c>
       <c r="B65" t="n">
-        <v>91908</v>
+        <v>80336</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7381,10 +7381,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>669241</v>
+        <v>669126</v>
       </c>
       <c r="R65" t="n">
-        <v>6692784</v>
+        <v>6692721</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7428,19 +7428,9 @@
       <c r="AG65" t="b">
         <v>0</v>
       </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>Populas tremula</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -7458,32 +7448,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132019897</v>
+        <v>132019889</v>
       </c>
       <c r="B66" t="n">
-        <v>80336</v>
+        <v>91908</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7493,10 +7483,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>669126</v>
+        <v>669241</v>
       </c>
       <c r="R66" t="n">
-        <v>6692721</v>
+        <v>6692784</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7540,9 +7530,19 @@
       <c r="AG66" t="b">
         <v>0</v>
       </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>Populas tremula</t>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -7657,32 +7657,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132019903</v>
+        <v>132019888</v>
       </c>
       <c r="B68" t="n">
-        <v>75428</v>
+        <v>91908</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7692,10 +7692,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>669148</v>
+        <v>669198</v>
       </c>
       <c r="R68" t="n">
-        <v>6692645</v>
+        <v>6692759</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7739,9 +7739,19 @@
       <c r="AG68" t="b">
         <v>0</v>
       </c>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>Gran</t>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -7759,10 +7769,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132019898</v>
+        <v>132019903</v>
       </c>
       <c r="B69" t="n">
-        <v>80336</v>
+        <v>75428</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7770,21 +7780,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6456</v>
+        <v>6426</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7794,10 +7804,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>669154</v>
+        <v>669148</v>
       </c>
       <c r="R69" t="n">
-        <v>6692684</v>
+        <v>6692645</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7843,7 +7853,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Populas tremula</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -7861,10 +7871,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132019901</v>
+        <v>132019898</v>
       </c>
       <c r="B70" t="n">
-        <v>75428</v>
+        <v>80336</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7872,21 +7882,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6426</v>
+        <v>6456</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7896,7 +7906,7 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>669196</v>
+        <v>669154</v>
       </c>
       <c r="R70" t="n">
         <v>6692684</v>
@@ -7945,7 +7955,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>Populas tremula</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -7963,32 +7973,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132019888</v>
+        <v>132019901</v>
       </c>
       <c r="B71" t="n">
-        <v>91908</v>
+        <v>75428</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7998,10 +8008,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>669198</v>
+        <v>669196</v>
       </c>
       <c r="R71" t="n">
-        <v>6692759</v>
+        <v>6692684</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8045,19 +8055,9 @@
       <c r="AG71" t="b">
         <v>0</v>
       </c>
-      <c r="AJ71" t="inlineStr">
+      <c r="AI71" t="inlineStr">
         <is>
           <t>gran</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8177,32 +8177,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132019921</v>
+        <v>132019887</v>
       </c>
       <c r="B73" t="n">
-        <v>101323</v>
+        <v>91908</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8212,10 +8212,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>669204</v>
+        <v>669285</v>
       </c>
       <c r="R73" t="n">
-        <v>6692803</v>
+        <v>6692776</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8258,6 +8258,21 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -8274,32 +8289,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132019887</v>
+        <v>132019921</v>
       </c>
       <c r="B74" t="n">
-        <v>91908</v>
+        <v>101323</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8309,10 +8324,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>669285</v>
+        <v>669204</v>
       </c>
       <c r="R74" t="n">
-        <v>6692776</v>
+        <v>6692803</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8355,21 +8370,6 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -8804,10 +8804,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132019908</v>
+        <v>132019894</v>
       </c>
       <c r="B79" t="n">
-        <v>79327</v>
+        <v>58114</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8815,34 +8815,39 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>669179</v>
+        <v>669208</v>
       </c>
       <c r="R79" t="n">
-        <v>6692672</v>
+        <v>6692665</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8885,11 +8890,6 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
-      </c>
-      <c r="AI79" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -8906,10 +8906,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132019894</v>
+        <v>132019908</v>
       </c>
       <c r="B80" t="n">
-        <v>58114</v>
+        <v>79327</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8917,39 +8917,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>669208</v>
+        <v>669179</v>
       </c>
       <c r="R80" t="n">
-        <v>6692665</v>
+        <v>6692672</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8992,6 +8987,11 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -6540,10 +6540,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132019922</v>
+        <v>132019904</v>
       </c>
       <c r="B57" t="n">
-        <v>101323</v>
+        <v>91330</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6551,21 +6551,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222498</v>
+        <v>4189</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Pers., nom.sanct</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6575,10 +6575,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>669218</v>
+        <v>669298</v>
       </c>
       <c r="R57" t="n">
-        <v>6692730</v>
+        <v>6692803</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6611,6 +6611,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Kalkrik granskog, under gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6637,10 +6642,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132019904</v>
+        <v>132019922</v>
       </c>
       <c r="B58" t="n">
-        <v>91329</v>
+        <v>101325</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6648,21 +6653,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4189</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6672,10 +6677,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>669298</v>
+        <v>669218</v>
       </c>
       <c r="R58" t="n">
-        <v>6692803</v>
+        <v>6692730</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6708,11 +6713,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Kalkrik granskog, under gran</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7048,7 +7048,7 @@
         <v>132019905</v>
       </c>
       <c r="B62" t="n">
-        <v>96552</v>
+        <v>96554</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7346,32 +7346,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132019897</v>
+        <v>132019889</v>
       </c>
       <c r="B65" t="n">
-        <v>80336</v>
+        <v>91909</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7381,10 +7381,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>669126</v>
+        <v>669241</v>
       </c>
       <c r="R65" t="n">
-        <v>6692721</v>
+        <v>6692784</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7428,9 +7428,19 @@
       <c r="AG65" t="b">
         <v>0</v>
       </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>Populas tremula</t>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -7448,32 +7458,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132019889</v>
+        <v>132019920</v>
       </c>
       <c r="B66" t="n">
-        <v>91908</v>
+        <v>101325</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7483,10 +7493,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>669241</v>
+        <v>669116</v>
       </c>
       <c r="R66" t="n">
-        <v>6692784</v>
+        <v>6692739</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7529,21 +7539,6 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -7560,10 +7555,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132019920</v>
+        <v>132019897</v>
       </c>
       <c r="B67" t="n">
-        <v>101323</v>
+        <v>80336</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7571,21 +7566,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>222498</v>
+        <v>6456</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7595,10 +7590,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>669116</v>
+        <v>669126</v>
       </c>
       <c r="R67" t="n">
-        <v>6692739</v>
+        <v>6692721</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7641,6 +7636,11 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>Populas tremula</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -7657,32 +7657,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132019888</v>
+        <v>132019903</v>
       </c>
       <c r="B68" t="n">
-        <v>91908</v>
+        <v>75428</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7692,10 +7692,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>669198</v>
+        <v>669148</v>
       </c>
       <c r="R68" t="n">
-        <v>6692759</v>
+        <v>6692645</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7739,19 +7739,9 @@
       <c r="AG68" t="b">
         <v>0</v>
       </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -7769,10 +7759,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132019903</v>
+        <v>132019898</v>
       </c>
       <c r="B69" t="n">
-        <v>75428</v>
+        <v>80336</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7780,21 +7770,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6426</v>
+        <v>6456</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7804,10 +7794,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>669148</v>
+        <v>669154</v>
       </c>
       <c r="R69" t="n">
-        <v>6692645</v>
+        <v>6692684</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7853,7 +7843,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Populas tremula</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -7871,10 +7861,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132019898</v>
+        <v>132019901</v>
       </c>
       <c r="B70" t="n">
-        <v>80336</v>
+        <v>75428</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7882,21 +7872,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6456</v>
+        <v>6426</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7906,7 +7896,7 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>669154</v>
+        <v>669196</v>
       </c>
       <c r="R70" t="n">
         <v>6692684</v>
@@ -7955,7 +7945,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Populas tremula</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -7973,32 +7963,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132019901</v>
+        <v>132019888</v>
       </c>
       <c r="B71" t="n">
-        <v>75428</v>
+        <v>91909</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8008,10 +7998,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>669196</v>
+        <v>669198</v>
       </c>
       <c r="R71" t="n">
-        <v>6692684</v>
+        <v>6692759</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8055,9 +8045,19 @@
       <c r="AG71" t="b">
         <v>0</v>
       </c>
-      <c r="AI71" t="inlineStr">
+      <c r="AJ71" t="inlineStr">
         <is>
           <t>gran</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8177,32 +8177,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132019887</v>
+        <v>132019921</v>
       </c>
       <c r="B73" t="n">
-        <v>91908</v>
+        <v>101325</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8212,10 +8212,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>669285</v>
+        <v>669204</v>
       </c>
       <c r="R73" t="n">
-        <v>6692776</v>
+        <v>6692803</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8258,21 +8258,6 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -8289,32 +8274,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132019921</v>
+        <v>132019887</v>
       </c>
       <c r="B74" t="n">
-        <v>101323</v>
+        <v>91909</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8324,10 +8309,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>669204</v>
+        <v>669285</v>
       </c>
       <c r="R74" t="n">
-        <v>6692803</v>
+        <v>6692776</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8370,6 +8355,21 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -8488,32 +8488,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132019886</v>
+        <v>132019899</v>
       </c>
       <c r="B76" t="n">
-        <v>91908</v>
+        <v>80336</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8523,10 +8523,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>669131</v>
+        <v>669151</v>
       </c>
       <c r="R76" t="n">
-        <v>6692781</v>
+        <v>6692676</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8570,19 +8570,9 @@
       <c r="AG76" t="b">
         <v>0</v>
       </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>Populas tremula</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -8600,32 +8590,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132019899</v>
+        <v>132019886</v>
       </c>
       <c r="B77" t="n">
-        <v>80336</v>
+        <v>91909</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8635,10 +8625,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>669151</v>
+        <v>669131</v>
       </c>
       <c r="R77" t="n">
-        <v>6692676</v>
+        <v>6692781</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8682,9 +8672,19 @@
       <c r="AG77" t="b">
         <v>0</v>
       </c>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>Populas tremula</t>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -8804,10 +8804,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132019894</v>
+        <v>132019908</v>
       </c>
       <c r="B79" t="n">
-        <v>58114</v>
+        <v>79327</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8815,39 +8815,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>669208</v>
+        <v>669179</v>
       </c>
       <c r="R79" t="n">
-        <v>6692665</v>
+        <v>6692672</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8890,6 +8885,11 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -8906,10 +8906,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132019908</v>
+        <v>132019894</v>
       </c>
       <c r="B80" t="n">
-        <v>79327</v>
+        <v>58114</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8917,34 +8917,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>669179</v>
+        <v>669208</v>
       </c>
       <c r="R80" t="n">
-        <v>6692672</v>
+        <v>6692665</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8987,11 +8992,6 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AI80" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -6739,45 +6739,50 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132019907</v>
+        <v>132019892</v>
       </c>
       <c r="B59" t="n">
-        <v>4781</v>
+        <v>58114</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>102306</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>669141</v>
+        <v>669331</v>
       </c>
       <c r="R59" t="n">
-        <v>6692648</v>
+        <v>6692814</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6820,11 +6825,6 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -6841,50 +6841,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132019892</v>
+        <v>132019907</v>
       </c>
       <c r="B60" t="n">
-        <v>58114</v>
+        <v>4781</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>102306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>669331</v>
+        <v>669141</v>
       </c>
       <c r="R60" t="n">
-        <v>6692814</v>
+        <v>6692648</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6927,6 +6922,11 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -8488,32 +8488,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132019899</v>
+        <v>132019886</v>
       </c>
       <c r="B76" t="n">
-        <v>80336</v>
+        <v>91909</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8523,10 +8523,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>669151</v>
+        <v>669131</v>
       </c>
       <c r="R76" t="n">
-        <v>6692676</v>
+        <v>6692781</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8570,9 +8570,19 @@
       <c r="AG76" t="b">
         <v>0</v>
       </c>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>Populas tremula</t>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -8590,32 +8600,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132019886</v>
+        <v>132019899</v>
       </c>
       <c r="B77" t="n">
-        <v>91909</v>
+        <v>80336</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8625,10 +8635,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>669131</v>
+        <v>669151</v>
       </c>
       <c r="R77" t="n">
-        <v>6692781</v>
+        <v>6692676</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8672,19 +8682,9 @@
       <c r="AG77" t="b">
         <v>0</v>
       </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>Populas tremula</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -6540,10 +6540,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132019904</v>
+        <v>132019922</v>
       </c>
       <c r="B57" t="n">
-        <v>91330</v>
+        <v>101326</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6551,21 +6551,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4189</v>
+        <v>222498</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6575,10 +6575,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>669298</v>
+        <v>669218</v>
       </c>
       <c r="R57" t="n">
-        <v>6692803</v>
+        <v>6692730</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6611,11 +6611,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Kalkrik granskog, under gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6642,10 +6637,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132019922</v>
+        <v>132019904</v>
       </c>
       <c r="B58" t="n">
-        <v>101325</v>
+        <v>91330</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6653,21 +6648,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>4189</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Pers., nom.sanct</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6677,10 +6672,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>669218</v>
+        <v>669298</v>
       </c>
       <c r="R58" t="n">
-        <v>6692730</v>
+        <v>6692803</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6713,6 +6708,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Kalkrik granskog, under gran</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7461,7 +7461,7 @@
         <v>132019920</v>
       </c>
       <c r="B66" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7657,32 +7657,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132019903</v>
+        <v>132019888</v>
       </c>
       <c r="B68" t="n">
-        <v>75428</v>
+        <v>91909</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7692,10 +7692,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>669148</v>
+        <v>669198</v>
       </c>
       <c r="R68" t="n">
-        <v>6692645</v>
+        <v>6692759</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7739,9 +7739,19 @@
       <c r="AG68" t="b">
         <v>0</v>
       </c>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>Gran</t>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -7759,10 +7769,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132019898</v>
+        <v>132019903</v>
       </c>
       <c r="B69" t="n">
-        <v>80336</v>
+        <v>75428</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7770,21 +7780,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6456</v>
+        <v>6426</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7794,10 +7804,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>669154</v>
+        <v>669148</v>
       </c>
       <c r="R69" t="n">
-        <v>6692684</v>
+        <v>6692645</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7843,7 +7853,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Populas tremula</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -7861,10 +7871,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132019901</v>
+        <v>132019898</v>
       </c>
       <c r="B70" t="n">
-        <v>75428</v>
+        <v>80336</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7872,21 +7882,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6426</v>
+        <v>6456</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7896,7 +7906,7 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>669196</v>
+        <v>669154</v>
       </c>
       <c r="R70" t="n">
         <v>6692684</v>
@@ -7945,7 +7955,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>Populas tremula</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -7963,32 +7973,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132019888</v>
+        <v>132019901</v>
       </c>
       <c r="B71" t="n">
-        <v>91909</v>
+        <v>75428</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7998,10 +8008,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>669198</v>
+        <v>669196</v>
       </c>
       <c r="R71" t="n">
-        <v>6692759</v>
+        <v>6692684</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8045,19 +8055,9 @@
       <c r="AG71" t="b">
         <v>0</v>
       </c>
-      <c r="AJ71" t="inlineStr">
+      <c r="AI71" t="inlineStr">
         <is>
           <t>gran</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8177,32 +8177,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132019921</v>
+        <v>132019887</v>
       </c>
       <c r="B73" t="n">
-        <v>101325</v>
+        <v>91909</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8212,10 +8212,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>669204</v>
+        <v>669285</v>
       </c>
       <c r="R73" t="n">
-        <v>6692803</v>
+        <v>6692776</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8258,6 +8258,21 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -8274,32 +8289,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132019887</v>
+        <v>132019921</v>
       </c>
       <c r="B74" t="n">
-        <v>91909</v>
+        <v>101326</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8309,10 +8324,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>669285</v>
+        <v>669204</v>
       </c>
       <c r="R74" t="n">
-        <v>6692776</v>
+        <v>6692803</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8355,21 +8370,6 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY81"/>
+  <dimension ref="A1:AY89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9108,6 +9108,862 @@
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>132894816</v>
+      </c>
+      <c r="B82" t="n">
+        <v>57142</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Östensbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>669240</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6692630</v>
+      </c>
+      <c r="S82" t="n">
+        <v>15</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Lämpligt tjäderhabitat</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>132894834</v>
+      </c>
+      <c r="B83" t="n">
+        <v>57142</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Östensbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>669227</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6692618</v>
+      </c>
+      <c r="S83" t="n">
+        <v>15</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Lämpligt tjäderhabitat</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>132894817</v>
+      </c>
+      <c r="B84" t="n">
+        <v>57142</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Östensbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>669242</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6692636</v>
+      </c>
+      <c r="S84" t="n">
+        <v>15</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Lämpligt tjäderhabitat</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>132894829</v>
+      </c>
+      <c r="B85" t="n">
+        <v>57142</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Östensbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>669083</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6692464</v>
+      </c>
+      <c r="S85" t="n">
+        <v>15</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Lämpligt tjäderhabitat</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>132894821</v>
+      </c>
+      <c r="B86" t="n">
+        <v>57142</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Östensbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>669229</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6692604</v>
+      </c>
+      <c r="S86" t="n">
+        <v>15</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Lämpligt tjäderhabitat</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>132894819</v>
+      </c>
+      <c r="B87" t="n">
+        <v>57142</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Östensbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>669194</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6692660</v>
+      </c>
+      <c r="S87" t="n">
+        <v>15</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Lämpligt tjäderhabitat</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>132894818</v>
+      </c>
+      <c r="B88" t="n">
+        <v>57142</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Östensbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>669192</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6692632</v>
+      </c>
+      <c r="S88" t="n">
+        <v>15</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Lämpligt tjäderhabitat</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>132894820</v>
+      </c>
+      <c r="B89" t="n">
+        <v>57142</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Östensbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>669183</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6692775</v>
+      </c>
+      <c r="S89" t="n">
+        <v>15</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Lämpligt tjäderhabitat</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -10822,10 +10822,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>133215169</v>
+        <v>133215175</v>
       </c>
       <c r="B98" t="n">
-        <v>91918</v>
+        <v>58444</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10833,34 +10833,39 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1202</v>
+        <v>103018</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>669207</v>
+        <v>669176</v>
       </c>
       <c r="R98" t="n">
-        <v>6692581</v>
+        <v>6692638</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10903,21 +10908,6 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ98" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK98" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO98" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
@@ -10934,10 +10924,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>133215175</v>
+        <v>133215169</v>
       </c>
       <c r="B99" t="n">
-        <v>58444</v>
+        <v>91918</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10945,39 +10935,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>103018</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>669176</v>
+        <v>669207</v>
       </c>
       <c r="R99" t="n">
-        <v>6692638</v>
+        <v>6692581</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11020,6 +11005,21 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
@@ -11036,10 +11036,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>133215173</v>
+        <v>133215172</v>
       </c>
       <c r="B100" t="n">
-        <v>111405</v>
+        <v>104642</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11047,16 +11047,16 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>219711</v>
+        <v>222412</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -11071,10 +11071,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>669404</v>
+        <v>669413</v>
       </c>
       <c r="R100" t="n">
-        <v>6692813</v>
+        <v>6692806</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11133,10 +11133,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>133215163</v>
+        <v>133215173</v>
       </c>
       <c r="B101" t="n">
-        <v>107624</v>
+        <v>111405</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11144,16 +11144,16 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>219686</v>
+        <v>219711</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -11161,31 +11161,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>669300</v>
+        <v>669404</v>
       </c>
       <c r="R101" t="n">
-        <v>6692773</v>
+        <v>6692813</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11244,10 +11230,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>133215172</v>
+        <v>133215163</v>
       </c>
       <c r="B102" t="n">
-        <v>104642</v>
+        <v>107624</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11255,16 +11241,16 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>222412</v>
+        <v>219686</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -11272,17 +11258,31 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>669413</v>
+        <v>669300</v>
       </c>
       <c r="R102" t="n">
-        <v>6692806</v>
+        <v>6692773</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11453,10 +11453,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133215190</v>
+        <v>133215176</v>
       </c>
       <c r="B104" t="n">
-        <v>106170</v>
+        <v>91929</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11464,21 +11464,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>221141</v>
+        <v>1205</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11488,10 +11488,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>669293</v>
+        <v>669259</v>
       </c>
       <c r="R104" t="n">
-        <v>6692782</v>
+        <v>6692692</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11534,6 +11534,21 @@
       </c>
       <c r="AG104" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
@@ -11550,10 +11565,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>133215176</v>
+        <v>133215190</v>
       </c>
       <c r="B105" t="n">
-        <v>91929</v>
+        <v>106170</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11561,21 +11576,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1205</v>
+        <v>221141</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11585,10 +11600,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>669259</v>
+        <v>669293</v>
       </c>
       <c r="R105" t="n">
-        <v>6692692</v>
+        <v>6692782</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11631,21 +11646,6 @@
       </c>
       <c r="AG105" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ105" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK105" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO105" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY132"/>
+  <dimension ref="A1:AZ132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860649</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860651</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860652</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132019905</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133215191</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860588</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1381,6 +1416,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860589</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1478,6 +1518,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860591</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1575,6 +1620,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860593</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1672,6 +1722,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860595</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1784,6 +1839,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132019886</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1896,6 +1956,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132019887</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2008,6 +2073,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132019888</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2120,6 +2190,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132019889</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2232,6 +2307,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133215168</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2344,6 +2424,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133215169</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2456,6 +2541,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133215170</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2568,6 +2658,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133215176</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2680,6 +2775,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860622</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2792,6 +2892,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133215181</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2904,6 +3009,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860688</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3016,6 +3126,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860689</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3128,6 +3243,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860690</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3240,6 +3360,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860691</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3337,6 +3462,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860623</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3434,6 +3564,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860624</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3531,6 +3666,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860625</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3628,6 +3768,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860626</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3725,6 +3870,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860627</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3822,6 +3972,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860628</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3919,6 +4074,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860629</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4016,6 +4176,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860630</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4113,6 +4278,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860631</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4210,6 +4380,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860632</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4307,6 +4482,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860633</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4404,6 +4584,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133215187</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4501,6 +4686,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133215188</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4613,6 +4803,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860603</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4730,6 +4925,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860604</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4827,6 +5027,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860605</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4924,6 +5129,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860607</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5026,6 +5236,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132019904</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5138,6 +5353,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860621</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5250,6 +5470,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860660</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5362,6 +5587,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860661</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5474,6 +5704,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860662</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5576,6 +5811,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132019908</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5688,6 +5928,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133215192</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5800,6 +6045,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133215193</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5912,6 +6162,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133215194</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6009,6 +6264,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860648</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6111,6 +6371,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132019901</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6213,6 +6478,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132019903</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6325,6 +6595,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860613</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6437,6 +6712,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860614</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6549,6 +6829,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860615</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6666,6 +6951,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860616</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6778,6 +7068,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860617</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6890,6 +7185,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860618</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7002,6 +7302,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860620</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7104,6 +7409,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132019897</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7206,6 +7516,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132019898</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7308,6 +7623,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132019899</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7420,6 +7740,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133215180</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7532,6 +7857,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860682</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7644,6 +7974,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860683</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7756,6 +8091,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860684</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7868,6 +8208,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860685</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7970,6 +8315,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132019918</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8072,6 +8422,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132019919</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8184,6 +8539,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860686</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8286,6 +8646,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860608</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8388,6 +8753,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860609</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8490,6 +8860,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132019896</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8597,6 +8972,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132894816</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8704,6 +9084,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132894817</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8811,6 +9196,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132894818</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8918,6 +9308,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132894819</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9025,6 +9420,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132894820</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9132,6 +9532,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132894821</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9239,6 +9644,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132894828</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9346,6 +9756,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132894829</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9453,6 +9868,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132894831</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9560,6 +9980,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132894834</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9672,6 +10097,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860687</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9784,6 +10214,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860653</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9896,6 +10331,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860654</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10008,6 +10448,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860655</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10120,6 +10565,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860656</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10232,6 +10682,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860658</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10334,6 +10789,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132019906</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10436,6 +10896,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132019907</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10538,6 +11003,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132019900</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10640,6 +11110,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133204383</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10742,6 +11217,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133215174</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10844,6 +11324,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133215175</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10946,6 +11431,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132019892</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11048,6 +11538,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132019893</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11150,6 +11645,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132019894</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11252,6 +11752,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132019895</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11354,6 +11859,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860596</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11456,6 +11966,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860597</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11565,6 +12080,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132019890</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11676,6 +12196,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133215163</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11773,6 +12298,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133215173</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11870,6 +12400,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133215190</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11967,6 +12502,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133215164</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12064,6 +12604,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133215172</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12161,6 +12706,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860692</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12258,6 +12808,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860694</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12355,6 +12910,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860695</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12452,6 +13012,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860696</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12549,6 +13114,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860697</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12646,6 +13216,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860698</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12743,6 +13318,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860699</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12840,6 +13420,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860700</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12937,6 +13522,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860701</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13034,6 +13624,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860702</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13131,6 +13726,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132019920</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13228,6 +13828,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132019921</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13325,6 +13930,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132019922</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13422,6 +14032,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133215202</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13519,6 +14134,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133215203</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13616,6 +14236,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133215182</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13728,6 +14353,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860634</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13840,6 +14470,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860635</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13952,6 +14587,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860637</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14064,6 +14704,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860639</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14176,6 +14821,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860641</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14288,6 +14938,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860642</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14400,8 +15055,146 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860643</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>